--- a/Contact_List_REL.xlsx
+++ b/Contact_List_REL.xlsx
@@ -750,7 +750,7 @@
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>Quoted forwarded header 'From: Samuel Beaumont &lt;sam@arcandco.com&gt;' in 'FW: North Lakes Opportunity' 11/02/2025</t>
+          <t>Arc &amp; Co broker who sent REL the North Lakes opportunity (Feb 2025).</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>Arc &amp; Co broker on the Melton Mowbray &amp; Lowestoft bridge loan</t>
+          <t>Arc &amp; Co broker on the Melton Mowbray &amp; Lowestoft bridge loan. Has since moved to FRP Advisory — use the frpadvisory.com address.</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Amy Woodthorpe</t>
+          <t>Alexander Pasche</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -875,55 +875,47 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Avison Young</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>London Investment</t>
-        </is>
-      </c>
+          <t>Avier Capital</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>amy.woodthorpe@avisonyoung.com</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+44 7887801762</t>
-        </is>
-      </c>
+          <t>alexander.pasche@aviercapital.com</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>Avison Young debt advisory team on the regional office financing (Eagle Tower, Cheltenham)</t>
+          <t>Forwarded HREF's letter of support to brokers after the MFS and Century Capital administrations, Feb 2026.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Richard Day</t>
+          <t>Amy Woodthorpe</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -938,17 +930,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Head of Debt Advisory, Capital Markets</t>
+          <t>London Investment</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>richard.day@avisonyoung.com</t>
+          <t>amy.woodthorpe@avisonyoung.com</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>+44 (0)782 531 3653</t>
+          <t>+44 7887801762</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -974,14 +966,14 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>Debt advisor who brought Eagle Tower, Cheltenham; lost on pricing</t>
+          <t>Avison Young debt advisory team on the regional office financing (Eagle Tower, Cheltenham)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Alison Zambrano</t>
+          <t>Richard Day</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -991,47 +983,55 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>BBS Capital</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
+          <t>Avison Young</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Head of Debt Advisory, Capital Markets</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>alison@bbscapital.com</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr"/>
+          <t>richard.day@avisonyoung.com</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0)782 531 3653</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>BBS Capital side on the Kentish Town co-living funding enquiry</t>
+          <t>Debt advisor who brought Eagle Tower, Cheltenham; lost on pricing</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Joseph Clery</t>
+          <t>Alison Zambrano</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1047,7 +1047,7 @@
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>joseph@bbscapital.com</t>
+          <t>alison@bbscapital.com</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Dominic Gibson</t>
+          <t>Joseph Clery</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Beckford Advisory</t>
+          <t>BBS Capital</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>dominic@beckfordadvisory.com</t>
+          <t>joseph@bbscapital.com</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="I12" s="6" t="n">
@@ -1124,14 +1124,14 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>Beckford colleague on the GBP 25m prime central London bridge</t>
+          <t>BBS Capital side on the Kentish Town co-living funding enquiry</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>John Kerrigan</t>
+          <t>Dominic Gibson</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1144,21 +1144,13 @@
           <t>Beckford Advisory</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
+      <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>john@beckfordadvisory.com</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+44 (0) 7508 225 678</t>
-        </is>
-      </c>
+          <t>dominic@beckfordadvisory.com</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>2026-06-15</t>
@@ -1170,26 +1162,26 @@
         </is>
       </c>
       <c r="I13" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>Brought the GBP 25m prime central London bridge loan</t>
+          <t>Beckford colleague on the £25m prime central London bridge</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Charlie Latimer</t>
+          <t>John Kerrigan</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1199,32 +1191,36 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Blackbear Capital Partners LLP</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
+          <t>Beckford Advisory</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>charlie.latimer@blackbear-capital.com</t>
+          <t>john@beckfordadvisory.com</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>+44 (0)20 3750 6302, +44 (0)7716 234537</t>
+          <t>+44 (0) 7508 225 678</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>0</v>
@@ -1236,14 +1232,14 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>Debt advisor on 9 Eaton Place refinance and the Julius London GBP 25.5m acquisition facility (REL/OakNorth terms issued)</t>
+          <t>Brought the £25m prime central London bridge loan</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Heath Forusz</t>
+          <t>Charlie Latimer</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1259,10 +1255,14 @@
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>heath.forusz@blackbear-capital.com</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr"/>
+          <t>charlie.latimer@blackbear-capital.com</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0)20 3750 6302, +44 (0)7716 234537</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>2025-06-03</t>
@@ -1274,26 +1274,26 @@
         </is>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>Blackbear colleague of Charlie Latimer on 9 Eaton Place and The Julius London</t>
+          <t>Debt advisor on 9 Eaton Place refinance and the Julius London £25.5m acquisition facility (REL/OakNorth terms issued)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Richard Akka</t>
+          <t>Heath Forusz</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1303,24 +1303,24 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>C10 Finance</t>
+          <t>Blackbear Capital Partners LLP</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>richard@c10finance.com</t>
+          <t>heath.forusz@blackbear-capital.com</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="I16" s="6" t="n">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>Presented the Audley House, Liverpool mezzanine development finance request</t>
+          <t>Blackbear colleague of Charlie Latimer on 9 Eaton Place and The Julius London</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Raj Kumar</t>
+          <t>Richard Akka</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1353,24 +1353,24 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Carrowmore Capital</t>
+          <t>C10 Finance</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>raj@carrowmorecapital.com</t>
+          <t>richard@c10finance.com</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="I17" s="6" t="n">
@@ -1386,14 +1386,14 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>Brought Quayside House, Town Quay Wharf, Barking</t>
+          <t>Presented the Audley House, Liverpool mezzanine development finance request</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Archi Wallace Griffin</t>
+          <t>Raj Kumar</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1403,51 +1403,47 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Charles Irvine Group LLP</t>
+          <t>Carrowmore Capital</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>archi.griffin@charlesirvine.com</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+44 7415 931 700</t>
-        </is>
-      </c>
+          <t>raj@carrowmorecapital.com</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>Charles Irvine team on the SE industrial portfolio refinance and Croydon office refurbishment debt.</t>
+          <t>Brought Quayside House, Town Quay Wharf, Barking</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>David Cunnington</t>
+          <t>Archi Wallace Griffin</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1463,10 +1459,14 @@
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>david.cunnington@charlesirvine.com</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
+          <t>archi.griffin@charlesirvine.com</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>+44 7415 931 700</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>2025-10-07</t>
@@ -1478,26 +1478,26 @@
         </is>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>Charles Irvine contact on the Croydon office refurbishment debt and SE industrial portfolio refinance.</t>
+          <t>Charles Irvine team on the SE industrial portfolio refinance and Croydon office refurbishment debt.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Thomas Bland</t>
+          <t>David Cunnington</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -1510,21 +1510,13 @@
           <t>Charles Irvine Group LLP</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
+      <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>thomas.bland@charlesirvine.com</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+44 7584 518 263</t>
-        </is>
-      </c>
+          <t>david.cunnington@charlesirvine.com</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>2025-10-07</t>
@@ -1532,30 +1524,30 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="I20" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>Debt advisor on the £32.5m Southeast UK industrial portfolio refinancing.</t>
+          <t>Charles Irvine contact on the Croydon office refurbishment debt and SE industrial portfolio refinance.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Arsh Basi</t>
+          <t>Thomas Bland</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1565,47 +1557,55 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Conduit Real Estate (ConduitRE)</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
+          <t>Charles Irvine Group LLP</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>arsh@conduitre.com</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
+          <t>thomas.bland@charlesirvine.com</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>+44 7584 518 263</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>Quoted Cc header in 'FW: Project Bradley - Audley Cooper's Hill - Inventory Loan - REL Finance' 15/10/2025 (ConduitRE mandated by Audley Group).</t>
+          <t>Debt advisor on the £32.5m Southeast UK industrial portfolio refinancing.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Balaji Nagabhushan</t>
+          <t>Arsh Basi</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1615,20 +1615,16 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Conduit Real Estate (ConduitRE)</t>
+          <t>Conduit Real Estate</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>balaji@conduitre.com</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+44 7824 528631</t>
-        </is>
-      </c>
+          <t>arsh@conduitre.com</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
@@ -1652,14 +1648,14 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>Forwarded header and signature in 'FW: Project Bradley - Audley Cooper's Hill - Inventory Loan - REL Finance' 15/10/2025. Body: 'Conduit Real Estate are working exclusively for Audley Group (the Sponsor)'. Address 13 Hanover Square, London W1S 1HN.</t>
+          <t>Conduit Real Estate team member on Project Bradley, the Audley Cooper's Hill inventory loan; ConduitRE is mandated exclusively by Audley Group, the sponsor.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Jonathan Jay</t>
+          <t>Balaji Nagabhushan</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1669,16 +1665,20 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Conduit Real Estate (ConduitRE)</t>
+          <t>Conduit Real Estate</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>jonathan@conduitre.com</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
+          <t>balaji@conduitre.com</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>+44 7824 528631</t>
+        </is>
+      </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
@@ -1702,14 +1702,14 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>Quoted Cc header in 'FW: Project Bradley - Audley Cooper's Hill - Inventory Loan - REL Finance' 15/10/2025 (ConduitRE mandated by Audley Group).</t>
+          <t>Conduit Real Estate contact who took Project Bradley (Audley Cooper's Hill inventory loan) to REL; ConduitRE acts exclusively for Audley Group, the sponsor. Based at 13 Hanover Square, London W1S 1HN.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Garv Sud</t>
+          <t>Jonathan Jay</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -1719,24 +1719,24 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Elixir London</t>
+          <t>Conduit Real Estate</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>garv@elixirlondon.co.uk</t>
+          <t>jonathan@conduitre.com</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="I24" s="6" t="n">
@@ -1752,14 +1752,14 @@
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>Introduced the Edridge Place loan.</t>
+          <t>Conduit Real Estate team member on Project Bradley, the Audley Cooper's Hill inventory loan; ConduitRE is mandated exclusively by Audley Group, the sponsor.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Chris Whitney</t>
+          <t>Garv Sud</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1769,24 +1769,24 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Enness Global</t>
+          <t>Elixir London</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>chris@enness.co.uk</t>
+          <t>garv@elixirlondon.co.uk</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I25" s="6" t="n">
@@ -1802,14 +1802,14 @@
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>Debt broker; brought Project Atlantic to REL.</t>
+          <t>Introduced the Edridge Place loan.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Robert Sadler</t>
+          <t>Chris Whitney</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -1819,24 +1819,24 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Excellion Capital</t>
+          <t>Enness Global</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>robert.sadler@excellioncapital.com</t>
+          <t>chris@enness.co.uk</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="I26" s="6" t="n">
@@ -1852,14 +1852,14 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>Covers two deals-sheet targets ('Robert Sandler' and 'Excellion'). Quoted forwarded header 'From: Robert Sadler &lt;Robert.sadler@excellioncapital.com&gt;' in 'FW: The Whiteley' 08/04/2025</t>
+          <t>Debt broker; brought Project Atlantic to REL.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Abilasha Ranganathappa</t>
+          <t>Robert Sadler</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -1869,24 +1869,24 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Fast Forward Capital</t>
+          <t>Excellion Capital</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>abilash@fastforwardcapital.co.uk</t>
+          <t>robert.sadler@excellioncapital.com</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="I27" s="6" t="n">
@@ -1902,14 +1902,14 @@
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>Fast Forward Capital team on the Leicester Haymarket / Humberstone Gate bridge proposal.</t>
+          <t>Excellion Capital debt advisor; brought The Whiteley to REL (Apr 2025). Appears on the deals sheet as 'Robert Sandler'.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Imran Raja</t>
+          <t>Abilasha Ranganathappa</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -1919,55 +1919,47 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>First Wealth Management</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Commercial Finance Specialist</t>
-        </is>
-      </c>
+          <t>Fast Forward Capital</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>imran@firstwml.com</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>07900 493 468</t>
-        </is>
-      </c>
+          <t>abilash@fastforwardcapital.co.uk</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="6" t="inlineStr">
         <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
       <c r="I28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>First Wealth Management colleague of Jay Bhogal; Kettering enquiry.</t>
+          <t>Fast Forward Capital team on the Leicester Haymarket / Humberstone Gate bridge proposal.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Jay Bhogal</t>
+          <t>Imran Raja</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -1982,31 +1974,31 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Real Estate Funding Specialist</t>
+          <t>Commercial Finance Specialist</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>jay@firstwml.com</t>
+          <t>imran@firstwml.com</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>07912 262 511, 0207 486 0405</t>
+          <t>07900 493 468</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="I29" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" s="6" t="n">
         <v>0</v>
@@ -2018,14 +2010,14 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>Regular introducer - Sheffield City Centre bridge, 1 Farringdon Street, One Croydon and a 3-asset hotel refinance.</t>
+          <t>First Wealth Management colleague of Jay Bhogal; Kettering enquiry.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Tom Goldsmith</t>
+          <t>Jay Bhogal</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -2035,47 +2027,55 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>FRP Advisory</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
+          <t>First Wealth Management</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Real Estate Funding Specialist</t>
+        </is>
+      </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>tom.goldsmith@frpadvisory.com</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>jay@firstwml.com</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>07912 262 511, 0207 486 0405</t>
+        </is>
+      </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>FRP debt advisory - introduced the Chivenor Park, Barnstaple holiday park bridge enquiry (declined, too small).</t>
+          <t>Regular introducer - Sheffield City Centre bridge, 1 Farringdon Street, One Croydon and a 3-asset hotel refinance.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Tom Savill</t>
+          <t>Tom Goldsmith</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -2091,18 +2091,18 @@
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>tom.savill@frpadvisory.com</t>
+          <t>tom.goldsmith@frpadvisory.com</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="I31" s="6" t="n">
@@ -2118,14 +2118,14 @@
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>FRP debt advisory - introduced The Store Room, Solihull bridge enquiry (£10.2m indicative terms issued).</t>
+          <t>FRP debt advisory; introduced the Chivenor Park, Barnstaple holiday park bridge. Previously at Arc &amp; Co.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Emma Solazzo</t>
+          <t>Tom Savill</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -2135,51 +2135,47 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>GLPG</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Capital Advisory</t>
-        </is>
-      </c>
+          <t>FRP Advisory</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>emma.solazzo@glpg.co.uk</t>
+          <t>tom.savill@frpadvisory.com</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>Works with Nick Swerner in GLPG Capital Advisory; negotiated the OakNorth/REL Dulwich terms.</t>
+          <t>FRP debt advisory - introduced The Store Room, Solihull bridge enquiry (£10.2m indicative terms issued).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>GLPG Capital Advisory</t>
+          <t>Emma Solazzo</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -2192,44 +2188,48 @@
           <t>GLPG</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Capital Advisory</t>
+        </is>
+      </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>capital@glpg.co.uk</t>
+          <t>emma.solazzo@glpg.co.uk</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>GLPG Capital Advisory shared team mailbox.</t>
+          <t>Works with Nick Swerner in GLPG Capital Advisory; negotiated the OakNorth/REL Dulwich terms.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Johnny Grassick</t>
+          <t>GLPG Capital Advisory</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -2245,18 +2245,18 @@
       <c r="D34" s="4" t="inlineStr"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>johnny.grassick@glpg.co.uk</t>
+          <t>capital@glpg.co.uk</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I34" s="6" t="n">
@@ -2272,14 +2272,14 @@
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>GLPG capital advisory contact on the Cresswick Dulwich financing.</t>
+          <t>GLPG Capital Advisory shared team mailbox.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Nick Swerner</t>
+          <t>Johnny Grassick</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -2292,24 +2292,16 @@
           <t>GLPG</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
+      <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>nick.swerner@glpg.co.uk</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>0203 089 0695, 07966 487 790</t>
-        </is>
-      </c>
+          <t>johnny.grassick@glpg.co.uk</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
@@ -2318,26 +2310,26 @@
         </is>
       </c>
       <c r="I35" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>Debt advisor on the Cresswick Dulwich deal with OakNorth, and on Housing First Group.</t>
+          <t>GLPG capital advisory contact on the Cresswick Dulwich financing.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Nick Jones</t>
+          <t>Nick Swerner</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -2347,47 +2339,55 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>GSB Global</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr"/>
+          <t>GLPG</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>nick.jones@gsbglobal.com</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr"/>
+          <t>nick.swerner@glpg.co.uk</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>0203 089 0695, 07966 487 790</t>
+        </is>
+      </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J36" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>Origin of a GSB bridging enquiry forwarded to REL</t>
+          <t>Debt advisor on the Cresswick Dulwich deal with OakNorth, and on Housing First Group.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>James Daniels</t>
+          <t>Nick Jones</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -2397,24 +2397,24 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Hallcroft Finance</t>
+          <t>GSB Global</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>james@hallcroftfinance.co.uk</t>
+          <t>nick.jones@gsbglobal.com</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I37" s="6" t="n">
@@ -2430,14 +2430,14 @@
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>Presented a developer exit on The Courtyard, West Street, Farnham</t>
+          <t>Origin of a GSB bridging enquiry forwarded to REL</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Imad Fathallah</t>
+          <t>James Daniels</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -2447,51 +2447,47 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>IMF Finance</t>
+          <t>Hallcroft Finance</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>imad@imffinance.com</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+44 7798 530234</t>
-        </is>
-      </c>
+          <t>james@hallcroftfinance.co.uk</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="I38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>Circulated a loan request secured on ultra-prime collateral</t>
+          <t>Presented a developer exit on The Courtyard, West Street, Farnham</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Lee Neenan</t>
+          <t>Imad Fathallah</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -2501,32 +2497,32 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Irwell Property Finance</t>
+          <t>IMF Finance</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>lee@irwellpropertyfinance.co.uk</t>
+          <t>imad@imffinance.com</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>07854 455559, 0161 537 7099</t>
+          <t>+44 7798 530234</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="I39" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J39" s="6" t="n">
         <v>0</v>
@@ -2538,14 +2534,14 @@
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>Manchester-based introducer; brought Rutland Gate and new enquiries, charges a 1% broker fee</t>
+          <t>Circulated a loan request secured on ultra-prime collateral</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Adrian Dowdle</t>
+          <t>Lee Neenan</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -2555,47 +2551,51 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Karis Capital</t>
+          <t>Irwell Property Finance</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>adrian.dowdle@kariscapital.co.uk</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr"/>
+          <t>lee@irwellpropertyfinance.co.uk</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>07854 455559, 0161 537 7099</t>
+        </is>
+      </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I40" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>Karis Capital contact on the Milton Keynes enquiry</t>
+          <t>Manchester-based introducer; brought Rutland Gate and new enquiries, charges a 1% broker fee</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Nicholas Christofi</t>
+          <t>Adrian Dowdle</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -2611,7 +2611,7 @@
       <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>nicholas.christofi@kariscapital.co.uk</t>
+          <t>adrian.dowdle@kariscapital.co.uk</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Nirav Patel</t>
+          <t>Nicholas Christofi</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -2655,19 +2655,19 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Mantra Commercial</t>
+          <t>Karis Capital</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>nirav@mantracommercial.com</t>
+          <t>nicholas.christofi@kariscapital.co.uk</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -2688,14 +2688,14 @@
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>Introduced 77 and 87-89 Walton Street GBP 9m request and The Stroud Hotel</t>
+          <t>Karis Capital contact on the Milton Keynes enquiry</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Rickesh Patel</t>
+          <t>Nirav Patel</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -2711,7 +2711,7 @@
       <c r="D43" s="4" t="inlineStr"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>rickesh@mantracommercial.com</t>
+          <t>nirav@mantracommercial.com</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I43" s="6" t="n">
@@ -2738,14 +2738,14 @@
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
-          <t>Main Mantra contact - Kamco GBP 22.5m, Walton Street GBP 9m, The Stroud Hotel</t>
+          <t>Introduced 77 and 87-89 Walton Street £9m request and The Stroud Hotel</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Zahra</t>
+          <t>Rickesh Patel</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -2761,13 +2761,13 @@
       <c r="D44" s="4" t="inlineStr"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>zahra@mantracommercial.com</t>
+          <t>rickesh@mantracommercial.com</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
@@ -2788,14 +2788,14 @@
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>On the Elixir House GBP 5m commercial bridging facility</t>
+          <t>Main Mantra contact - Kamco £22.5m, Walton Street £9m, The Stroud Hotel</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Nimesh Sanghrajka</t>
+          <t>Zahra</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -2805,24 +2805,24 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Mantra Group</t>
+          <t>Mantra Commercial</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>nimesh@mantra-group.com</t>
+          <t>zahra@mantracommercial.com</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="I45" s="6" t="n">
@@ -2838,14 +2838,14 @@
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
-          <t>Mantra debt brokerage; on the Kamco GBP 22.5m enquiry</t>
+          <t>On the Elixir House £5m commercial bridging facility</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Lindsay Baker</t>
+          <t>Nimesh Sanghrajka</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -2855,28 +2855,24 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Melbray London</t>
+          <t>Mantra Group</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>lindsay@melbraylondon.com</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>+44 7557 749580</t>
-        </is>
-      </c>
+          <t>nimesh@mantra-group.com</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I46" s="6" t="n">
@@ -2892,14 +2888,14 @@
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t>Finance brokerage; on the Indigo Scott Hammersmith development thread</t>
+          <t>Mantra debt brokerage; on the Kamco £22.5m enquiry</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Max Warren</t>
+          <t>Lindsay Baker</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -2915,10 +2911,14 @@
       <c r="D47" s="4" t="inlineStr"/>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>max@melbraylondon.com</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr"/>
+          <t>lindsay@melbraylondon.com</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>+44 7557 749580</t>
+        </is>
+      </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
           <t>2026-03-11</t>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="I47" s="6" t="n">
@@ -2942,14 +2942,14 @@
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
-          <t>Founder of Melbray; brokering the Indigo Scott Hammersmith development</t>
+          <t>Finance brokerage; on the Indigo Scott Hammersmith development thread</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Simon Warren</t>
+          <t>Max Warren</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -2965,7 +2965,7 @@
       <c r="D48" s="4" t="inlineStr"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>simon@melbraylondon.com</t>
+          <t>max@melbraylondon.com</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
@@ -2992,14 +2992,14 @@
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>On the Indigo Scott Hammersmith development enquiry</t>
+          <t>Founder of Melbray; brokering the Indigo Scott Hammersmith development</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>George Melling</t>
+          <t>Simon Warren</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -3009,24 +3009,24 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Merry Oaks</t>
+          <t>Melbray London</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>george@merryoaks.com</t>
+          <t>simon@melbraylondon.com</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I49" s="6" t="n">
@@ -3042,14 +3042,14 @@
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
-          <t>Introduced High Trees, Bishops Avenue and other Camden assets</t>
+          <t>On the Indigo Scott Hammersmith development enquiry</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Saam Lowni</t>
+          <t>George Melling</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -3065,14 +3065,10 @@
       <c r="D50" s="4" t="inlineStr"/>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>saam@merryoaks.com</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+44 (0) 203 797 7559, +44 (0) 749 536 2211</t>
-        </is>
-      </c>
+          <t>george@merryoaks.com</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="6" t="inlineStr">
         <is>
           <t>2025-03-22</t>
@@ -3103,7 +3099,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Keryn Thompsett</t>
+          <t>Saam Lowni</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -3113,26 +3109,30 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Moorhall Capital</t>
+          <t>Merry Oaks</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>keryn@moorhallcapital.com</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr"/>
+          <t>saam@merryoaks.com</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0) 203 797 7559, +44 (0) 749 536 2211</t>
+        </is>
+      </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
       <c r="I51" s="6" t="n">
         <v>0</v>
       </c>
@@ -3146,14 +3146,14 @@
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>Real estate capital advisory; annual drinks invitation</t>
+          <t>Introduced High Trees, Bishops Avenue and other Camden assets</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Robert Jones</t>
+          <t>Keryn Thompsett</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -3169,7 +3169,7 @@
       <c r="D52" s="4" t="inlineStr"/>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>rob@moorhallcapital.com</t>
+          <t>keryn@moorhallcapital.com</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
@@ -3196,14 +3196,14 @@
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>Founder of Moorhall Capital, real estate debt advisory</t>
+          <t>Real estate capital advisory; annual drinks invitation</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Tom Boize</t>
+          <t>Robert Jones</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -3219,7 +3219,7 @@
       <c r="D53" s="4" t="inlineStr"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>tom@moorhallcapital.com</t>
+          <t>rob@moorhallcapital.com</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
@@ -3246,14 +3246,14 @@
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>Real estate capital advisory contact at Moorhall</t>
+          <t>Founder of Moorhall Capital, real estate debt advisory</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Raed Hanna</t>
+          <t>Tom Boize</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -3263,24 +3263,24 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Mutual Finance</t>
+          <t>Moorhall Capital</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>r.hanna@mutual-finance.co.uk</t>
+          <t>tom@moorhallcapital.com</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I54" s="6" t="n">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>Introduced the refinance of Centenary House, Manchester</t>
+          <t>Real estate capital advisory contact at Moorhall</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Tariq Ansari</t>
+          <t>Raed Hanna</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -3319,18 +3319,18 @@
       <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>t.ansari@mutual-finance.co.uk</t>
+          <t>r.hanna@mutual-finance.co.uk</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I55" s="6" t="n">
@@ -3346,14 +3346,14 @@
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
-          <t>New enquiry - refinance of two luxury houses in Wimbledon Village</t>
+          <t>Introduced the refinance of Centenary House, Manchester</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Masood Rashid</t>
+          <t>Tariq Ansari</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -3363,24 +3363,24 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Opes Financial Partners</t>
+          <t>Mutual Finance</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>masood.rashid@opesfp.com</t>
+          <t>t.ansari@mutual-finance.co.uk</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="I56" s="6" t="n">
@@ -3396,14 +3396,14 @@
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>Opes introduction of 58 Pont Street, London SW1X</t>
+          <t>New enquiry - refinance of two luxury houses in Wimbledon Village</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Matthew Davies</t>
+          <t>Masood Rashid</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -3419,7 +3419,7 @@
       <c r="D57" s="4" t="inlineStr"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>matthew.davies@opesfp.com</t>
+          <t>masood.rashid@opesfp.com</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr"/>
@@ -3453,7 +3453,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Lewis</t>
+          <t>Matthew Davies</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -3463,24 +3463,24 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Pure Structured Finance</t>
+          <t>Opes Financial Partners</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>lewis@purestructuredfinance.co.uk</t>
+          <t>matthew.davies@opesfp.com</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I58" s="6" t="n">
@@ -3496,14 +3496,14 @@
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
-          <t>On the Project Nest debt raise, Elephant &amp; Castle SE1</t>
+          <t>Opes introduction of 58 Pont Street, London SW1X</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Lewis</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -3519,7 +3519,7 @@
       <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>tom@purestructuredfinance.co.uk</t>
+          <t>lewis@purestructuredfinance.co.uk</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr"/>
@@ -3553,7 +3553,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Dan Tisdall</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -3563,47 +3563,47 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Quanta Investment</t>
+          <t>Pure Structured Finance</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>dan@quanta-investment.com</t>
+          <t>tom@purestructuredfinance.co.uk</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="I60" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J60" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
-          <t>Introduced the 11, 13 &amp; 15 Askew Road W12 bridge; takes 1% of the 2% arrangement fee. Trades as Capital and Property Limited</t>
+          <t>On the Project Nest debt raise, Elephant &amp; Castle SE1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Christopher Khoi</t>
+          <t>Dan Tisdall</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -3613,13 +3613,13 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>RCP Finance</t>
+          <t>Quanta Investment</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>ckhoi@rcpfinance.com</t>
+          <t>dan@quanta-investment.com</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr"/>
@@ -3630,30 +3630,30 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I61" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J61" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
-          <t>On a Canterbury hotel finance enquiry</t>
+          <t>Introduced the 11, 13 &amp; 15 Askew Road W12 bridge; takes 1% of the 2% arrangement fee. Trades as Capital and Property Limited</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Ruben Chicheportiche</t>
+          <t>Christopher Khoi</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -3669,7 +3669,7 @@
       <c r="D62" s="4" t="inlineStr"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>rchicheportiche@rcpfinance.com</t>
+          <t>ckhoi@rcpfinance.com</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr"/>
@@ -3703,7 +3703,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Suleman Rafiq</t>
+          <t>Ruben Chicheportiche</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -3713,24 +3713,24 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Ros Capital (roscap.co.uk)</t>
+          <t>RCP Finance</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>suleman@roscap.co.uk</t>
+          <t>rchicheportiche@rcpfinance.com</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I63" s="6" t="n">
@@ -3746,14 +3746,14 @@
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
-          <t>Quoted To header "To: 'Suleman Rafiq' &lt;suleman@roscap.co.uk&gt;" in 'FW: 188 Wilmslow Road, Fallowfield, Manchester, M14 6LJ | Commercial Asset Acquisition Bridge Required' 09/10/2025</t>
+          <t>On a Canterbury hotel finance enquiry</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Daniel O'Neil</t>
+          <t>Clemente Apollonj</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -3763,24 +3763,24 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>SPF Private Clients</t>
+          <t>Roscap</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>doneil@spf.co.uk</t>
+          <t>clemente@roscap.co.uk</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I64" s="6" t="n">
@@ -3796,14 +3796,14 @@
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
-          <t>SPF broker enquiring on REL's lending appetite</t>
+          <t>Sought a max-leverage Central London bridge, £12m purchase against £15m market value</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>David Yeadon</t>
+          <t>Suleman Rafiq</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -3813,24 +3813,24 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>SPF Private Clients</t>
+          <t>Roscap</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>dyeadon@spf.co.uk</t>
+          <t>suleman@roscap.co.uk</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="I65" s="6" t="n">
@@ -3846,14 +3846,14 @@
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
-          <t>SPF broker; Beaufort Hotel, Knightsbridge refinance / bridge application</t>
+          <t>Partner &amp; CEO of Roscap, real estate debt and equity advisory; mandated to arrange the acquisition bridge on 188 Wilmslow Road, Fallowfield, Manchester (£4m net requested, Oct 2025, REL quoted £3.7m).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Laurie Marsh</t>
+          <t>Daniel O'Neil</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -3863,51 +3863,47 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>TRST Advisory</t>
+          <t>SPF Private Clients</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>laurie.marsh@trst-advisory.com</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>+44 7525 582897</t>
-        </is>
-      </c>
+          <t>doneil@spf.co.uk</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="I66" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
-          <t>TRST debt advisor alongside Sarah Strang; Cedarstone KWH and Castleton Works</t>
+          <t>SPF broker enquiring on REL's lending appetite</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Sarah Strang</t>
+          <t>David Yeadon</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -3917,51 +3913,47 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>TRST Advisory</t>
+          <t>SPF Private Clients</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>sarah.strang@trst-advisory.com</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+44 7742 466 791</t>
-        </is>
-      </c>
+          <t>dyeadon@spf.co.uk</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="I67" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J67" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L67" s="8" t="inlineStr">
         <is>
-          <t>Debt advisor running the Solaris / Castleton Works, Leeds c.£3.6m senior development bridge</t>
+          <t>SPF broker; Beaufort Hotel, Knightsbridge refinance / bridge application</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Devraj Ray</t>
+          <t>Laurie Marsh</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -3971,32 +3963,28 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Westdown Private Finance</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
+          <t>TRST Advisory</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr"/>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>devraj@westdownpf.com</t>
+          <t>laurie.marsh@trst-advisory.com</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>07770 929 757, 020 3633 1566</t>
+          <t>+44 7525 582897</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I68" s="6" t="n">
@@ -4012,14 +4000,14 @@
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
-          <t>Introduced 24 &amp; 30 Sussex Gardens, a hotel with Westminster bookings</t>
+          <t>TRST debt advisor alongside Sarah Strang; Cedarstone KWH and Castleton Works</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Indy Hora</t>
+          <t>Sarah Strang</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -4027,45 +4015,53 @@
           <t>Broker</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr"/>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>TRST Advisory</t>
+        </is>
+      </c>
       <c r="D69" s="4" t="inlineStr"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>indyhora@gmail.com</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr"/>
+          <t>sarah.strang@trst-advisory.com</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>+44 7742 466 791</t>
+        </is>
+      </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I69" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K69" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
-          <t>Source of a £20m hotel financing enquiry forwarded into REL</t>
+          <t>Debt advisor running the Solaris / Castleton Works, Leeds c.£3.6m senior development bridge</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Manish Babla</t>
+          <t>Chris Kelly</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -4073,80 +4069,76 @@
           <t>Broker</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr"/>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>Debt Advisor</t>
-        </is>
-      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Waypoint Asset Management</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr"/>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>manishbabla@gmail.com</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>07866 435 144</t>
-        </is>
-      </c>
+          <t>chris.kelly@waypointam.co.uk</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="I70" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J70" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
-          <t>Independent introducer; brought Bemal Patel and Lincolns Inn Fields (£8.9m-£10.8m refi), takes 0.75% debt advisor fee</t>
+          <t>Consultant at Waypoint; introduced the Tribeca financing to OakNorth and REL via Jay Bhogal and ran the deal alongside Priya Harley at OakNorth.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>GB Bank Loan Completions Team</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>Lender / Bank</t>
+          <t>Jon Leefe</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Broker</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>GB Bank</t>
+          <t>Waypoint Asset Management</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>lct@thegbb.co.uk</t>
+          <t>jon.leefe@waypointam.co.uk</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="I71" s="6" t="n">
@@ -4162,41 +4154,41 @@
       </c>
       <c r="L71" s="8" t="inlineStr">
         <is>
-          <t>GB Bank completions team inbox used for the London Land Bromley drawdown</t>
+          <t>Waypoint colleague of Chris Kelly; named as a cover contact on the Tribeca financing.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>GB Bank Portfolio Team</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>Lender / Bank</t>
+          <t>Kirstyn Rutter</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Broker</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>GB Bank</t>
+          <t>Waypoint Asset Management</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>portfolio@thegbb.co.uk</t>
+          <t>kirstyn@waypointam.co.uk</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="I72" s="6" t="n">
@@ -4212,53 +4204,53 @@
       </c>
       <c r="L72" s="8" t="inlineStr">
         <is>
-          <t>GB Bank portfolio management inbox on the DNA Uxbridge loan</t>
+          <t>Waypoint colleague of Chris Kelly; named as a cover contact on the Tribeca financing.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Hanan Abubaker</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>Lender / Bank</t>
+          <t>Devraj Ray</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Broker</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>GB Bank</t>
+          <t>Westdown Private Finance</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Portfolio Manager</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>hanan.abubaker@thegbb.co.uk</t>
+          <t>devraj@westdownpf.com</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>03330 387623</t>
+          <t>07770 929 757, 020 3633 1566</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="I73" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J73" s="6" t="n">
         <v>0</v>
@@ -4270,107 +4262,91 @@
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
-          <t>GB Bank portfolio manager on the DNA Uxbridge loan</t>
+          <t>Introduced 24 &amp; 30 Sussex Gardens, a hotel with Westminster bookings</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Hardik Gogia</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>Lender / Bank</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>GB Bank</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>Business Development Manager</t>
-        </is>
-      </c>
+          <t>Indy Hora</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr"/>
+      <c r="D74" s="4" t="inlineStr"/>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>hardik.gogia@thegbb.co.uk</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+44 7586234864</t>
-        </is>
-      </c>
+          <t>indyhora@gmail.com</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I74" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J74" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K74" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
-          <t>Main GB Bank originator on the REL loan-on-loan line; London Land Bromley and DNA Uxbridge</t>
+          <t>Source of a £20m hotel financing enquiry forwarded into REL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Hrishikesh Tendulkar</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>Lender / Bank</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>GB Bank</t>
-        </is>
-      </c>
+          <t>Manish Babla</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr"/>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Loan Completions Manager</t>
+          <t>Debt Advisor</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>hrishikesh.tendulkar@thegbb.co.uk</t>
+          <t>manishbabla@gmail.com</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>+44 (0) 333 038 7563</t>
+          <t>07866 435 144</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I75" s="6" t="n">
@@ -4386,14 +4362,14 @@
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
-          <t>Runs GB Bank completions on the London Land Bromley drawdown</t>
+          <t>Independent introducer; brought Bemal Patel and Lincolns Inn Fields (£8.9m-£10.8m refi), takes 0.75% debt advisor fee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Nick Lynch</t>
+          <t>GB Bank Loan Completions Team</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -4406,52 +4382,44 @@
           <t>GB Bank</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>Head of Loan Originations &amp; Portfolio Management</t>
-        </is>
-      </c>
+      <c r="D76" s="4" t="inlineStr"/>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>nick.lynch@thegbb.co.uk</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+44 (0)333 038 7564</t>
-        </is>
-      </c>
+          <t>lct@thegbb.co.uk</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="I76" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J76" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K76" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L76" s="8" t="inlineStr">
         <is>
-          <t>GB Bank originations head across the London Land Bromley deal</t>
+          <t>GB Bank completions team inbox used for the London Land Bromley drawdown</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Pankaj Thukral</t>
+          <t>GB Bank Portfolio Team</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -4467,41 +4435,41 @@
       <c r="D77" s="4" t="inlineStr"/>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>pankaj.thukral@thegbb.co.uk</t>
+          <t>portfolio@thegbb.co.uk</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I77" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J77" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L77" s="8" t="inlineStr">
         <is>
-          <t>GB Bank decision-maker; agreed the c.£50m loan-on-loan framework at 1% fee / 4% margin</t>
+          <t>GB Bank portfolio management inbox on the DNA Uxbridge loan</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Pranav Jain</t>
+          <t>Hanan Abubaker</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
@@ -4514,13 +4482,21 @@
           <t>GB Bank</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr"/>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Portfolio Manager</t>
+        </is>
+      </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>pranav.jain@thegbb.co.uk</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr"/>
+          <t>hanan.abubaker@thegbb.co.uk</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>03330 387623</t>
+        </is>
+      </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -4532,22 +4508,26 @@
         </is>
       </c>
       <c r="I78" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J78" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K78" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
-        </is>
-      </c>
-      <c r="L78" s="8" t="inlineStr"/>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L78" s="8" t="inlineStr">
+        <is>
+          <t>GB Bank portfolio manager on the DNA Uxbridge loan</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Richard Clare</t>
+          <t>Hardik Gogia</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -4560,40 +4540,52 @@
           <t>GB Bank</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr"/>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>richard.clare@thegbb.co.uk</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr"/>
+          <t>hardik.gogia@thegbb.co.uk</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>+44 7586234864</t>
+        </is>
+      </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I79" s="6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J79" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K79" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
-        </is>
-      </c>
-      <c r="L79" s="8" t="inlineStr"/>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>Main GB Bank originator on the REL loan-on-loan line; London Land Bromley and DNA Uxbridge</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Saba Kebede</t>
+          <t>Hrishikesh Tendulkar</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
@@ -4606,40 +4598,52 @@
           <t>GB Bank</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr"/>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Loan Completions Manager</t>
+        </is>
+      </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>saba.kebede@thegbb.co.uk</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr"/>
+          <t>hrishikesh.tendulkar@thegbb.co.uk</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0) 333 038 7563</t>
+        </is>
+      </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="I80" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J80" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K80" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
-        </is>
-      </c>
-      <c r="L80" s="8" t="inlineStr"/>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L80" s="8" t="inlineStr">
+        <is>
+          <t>Runs GB Bank completions on the London Land Bromley drawdown</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Suravi Garg</t>
+          <t>Nick Lynch</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -4652,16 +4656,24 @@
           <t>GB Bank</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr"/>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Head of Loan Originations &amp; Portfolio Management</t>
+        </is>
+      </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>suravi.garg@thegbb.co.uk</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr"/>
+          <t>nick.lynch@thegbb.co.uk</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0)333 038 7564</t>
+        </is>
+      </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
@@ -4670,7 +4682,7 @@
         </is>
       </c>
       <c r="I81" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J81" s="6" t="n">
         <v>0</v>
@@ -4682,14 +4694,14 @@
       </c>
       <c r="L81" s="8" t="inlineStr">
         <is>
-          <t>GB Bank analyst; Bromley unit breakdown and comparables</t>
+          <t>GB Bank originations head across the London Land Bromley deal</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Alexey Shokhin</t>
+          <t>Pankaj Thukral</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
@@ -4699,55 +4711,47 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Hilco Real Estate Finance (HREF) UK</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
+          <t>GB Bank</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr"/>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>ashokhin@hilcoglobal.com</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+44 7984 748773</t>
-        </is>
-      </c>
+          <t>pankaj.thukral@thegbb.co.uk</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="I82" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J82" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K82" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L82" s="8" t="inlineStr">
         <is>
-          <t>HREF UK origination team contact block in the forwarded HREF letter of support, 24/02/2026.</t>
+          <t>GB Bank decision-maker; agreed the c.£50m loan-on-loan framework at 1% fee / 4% margin</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Asim Shirawani</t>
+          <t>Pranav Jain</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -4757,32 +4761,24 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Hilco Real Estate Finance (HREF) UK</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
+          <t>GB Bank</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr"/>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>ashirwani@hilcoglobal.com</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>+44 7846 632245</t>
-        </is>
-      </c>
+          <t>pranav.jain@thegbb.co.uk</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I83" s="6" t="n">
@@ -4796,16 +4792,12 @@
           <t>Named in a thread</t>
         </is>
       </c>
-      <c r="L83" s="8" t="inlineStr">
-        <is>
-          <t>HREF UK origination team contact block in the forwarded HREF letter of support, 24/02/2026.</t>
-        </is>
-      </c>
+      <c r="L83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Hilco Real Estate Finance UK (general mailbox)</t>
+          <t>Richard Clare</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -4815,24 +4807,24 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Hilco Real Estate Finance (HREF) UK</t>
+          <t>GB Bank</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr"/>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>info@hilcoglobal.com</t>
+          <t>richard.clare@thegbb.co.uk</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I84" s="6" t="n">
@@ -4846,16 +4838,12 @@
           <t>Named in a thread</t>
         </is>
       </c>
-      <c r="L84" s="8" t="inlineStr">
-        <is>
-          <t>Sender of the HREF broker letter quoted in 'FW: Letter of Support from HREF Chief Investment Officer...' — 'From: Hilco Real Estate Finance UK &lt;info@hilcoglobal.com&gt; Date: Tuesday, 24 February 2026'.</t>
-        </is>
-      </c>
+      <c r="L84" s="8" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Sean Adams</t>
+          <t>Saba Kebede</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -4865,32 +4853,24 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Hilco Real Estate Finance (HREF) UK</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
+          <t>GB Bank</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr"/>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>sadams@hilcoglobal.com</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>+44 7968 553341</t>
-        </is>
-      </c>
+          <t>saba.kebede@thegbb.co.uk</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I85" s="6" t="n">
@@ -4904,16 +4884,12 @@
           <t>Named in a thread</t>
         </is>
       </c>
-      <c r="L85" s="8" t="inlineStr">
-        <is>
-          <t>HREF UK origination team contact block inside forwarded 'Letter of Support from HREF Chief Investment Officer to Broker Clients Following MFS and Century Capital Administrations', forwarded to REL 25/02/2026 (original 24/02/2026).</t>
-        </is>
-      </c>
+      <c r="L85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Steve Allen</t>
+          <t>Suravi Garg</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -4923,55 +4899,47 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Hilco Real Estate Finance (HREF) UK</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
+          <t>GB Bank</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr"/>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>sallen@hilcoglobal.com</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>+44 7355 035003</t>
-        </is>
-      </c>
+          <t>suravi.garg@thegbb.co.uk</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I86" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K86" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
-          <t>HREF UK origination team contact block in the forwarded HREF letter of support, 24/02/2026.</t>
+          <t>GB Bank analyst; Bromley unit breakdown and comparables</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Anek Mhajan</t>
+          <t>Alexey Shokhin</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -4981,24 +4949,32 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Investec Bank plc</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr"/>
+          <t>Hilco Real Estate Finance</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>anek.mhajan@investec.com</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr"/>
+          <t>ashokhin@hilcoglobal.com</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>+44 7984 748773</t>
+        </is>
+      </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="I87" s="6" t="n">
@@ -5014,14 +4990,14 @@
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
-          <t>Forwarded header in 'FW: LOAN REQUEST SECURED BY ULTRA PRIME COLLATERAL' 12/02/2026 — Investec passed the Westvile Securities / 46 Holland Park refinance to REL.</t>
+          <t>UK origination contact at Hilco Real Estate Finance (HREF), an institutionally backed property lender covering £2m-£150m real estate loans.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Tom Bradshaw</t>
+          <t>Asim Shirawani</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
@@ -5031,24 +5007,32 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Investec Bank plc</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr"/>
+          <t>Hilco Real Estate Finance</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>tom.bradshaw@investec.com</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr"/>
+          <t>ashirwani@hilcoglobal.com</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>+44 7846 632245</t>
+        </is>
+      </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="I88" s="6" t="n">
@@ -5064,14 +5048,14 @@
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
-          <t>Quoted 'To:' header inside the same forwarded Westvile Securities loan request chain, 11/02/2026.</t>
+          <t>UK origination contact at Hilco Real Estate Finance (HREF), an institutionally backed property lender covering £2m-£150m real estate loans.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Deepesh Thakrar</t>
+          <t>Sean Adams</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -5081,55 +5065,55 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>OakNorth</t>
+          <t>Hilco Real Estate Finance</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Managing Director, Debt Finance</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>deepesh.thakrar@oaknorth.co.uk</t>
+          <t>sadams@hilcoglobal.com</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>+447776154745</t>
+          <t>+44 7968 553341</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="I89" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K89" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+        <v>0</v>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L89" s="8" t="inlineStr">
         <is>
-          <t>Senior OakNorth relationship - Elysian Stanmore and St Clements valuation</t>
+          <t>UK origination contact at Hilco Real Estate Finance (HREF), an institutionally backed property lender covering £2m-£150m real estate loans.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Gagandeep Singh</t>
+          <t>Steve Allen</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -5139,55 +5123,55 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>OakNorth</t>
+          <t>Hilco Real Estate Finance</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Senior Director, Portfolio Monitoring</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>gagandeep.singh@oaknorth.co.uk</t>
+          <t>sallen@hilcoglobal.com</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>+447586031463, +44 7586 031463</t>
+          <t>+44 7355 035003</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="I90" s="6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K90" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+        <v>0</v>
+      </c>
+      <c r="K90" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L90" s="8" t="inlineStr">
         <is>
-          <t>Runs OakNorth monitoring and MI reporting on the ESSL facility</t>
+          <t>UK origination contact at Hilco Real Estate Finance (HREF), an institutionally backed property lender covering £2m-£150m real estate loans.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Hemesh Patel</t>
+          <t>Anek Mhajan</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -5197,55 +5181,47 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>OakNorth</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>Director, Property Finance</t>
-        </is>
-      </c>
+          <t>Investec Bank plc</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr"/>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>hemesh.patel@oaknorth.co.uk</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>+447771375386, +44 7771 375386</t>
-        </is>
-      </c>
+          <t>anek.mhajan@investec.com</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I91" s="6" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J91" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L91" s="8" t="inlineStr">
         <is>
-          <t>GBP 32.5m Southeast industrial portfolio refinance and Plant Basingstoke</t>
+          <t>Investec contact who passed the Westvile Securities / 46 Holland Park refinance request across to REL (Feb 2026).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Luke Branchflower</t>
+          <t>Tom Bradshaw</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -5255,55 +5231,47 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>OakNorth</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>Associate, Debt Finance</t>
-        </is>
-      </c>
+          <t>Investec Bank plc</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr"/>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>luke.branchflower@oaknorth.co.uk</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>07582748413</t>
-        </is>
-      </c>
+          <t>tom.bradshaw@investec.com</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I92" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J92" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K92" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K92" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L92" s="8" t="inlineStr">
         <is>
-          <t>Debt finance associate on Plant Basingstoke</t>
+          <t>Investec contact on the Westvile Securities / 46 Holland Park loan request that was passed to REL (Feb 2026).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Magdalena Wierzchowska</t>
+          <t>Alisha Pandey</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -5313,24 +5281,16 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>OakNorth</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>Director, Legal and Transaction Management</t>
-        </is>
-      </c>
+          <t>OakNorth Bank</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr"/>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>magdalena.wierzchowska@oaknorth.co.uk</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+44 7841 423326</t>
-        </is>
-      </c>
+          <t>alisha.pandey@oaknorth.co.uk</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="6" t="inlineStr">
         <is>
           <t>2026-06-26</t>
@@ -5342,26 +5302,22 @@
         </is>
       </c>
       <c r="I93" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J93" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K93" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
-        </is>
-      </c>
-      <c r="L93" s="8" t="inlineStr">
-        <is>
-          <t>Legals and funds flow on the Charte Forte (Monument) REL refinance</t>
-        </is>
-      </c>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
+        </is>
+      </c>
+      <c r="L93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Shubham Kalra</t>
+          <t>Azayr Raja</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -5371,55 +5327,47 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>OakNorth</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>Deputy Vice President</t>
-        </is>
-      </c>
+          <t>OakNorth Bank</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr"/>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>shubham.kalra@oaknorth.co.uk</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+91-7206717001</t>
-        </is>
-      </c>
+          <t>azayr.raja@oaknorth.co.uk</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="I94" s="6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J94" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K94" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K94" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L94" s="8" t="inlineStr">
         <is>
-          <t>REL GMP information requests and the Oryx 2 Real Estate redemption</t>
+          <t>Copied on the OakNorth deal team for the St Clements final valuation</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Vivek Jaiswal</t>
+          <t>Chloe Skae</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -5429,39 +5377,39 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>OakNorth</t>
+          <t>OakNorth Bank</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Senior Associate</t>
+          <t>Director, Portfolio Management</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>vivek.jaiswal@oaknorth.co.uk</t>
+          <t>chloe.skae@oaknorth.co.uk</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>+91-9044471739, +91 9044471739</t>
+          <t>07858823534</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I95" s="6" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
@@ -5470,14 +5418,14 @@
       </c>
       <c r="L95" s="8" t="inlineStr">
         <is>
-          <t>Portfolio monitoring on ESSL - M&amp;S reports, reservations, bank statements</t>
+          <t>OakNorth portfolio manager on the Charte Forte (Monument) Limited facility</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Alisha Pandey</t>
+          <t>Deepesh Thakrar</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
@@ -5490,40 +5438,52 @@
           <t>OakNorth Bank</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr"/>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Managing Director, Debt Finance</t>
+        </is>
+      </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>alisha.pandey@oaknorth.co.uk</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr"/>
+          <t>deepesh.thakrar@oaknorth.co.uk</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>+447776154745</t>
+        </is>
+      </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I96" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
-        </is>
-      </c>
-      <c r="L96" s="8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L96" s="8" t="inlineStr">
+        <is>
+          <t>Senior OakNorth relationship - Elysian Stanmore and St Clements valuation</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Azayr Raja</t>
+          <t>Felix Price</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -5536,44 +5496,52 @@
           <t>OakNorth Bank</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr"/>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Senior Associate, Debt Finance</t>
+        </is>
+      </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>azayr.raja@oaknorth.co.uk</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr"/>
+          <t>felix.price@oaknorth.co.uk</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>07725474291</t>
+        </is>
+      </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I97" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J97" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K97" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
-          <t>Copied on the OakNorth deal team for the St Clements final valuation</t>
+          <t>Runs OakNorth pricing and fees on St Clements Lane and Peninsular House, where ON sits senior to REL</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Chloe Skae</t>
+          <t>Gagandeep Singh</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -5588,34 +5556,34 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Director, Portfolio Management</t>
+          <t>Senior Director, Portfolio Monitoring</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>chloe.skae@oaknorth.co.uk</t>
+          <t>gagandeep.singh@oaknorth.co.uk</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>07858823534</t>
+          <t>+447586031463</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I98" s="6" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J98" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
@@ -5624,14 +5592,14 @@
       </c>
       <c r="L98" s="8" t="inlineStr">
         <is>
-          <t>OakNorth portfolio manager on the Charte Forte (Monument) Limited facility</t>
+          <t>Runs OakNorth monitoring and MI reporting on the ESSL facility</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Felix Price</t>
+          <t>Hemesh Patel</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -5646,31 +5614,31 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Senior Associate, Debt Finance</t>
+          <t>Director, Property Finance</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>felix.price@oaknorth.co.uk</t>
+          <t>hemesh.patel@oaknorth.co.uk</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>07725474291</t>
+          <t>+447771375386</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I99" s="6" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="J99" s="6" t="n">
         <v>0</v>
@@ -5682,7 +5650,7 @@
       </c>
       <c r="L99" s="8" t="inlineStr">
         <is>
-          <t>Runs OakNorth pricing and fees on St Clements Lane and Peninsular House, where ON sits senior to REL</t>
+          <t>£32.5m Southeast industrial portfolio refinance and Plant Basingstoke</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5707,7 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Mandy Sanaghan</t>
+          <t>Luke Branchflower</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -5752,44 +5720,52 @@
           <t>OakNorth Bank</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr"/>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Associate, Debt Finance</t>
+        </is>
+      </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>mandy.sanaghan@oaknorth.co.uk</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr"/>
+          <t>luke.branchflower@oaknorth.co.uk</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>07582748413</t>
+        </is>
+      </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I101" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J101" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K101" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L101" s="8" t="inlineStr">
         <is>
-          <t>Copied on the Oryx 2 Real Estate REL/ON redemption</t>
+          <t>Debt finance associate on Plant Basingstoke</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Matteo Fuschillo</t>
+          <t>Magdalena Wierzchowska</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -5802,25 +5778,33 @@
           <t>OakNorth Bank</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr"/>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Director, Legal and Transaction Management</t>
+        </is>
+      </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>matteo.fuschillo@oaknorth.co.uk</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr"/>
+          <t>magdalena.wierzchowska@oaknorth.co.uk</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>+44 7841 423326</t>
+        </is>
+      </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J102" s="6" t="n">
         <v>0</v>
@@ -5832,14 +5816,14 @@
       </c>
       <c r="L102" s="8" t="inlineStr">
         <is>
-          <t>On the OakNorth deal team for the St Clements final valuation</t>
+          <t>Legals and funds flow on the Charte Forte (Monument) REL refinance</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Mayank Gupta</t>
+          <t>Mandy Sanaghan</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -5852,21 +5836,13 @@
           <t>OakNorth Bank</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>Associate Director</t>
-        </is>
-      </c>
+      <c r="D103" s="4" t="inlineStr"/>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>mayank.gupta1@oaknorth.co.uk</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+91-9818434109</t>
-        </is>
-      </c>
+          <t>mandy.sanaghan@oaknorth.co.uk</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="6" t="inlineStr">
         <is>
           <t>2026-02-25</t>
@@ -5878,26 +5854,26 @@
         </is>
       </c>
       <c r="I103" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K103" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L103" s="8" t="inlineStr">
         <is>
-          <t>OakNorth side of the Oryx 2 Real Estate REL/ON redemption</t>
+          <t>Copied on the Oryx 2 Real Estate REL/ON redemption</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Mohit Malik</t>
+          <t>Matteo Fuschillo</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -5913,18 +5889,18 @@
       <c r="D104" s="4" t="inlineStr"/>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>mohit.malik@oaknorth.co.uk</t>
+          <t>matteo.fuschillo@oaknorth.co.uk</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr"/>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="I104" s="6" t="n">
@@ -5940,14 +5916,14 @@
       </c>
       <c r="L104" s="8" t="inlineStr">
         <is>
-          <t>OakNorth contact on the Oryx 2 Real Estate redemption</t>
+          <t>On the OakNorth deal team for the St Clements final valuation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Neha Gupta</t>
+          <t>Mayank Gupta</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -5960,44 +5936,52 @@
           <t>OakNorth Bank</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr"/>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Associate Director</t>
+        </is>
+      </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>neha.gupta@oaknorth.co.uk</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr"/>
+          <t>mayank.gupta1@oaknorth.co.uk</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>+91-9818434109</t>
+        </is>
+      </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I105" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K105" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L105" s="8" t="inlineStr">
         <is>
-          <t>Copied on the TCR valuation thread</t>
+          <t>OakNorth side of the Oryx 2 Real Estate REL/ON redemption</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Nishant Tyagi</t>
+          <t>Mohit Malik</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -6013,41 +5997,41 @@
       <c r="D106" s="4" t="inlineStr"/>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>nishant.tyagi1@oaknorth.co.uk</t>
+          <t>mohit.malik@oaknorth.co.uk</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr"/>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I106" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K106" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
-          <t>Copied on the TCR valuation thread</t>
+          <t>OakNorth contact on the Oryx 2 Real Estate redemption</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>OakNorth Portfolio Management</t>
+          <t>Neha Gupta</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -6063,18 +6047,18 @@
       <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>portfoliomanagement@oaknorth.co.uk</t>
+          <t>neha.gupta@oaknorth.co.uk</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I107" s="6" t="n">
@@ -6090,14 +6074,14 @@
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
-          <t>OakNorth portfolio monitoring inbox — information requests on REL GMP and ESSL reporting</t>
+          <t>Copied on the TCR valuation thread</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Priya Harley</t>
+          <t>Nishant Tyagi</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
@@ -6110,52 +6094,44 @@
           <t>OakNorth Bank</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>Director, Debt Finance</t>
-        </is>
-      </c>
+      <c r="D108" s="4" t="inlineStr"/>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>priya.chauhan@oaknorth.co.uk</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>+447904310146, +44 7904 310146</t>
-        </is>
-      </c>
+          <t>nishant.tyagi1@oaknorth.co.uk</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr"/>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I108" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J108" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K108" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L108" s="8" t="inlineStr">
         <is>
-          <t>OakNorth debt finance lead on Stanhope Gate, 57-60 Lincoln's Inn Fields and a regional office financing</t>
+          <t>Copied on the TCR valuation thread</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Sam Van Der Burgh</t>
+          <t>OakNorth Portfolio Management</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -6171,18 +6147,18 @@
       <c r="D109" s="4" t="inlineStr"/>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>sam.vanderburgh@oaknorth.co.uk</t>
+          <t>portfoliomanagement@oaknorth.co.uk</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I109" s="6" t="n">
@@ -6198,14 +6174,14 @@
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
-          <t>OakNorth deal team on St Clements and 57-60 Lincoln's Inn Fields</t>
+          <t>OakNorth portfolio monitoring inbox — information requests on REL GMP and ESSL reporting</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Sarthak Mohari</t>
+          <t>Priya Harley</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -6218,16 +6194,24 @@
           <t>OakNorth Bank</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr"/>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Director, Debt Finance</t>
+        </is>
+      </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>sarthak.mohari@oaknorth.co.uk</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr"/>
+          <t>priya.chauhan@oaknorth.co.uk</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>+447904310146</t>
+        </is>
+      </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H110" s="6" t="inlineStr">
@@ -6236,26 +6220,26 @@
         </is>
       </c>
       <c r="I110" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J110" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K110" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L110" s="8" t="inlineStr">
         <is>
-          <t>OakNorth contact on 57-60 Lincoln's Inn Fields</t>
+          <t>OakNorth debt finance lead on Stanhope Gate, 57-60 Lincoln's Inn Fields and a regional office financing</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Shivani Mishra</t>
+          <t>Sam Van Der Burgh</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -6271,41 +6255,41 @@
       <c r="D111" s="4" t="inlineStr"/>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>shivani.mishra@oaknorth.co.uk</t>
+          <t>sam.vanderburgh@oaknorth.co.uk</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I111" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J111" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K111" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K111" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L111" s="8" t="inlineStr">
         <is>
-          <t>Organises OakNorth / REL relationship drinks and dinners</t>
+          <t>OakNorth deal team on St Clements and 57-60 Lincoln's Inn Fields</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Sumant Srivastava</t>
+          <t>Sarthak Mohari</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -6321,18 +6305,18 @@
       <c r="D112" s="4" t="inlineStr"/>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>sumant.srivastava@oaknorth.co.uk</t>
+          <t>sarthak.mohari@oaknorth.co.uk</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I112" s="6" t="n">
@@ -6346,12 +6330,16 @@
           <t>Named in a thread</t>
         </is>
       </c>
-      <c r="L112" s="8" t="inlineStr"/>
+      <c r="L112" s="8" t="inlineStr">
+        <is>
+          <t>OakNorth contact on 57-60 Lincoln's Inn Fields</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Vishal Tulsyan</t>
+          <t>Shivani Mishra</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -6367,22 +6355,22 @@
       <c r="D113" s="4" t="inlineStr"/>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>vishal.tulsyan@oaknorth.co.uk</t>
+          <t>shivani.mishra@oaknorth.co.uk</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I113" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J113" s="6" t="n">
         <v>0</v>
@@ -6394,91 +6382,99 @@
       </c>
       <c r="L113" s="8" t="inlineStr">
         <is>
-          <t>OakNorth contact on Charte Forte (Monument) Limited</t>
+          <t>Organises OakNorth / REL relationship drinks and dinners</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>Chantelle Parish</t>
-        </is>
-      </c>
-      <c r="B114" s="10" t="inlineStr">
-        <is>
-          <t>Borrower / Sponsor</t>
+          <t>Shubham Kalra</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>Lender / Bank</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Audley Group</t>
-        </is>
-      </c>
-      <c r="D114" s="4" t="inlineStr"/>
+          <t>OakNorth Bank</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Deputy Vice President</t>
+        </is>
+      </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>chantelle.parish@audleygroup.com</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr"/>
+          <t>shubham.kalra@oaknorth.co.uk</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>+91-7206717001</t>
+        </is>
+      </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I114" s="6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J114" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K114" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L114" s="8" t="inlineStr">
         <is>
-          <t>Audley side contact on the Stanmore MI reporting template</t>
+          <t>REL GMP information requests and the Oryx 2 Real Estate redemption</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>Omer Weinberger</t>
-        </is>
-      </c>
-      <c r="B115" s="10" t="inlineStr">
-        <is>
-          <t>Borrower / Sponsor</t>
+          <t>Sumant Srivastava</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>Lender / Bank</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Avanton</t>
+          <t>OakNorth Bank</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr"/>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>omer@avanton.co.uk</t>
+          <t>sumant.srivastava@oaknorth.co.uk</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I115" s="6" t="n">
@@ -6492,43 +6488,39 @@
           <t>Named in a thread</t>
         </is>
       </c>
-      <c r="L115" s="8" t="inlineStr">
-        <is>
-          <t>Sponsor side on Steel Works, Culvert Court, Battersea</t>
-        </is>
-      </c>
+      <c r="L115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>Reis Usmani</t>
-        </is>
-      </c>
-      <c r="B116" s="10" t="inlineStr">
-        <is>
-          <t>Borrower / Sponsor</t>
+          <t>Vishal Tulsyan</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>Lender / Bank</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Avanton</t>
+          <t>OakNorth Bank</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr"/>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>reis@avanton.co.uk</t>
+          <t>vishal.tulsyan@oaknorth.co.uk</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I116" s="6" t="n">
@@ -6544,64 +6536,72 @@
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
-          <t>Sponsor side on Steel Works, Culvert Court, Battersea</t>
+          <t>OakNorth contact on Charte Forte (Monument) Limited</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>Romain Palpacuer</t>
-        </is>
-      </c>
-      <c r="B117" s="10" t="inlineStr">
-        <is>
-          <t>Borrower / Sponsor</t>
+          <t>Vivek Jaiswal</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>Lender / Bank</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Avanton</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr"/>
+          <t>OakNorth Bank</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Senior Associate</t>
+        </is>
+      </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>romain@avanton.co.uk</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr"/>
+          <t>vivek.jaiswal@oaknorth.co.uk</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>+91-9044471739</t>
+        </is>
+      </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I117" s="6" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+        <v>2</v>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L117" s="8" t="inlineStr">
         <is>
-          <t>Sponsor side on Steel Works, Culvert Court, Battersea</t>
+          <t>Portfolio monitoring on ESSL - M&amp;S reports, reservations, bank statements</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>Mahir Vachani</t>
+          <t>Chantelle Parish</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -6611,55 +6611,47 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>BPS London</t>
-        </is>
-      </c>
-      <c r="D118" s="4" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
+          <t>Audley Group</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr"/>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>mahir@bps.london</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>0207 831 1191, 07788 895 205</t>
-        </is>
-      </c>
+          <t>chantelle.parish@audleygroup.com</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I118" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J118" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K118" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K118" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L118" s="8" t="inlineStr">
         <is>
-          <t>Sponsor side (with Purestone Capital) on 80-85 Tottenham Court Road mezzanine</t>
+          <t>Audley side contact on the Stanmore MI reporting template</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>Rohan Jhaveri</t>
+          <t>Omer Weinberger</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -6669,55 +6661,47 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>BPS London</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>Investment Director</t>
-        </is>
-      </c>
+          <t>Avanton</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr"/>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>rohan@bps.london</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>0207 831 1191, 07388 816 368</t>
-        </is>
-      </c>
+          <t>omer@avanton.co.uk</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="I119" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K119" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K119" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L119" s="8" t="inlineStr">
         <is>
-          <t>Sponsor side on 80-85 Tottenham Court Road bridge/mezz terms</t>
+          <t>Sponsor side on Steel Works, Culvert Court, Battersea</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>Alex Randall</t>
+          <t>Reis Usmani</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -6727,47 +6711,47 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Brotherton Real Estate</t>
+          <t>Avanton</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr"/>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>a.randall@brothertonre.com</t>
+          <t>reis@avanton.co.uk</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="I120" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K120" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L120" s="8" t="inlineStr">
         <is>
-          <t>Brotherton side on the University Arms, Cambridge refinance</t>
+          <t>Sponsor side on Steel Works, Culvert Court, Battersea</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>Banner Sanders</t>
+          <t>Romain Palpacuer</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -6777,24 +6761,24 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Brotherton Real Estate</t>
+          <t>Avanton</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr"/>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>b.sanders@brothertonre.com</t>
+          <t>romain@avanton.co.uk</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="I121" s="6" t="n">
@@ -6810,14 +6794,14 @@
       </c>
       <c r="L121" s="8" t="inlineStr">
         <is>
-          <t>Brotherton side on the Princess Yachts industrial portfolio mezzanine</t>
+          <t>Sponsor side on Steel Works, Culvert Court, Battersea</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>Dan Uzan</t>
+          <t>Mahir Vachani</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -6827,47 +6811,55 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Brotherton Real Estate</t>
-        </is>
-      </c>
-      <c r="D122" s="4" t="inlineStr"/>
+          <t>BPS London</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>d.uzan@brothertonre.com</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr"/>
+          <t>mahir@bps.london</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>0207 831 1191, 07788 895 205</t>
+        </is>
+      </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I122" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J122" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K122" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L122" s="8" t="inlineStr">
         <is>
-          <t>Across University Arms Cambridge, Princess Yachts mezzanine and the Ellesmere JLR bridge</t>
+          <t>Sponsor side (with Purestone Capital) on 80-85 Tottenham Court Road mezzanine</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>Eduard Mantz</t>
+          <t>Rohan Jhaveri</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -6877,47 +6869,55 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Brotherton Real Estate</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr"/>
+          <t>BPS London</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Investment Director</t>
+        </is>
+      </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>e.mantz@brothertonre.com</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr"/>
+          <t>rohan@bps.london</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>0207 831 1191, 07388 816 368</t>
+        </is>
+      </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I123" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J123" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K123" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L123" s="8" t="inlineStr">
         <is>
-          <t>Brotherton side on the Princess Yachts industrial portfolio mezzanine</t>
+          <t>Sponsor side on 80-85 Tottenham Court Road bridge/mezz terms</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>G Tsitsis</t>
+          <t>Alex Randall</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -6933,18 +6933,18 @@
       <c r="D124" s="4" t="inlineStr"/>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>g.tsitsis@brothertonre.com</t>
+          <t>a.randall@brothertonre.com</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I124" s="6" t="n">
@@ -6960,14 +6960,14 @@
       </c>
       <c r="L124" s="8" t="inlineStr">
         <is>
-          <t>On the Princess Yachts mezzanine and Ellesmere JLR bridge threads</t>
+          <t>Brotherton side on the University Arms, Cambridge refinance</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>M Wild</t>
+          <t>Banner Sanders</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -6983,18 +6983,18 @@
       <c r="D125" s="4" t="inlineStr"/>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>m.wild@brothertonre.com</t>
+          <t>b.sanders@brothertonre.com</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="I125" s="6" t="n">
@@ -7010,14 +7010,14 @@
       </c>
       <c r="L125" s="8" t="inlineStr">
         <is>
-          <t>On the Ellesmere JLR bridge thread</t>
+          <t>Brotherton side on the Princess Yachts industrial portfolio mezzanine</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>N Anderson</t>
+          <t>Dan Uzan</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
@@ -7033,18 +7033,18 @@
       <c r="D126" s="4" t="inlineStr"/>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>n.anderson@brothertonre.com</t>
+          <t>d.uzan@brothertonre.com</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H126" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="I126" s="6" t="n">
@@ -7060,14 +7060,14 @@
       </c>
       <c r="L126" s="8" t="inlineStr">
         <is>
-          <t>On the Princess Yachts industrial portfolio mezzanine thread</t>
+          <t>Across University Arms Cambridge, Princess Yachts mezzanine and the Ellesmere JLR bridge</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>P Kennedy</t>
+          <t>Eduard Mantz</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -7083,7 +7083,7 @@
       <c r="D127" s="4" t="inlineStr"/>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>p.kennedy@brothertonre.com</t>
+          <t>e.mantz@brothertonre.com</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr"/>
@@ -7110,14 +7110,14 @@
       </c>
       <c r="L127" s="8" t="inlineStr">
         <is>
-          <t>On the Princess Yachts industrial portfolio mezzanine thread</t>
+          <t>Brotherton side on the Princess Yachts industrial portfolio mezzanine</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>Richard Fine</t>
+          <t>G Tsitsis</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -7133,13 +7133,13 @@
       <c r="D128" s="4" t="inlineStr"/>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>r.fine@brothertonre.com</t>
+          <t>g.tsitsis@brothertonre.com</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
@@ -7160,14 +7160,14 @@
       </c>
       <c r="L128" s="8" t="inlineStr">
         <is>
-          <t>On the University Arms Cambridge refinance and Ellesmere JLR bridge</t>
+          <t>On the Princess Yachts mezzanine and Ellesmere JLR bridge threads</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>Robert Kleinman</t>
+          <t>M Wild</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -7183,18 +7183,18 @@
       <c r="D129" s="4" t="inlineStr"/>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>r.kleinman@brothertonre.com</t>
+          <t>m.wild@brothertonre.com</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="I129" s="6" t="n">
@@ -7210,14 +7210,14 @@
       </c>
       <c r="L129" s="8" t="inlineStr">
         <is>
-          <t>On the University Arms, Cambridge refinance</t>
+          <t>On the Ellesmere JLR bridge thread</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>N Anderson</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -7227,24 +7227,24 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Cresswick</t>
+          <t>Brotherton Real Estate</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr"/>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>matt@cresswick.co.uk</t>
+          <t>n.anderson@brothertonre.com</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="I130" s="6" t="n">
@@ -7260,14 +7260,14 @@
       </c>
       <c r="L130" s="8" t="inlineStr">
         <is>
-          <t>Cresswick sponsor side on the Dulwich acquisition being funded by REL and OakNorth via GLPG.</t>
+          <t>On the Princess Yachts industrial portfolio mezzanine thread</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>Nick</t>
+          <t>P Kennedy</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -7277,24 +7277,24 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Cresswick</t>
+          <t>Brotherton Real Estate</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr"/>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>nick@cresswick.co.uk</t>
+          <t>p.kennedy@brothertonre.com</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="I131" s="6" t="n">
@@ -7310,14 +7310,14 @@
       </c>
       <c r="L131" s="8" t="inlineStr">
         <is>
-          <t>Cresswick principal on the Dulwich deal - fielded REL questions on the £18.5m purchase price and guarantors.</t>
+          <t>On the Princess Yachts industrial portfolio mezzanine thread</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>Amar Randhawa</t>
+          <t>Richard Fine</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -7327,47 +7327,47 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>DNA Capital Partners</t>
+          <t>Brotherton Real Estate</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr"/>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>a.randhawa@dna-cp.com</t>
+          <t>r.fine@brothertonre.com</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="I132" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J132" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K132" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K132" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L132" s="8" t="inlineStr">
         <is>
-          <t>Sponsor contact on the DNA Uxbridge (Belmont Place) loan - extension, equity and redemption negotiations.</t>
+          <t>On the University Arms Cambridge refinance and Ellesmere JLR bridge</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>David Scheurl</t>
+          <t>Robert Kleinman</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -7377,24 +7377,24 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>DNA Capital Partners</t>
+          <t>Brotherton Real Estate</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr"/>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>d.scheurl@dna-cp.com</t>
+          <t>r.kleinman@brothertonre.com</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I133" s="6" t="n">
@@ -7410,14 +7410,14 @@
       </c>
       <c r="L133" s="8" t="inlineStr">
         <is>
-          <t>DNA Capital Partners side of the Uxbridge loan monthly reporting and 31/07/26 maturity.</t>
+          <t>On the University Arms, Cambridge refinance</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>Alexander Larkins</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -7427,55 +7427,47 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Elysian Residences</t>
-        </is>
-      </c>
-      <c r="D134" s="4" t="inlineStr">
-        <is>
-          <t>Financial Accountant</t>
-        </is>
-      </c>
+          <t>Cresswick</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr"/>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>a.larkins@elysianresidences.com</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>07771 144264</t>
-        </is>
-      </c>
+          <t>matt@cresswick.co.uk</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="I134" s="6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J134" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K134" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+        <v>0</v>
+      </c>
+      <c r="K134" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
-          <t>Main borrower-side reporting contact on the ESSL / Stanmore and The Landsby loans.</t>
+          <t>Cresswick sponsor side on the Dulwich acquisition being funded by REL and OakNorth via GLPG.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>Ciara Eggenton</t>
+          <t>Nick</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -7485,28 +7477,24 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Elysian Residences</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>Conveyancing and Progressions Manager</t>
-        </is>
-      </c>
+          <t>Cresswick</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr"/>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>c.eggenton@elysianresidences.com</t>
+          <t>nick@cresswick.co.uk</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I135" s="6" t="n">
@@ -7522,14 +7510,14 @@
       </c>
       <c r="L135" s="8" t="inlineStr">
         <is>
-          <t>Handles ESSL reservations, completions and sales progression reporting to REL.</t>
+          <t>Cresswick principal on the Dulwich deal - fielded REL questions on the £18.5m purchase price and guarantors.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>Ciara Eggenton</t>
+          <t>Amar Randhawa</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -7539,36 +7527,28 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Elysian Residences</t>
-        </is>
-      </c>
-      <c r="D136" s="4" t="inlineStr">
-        <is>
-          <t>Conveyancing and Progressions Manager</t>
-        </is>
-      </c>
+          <t>DNA Capital Partners</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr"/>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>c.osullivan@elysianresidences.com</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>020 8158 6454</t>
-        </is>
-      </c>
+          <t>a.randhawa@dna-cp.com</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I136" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J136" s="6" t="n">
         <v>0</v>
@@ -7580,14 +7560,14 @@
       </c>
       <c r="L136" s="8" t="inlineStr">
         <is>
-          <t>Former address for Ciara Eggenton, now c.eggenton@elysianresidences.com.</t>
+          <t>Sponsor contact on the DNA Uxbridge (Belmont Place) loan - extension, equity and redemption negotiations.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>Gavin Stein</t>
+          <t>David Scheurl</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
@@ -7597,51 +7577,47 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Elysian Residences</t>
+          <t>DNA Capital Partners</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr"/>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>g.stein@elysianresidences.com</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>+44 (0) 78 2460 4438</t>
-        </is>
-      </c>
+          <t>d.scheurl@dna-cp.com</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I137" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J137" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K137" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K137" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L137" s="8" t="inlineStr">
         <is>
-          <t>Senior Elysian contact on The Landsby / Stanmore LTV covenant breach discussions.</t>
+          <t>DNA Capital Partners side of the Uxbridge loan monthly reporting and 31/07/26 maturity.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>Giles Stevens</t>
+          <t>Alexander Larkins</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -7656,18 +7632,22 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Director of Transactions</t>
+          <t>Financial Accountant</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>g.stevens@elysianresidences.com</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr"/>
+          <t>a.larkins@elysianresidences.com</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>07771 144264</t>
+        </is>
+      </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -7676,10 +7656,10 @@
         </is>
       </c>
       <c r="I138" s="6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J138" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
@@ -7688,14 +7668,14 @@
       </c>
       <c r="L138" s="8" t="inlineStr">
         <is>
-          <t>Elysian transactions lead on The Landsby / Stanmore OakNorth-REL facility.</t>
+          <t>Main borrower-side reporting contact on the ESSL / Stanmore and The Landsby loans.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>Paul Harries</t>
+          <t>Ciara Eggenton</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -7710,50 +7690,46 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Interim Finance Consultant</t>
+          <t>Conveyancing and Progressions Manager</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>p.harries@elysianresidences.com</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>07764 510962</t>
-        </is>
-      </c>
+          <t>c.eggenton@elysianresidences.com</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="I139" s="6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J139" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K139" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K139" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L139" s="8" t="inlineStr">
         <is>
-          <t>Leads Elysian's HSTAM1 loan-note tap to cure the Stanmore / Landsby LTV covenant breach.</t>
+          <t>Handles ESSL reservations, completions and sales progression reporting to REL.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>S. Spencer</t>
+          <t>Ciara Eggenton</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -7766,44 +7742,52 @@
           <t>Elysian Residences</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr"/>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>Conveyancing and Progressions Manager</t>
+        </is>
+      </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>s.spencer@elysianresidences.com</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr"/>
+          <t>c.osullivan@elysianresidences.com</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>020 8158 6454</t>
+        </is>
+      </c>
       <c r="G140" s="6" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="I140" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K140" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L140" s="8" t="inlineStr">
         <is>
-          <t>Elysian attendee on the Stanmore MI template discussions.</t>
+          <t>Former address for Ciara Eggenton, now c.eggenton@elysianresidences.com.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>Scott Thornton</t>
+          <t>Gavin Stein</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -7819,25 +7803,29 @@
       <c r="D141" s="4" t="inlineStr"/>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>s.thornton@elysianresidences.com</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr"/>
+          <t>g.stein@elysianresidences.com</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0) 78 2460 4438</t>
+        </is>
+      </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I141" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J141" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
@@ -7846,14 +7834,14 @@
       </c>
       <c r="L141" s="8" t="inlineStr">
         <is>
-          <t>Elysian contact on the enhanced MI template and Stanmore monitoring.</t>
+          <t>Senior Elysian contact on The Landsby / Stanmore LTV covenant breach discussions.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>Pete Williams</t>
+          <t>Giles Stevens</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
@@ -7863,47 +7851,51 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Empire Global</t>
-        </is>
-      </c>
-      <c r="D142" s="4" t="inlineStr"/>
+          <t>Elysian Residences</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>Director of Transactions</t>
+        </is>
+      </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>pete@empireglobal.co.uk</t>
+          <t>g.stevens@elysianresidences.com</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H142" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I142" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J142" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K142" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L142" s="8" t="inlineStr">
         <is>
-          <t>Supplied the Colonnade Hotel trading projections for a hotel financing.</t>
+          <t>Elysian transactions lead on The Landsby / Stanmore OakNorth-REL facility.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>Yash Hindocha</t>
+          <t>Paul Harries</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
@@ -7913,36 +7905,36 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Hindocha &amp; Co</t>
+          <t>Elysian Residences</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Chartered Accountant / principal contact for Anahi Properties Ltd</t>
+          <t>Interim Finance Consultant</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>yash@hindocha.co.uk</t>
+          <t>p.harries@elysianresidences.com</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>020 8952 9591</t>
+          <t>07764 510962</t>
         </is>
       </c>
       <c r="G143" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H143" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I143" s="6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J143" s="6" t="n">
         <v>0</v>
@@ -7954,14 +7946,14 @@
       </c>
       <c r="L143" s="8" t="inlineStr">
         <is>
-          <t>Sponsor behind Anahi Properties / Ashray Holdings; took REL terms on Houndswood House (£950k gross) before funding it via family and friends. Runs Hindocha &amp; Co, chartered accountants in Edgware</t>
+          <t>Leads Elysian's HSTAM1 loan-note tap to cure the Stanmore / Landsby LTV covenant breach.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>Davina Desai</t>
+          <t>S. Spencer</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
@@ -7971,24 +7963,24 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>IPCA Group</t>
+          <t>Elysian Residences</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr"/>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>davina.desai@ipcagroup.com</t>
+          <t>s.spencer@elysianresidences.com</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I144" s="6" t="n">
@@ -8004,14 +7996,14 @@
       </c>
       <c r="L144" s="8" t="inlineStr">
         <is>
-          <t>IPCA Group contact alongside Jignesh Desai</t>
+          <t>Elysian attendee on the Stanmore MI template discussions.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>Jignesh Desai</t>
+          <t>Scott Thornton</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
@@ -8021,39 +8013,31 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>IPCA Group</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
+          <t>Elysian Residences</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr"/>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>jignesh@ipcagroup.com</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>+44 7887 712 463</t>
-        </is>
-      </c>
+          <t>s.thornton@elysianresidences.com</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I145" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J145" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
@@ -8062,14 +8046,14 @@
       </c>
       <c r="L145" s="8" t="inlineStr">
         <is>
-          <t>Active finance discussion with REL including the Moove transaction</t>
+          <t>Elysian contact on the enhanced MI template and Stanmore monitoring.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>Preena Desai</t>
+          <t>Pete Williams</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
@@ -8079,24 +8063,24 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>IPCA Group</t>
+          <t>Empire Global</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr"/>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>preena.desai@ipcagroup.com</t>
+          <t>pete@empireglobal.co.uk</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H146" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I146" s="6" t="n">
@@ -8112,14 +8096,14 @@
       </c>
       <c r="L146" s="8" t="inlineStr">
         <is>
-          <t>IPCA Group contact alongside Jignesh Desai</t>
+          <t>Supplied the Colonnade Hotel trading projections for a hotel financing.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>Ajay Laxman</t>
+          <t>Yash Hindocha</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
@@ -8129,43 +8113,55 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>JMK Group</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr"/>
+          <t>Hindocha &amp; Co</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Chartered Accountant / principal contact for Anahi Properties Ltd</t>
+        </is>
+      </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>ajaylaxman@jmk-group.co.uk</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr"/>
+          <t>yash@hindocha.co.uk</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>020 8952 9591</t>
+        </is>
+      </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H147" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I147" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J147" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K147" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
-        </is>
-      </c>
-      <c r="L147" s="8" t="inlineStr"/>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L147" s="8" t="inlineStr">
+        <is>
+          <t>Sponsor behind Anahi Properties / Ashray Holdings; took REL terms on Houndswood House (£950k gross) before funding it via family and friends. Runs Hindocha &amp; Co, chartered accountants in Edgware</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>Harry Chapman</t>
+          <t>Davina Desai</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
@@ -8175,24 +8171,24 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Latium Group</t>
+          <t>IPCA Group</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr"/>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>harry.chapman@latium.co.uk</t>
+          <t>davina.desai@ipcagroup.com</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H148" s="6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I148" s="6" t="n">
@@ -8208,14 +8204,14 @@
       </c>
       <c r="L148" s="8" t="inlineStr">
         <is>
-          <t>Latium's contact on the 22-24 Southwark Bridge Road bridge facility</t>
+          <t>IPCA Group contact alongside Jignesh Desai</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>Reis</t>
+          <t>Jignesh Desai</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
@@ -8225,43 +8221,55 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Lock Terrace</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr"/>
+          <t>IPCA Group</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>reis@lockterrace.com</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr"/>
+          <t>jignesh@ipcagroup.com</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>+44 7887 712 463</t>
+        </is>
+      </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I149" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J149" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K149" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
-        </is>
-      </c>
-      <c r="L149" s="8" t="inlineStr"/>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L149" s="8" t="inlineStr">
+        <is>
+          <t>Active finance discussion with REL including the Moove transaction</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>Salman</t>
+          <t>Preena Desai</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
@@ -8271,24 +8279,24 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Lock Terrace</t>
+          <t>IPCA Group</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr"/>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>salman@lockterrace.com</t>
+          <t>preena.desai@ipcagroup.com</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H150" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I150" s="6" t="n">
@@ -8302,12 +8310,16 @@
           <t>Named in a thread</t>
         </is>
       </c>
-      <c r="L150" s="8" t="inlineStr"/>
+      <c r="L150" s="8" t="inlineStr">
+        <is>
+          <t>IPCA Group contact alongside Jignesh Desai</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>Tariq</t>
+          <t>Ajay Laxman</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
@@ -8317,24 +8329,24 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Lock Terrace</t>
+          <t>JMK Group</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr"/>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>tariq@lockterrace.com</t>
+          <t>ajaylaxman@jmk-group.co.uk</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I151" s="6" t="n">
@@ -8353,7 +8365,7 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>Daniela Guberova</t>
+          <t>Harry Chapman</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
@@ -8363,55 +8375,47 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>London Land Group</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr">
-        <is>
-          <t>Group Financial Controller</t>
-        </is>
-      </c>
+          <t>Latium Group</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr"/>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>dguberova@londonland.group</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>+44 7814 681502</t>
-        </is>
-      </c>
+          <t>harry.chapman@latium.co.uk</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H152" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I152" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J152" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K152" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K152" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L152" s="8" t="inlineStr">
         <is>
-          <t>Provides KYC and financial information for London Land's Bromley facility</t>
+          <t>Latium's contact on the 22-24 Southwark Bridge Road bridge facility</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Mario Luca Balducci</t>
+          <t>Reis</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
@@ -8421,51 +8425,43 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>London Land Group</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer</t>
-        </is>
-      </c>
+          <t>Lock Terrace</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr"/>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>mbalducci@londonland.group</t>
+          <t>reis@lockterrace.com</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H153" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="I153" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K153" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
-        </is>
-      </c>
-      <c r="L153" s="8" t="inlineStr">
-        <is>
-          <t>Sponsor principal on the REL / London Land Bromley deal</t>
-        </is>
-      </c>
+      <c r="K153" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
+        </is>
+      </c>
+      <c r="L153" s="8" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Nugen Group</t>
+          <t>Salman</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
@@ -8475,24 +8471,24 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Nugen Group</t>
+          <t>Lock Terrace</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr"/>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>info@nugen-group.co.uk</t>
+          <t>salman@lockterrace.com</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H154" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="I154" s="6" t="n">
@@ -8506,16 +8502,12 @@
           <t>Named in a thread</t>
         </is>
       </c>
-      <c r="L154" s="8" t="inlineStr">
-        <is>
-          <t>Developer enquiry on Hickstead &amp; Grovefield hotels</t>
-        </is>
-      </c>
+      <c r="L154" s="8" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>Rishi Passi</t>
+          <t>Tariq</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
@@ -8525,47 +8517,43 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Oblix Living</t>
+          <t>Lock Terrace</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr"/>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>rishi@oblixliving.com</t>
+          <t>tariq@lockterrace.com</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H155" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="I155" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J155" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K155" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
-        </is>
-      </c>
-      <c r="L155" s="8" t="inlineStr">
-        <is>
-          <t>Bidding on a Manchester office and discussing acquisition finance with REL</t>
-        </is>
-      </c>
+      <c r="K155" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
+        </is>
+      </c>
+      <c r="L155" s="8" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>Rishi Khurana</t>
+          <t>Daniela Guberova</t>
         </is>
       </c>
       <c r="B156" s="10" t="inlineStr">
@@ -8575,36 +8563,36 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Purestone Capital</t>
+          <t>London Land Group</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Group Financial Controller</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>rishi@purestone.uk</t>
+          <t>dguberova@londonland.group</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>+44 7946 258 420</t>
+          <t>+44 7814 681502</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H156" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="I156" s="6" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="J156" s="6" t="n">
         <v>0</v>
@@ -8616,14 +8604,14 @@
       </c>
       <c r="L156" s="8" t="inlineStr">
         <is>
-          <t>Very active sponsor contact on the 80-85 Tottenham Court Road bridge and the mezzanine finance book</t>
+          <t>Provides KYC and financial information for London Land's Bromley facility</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>Anand Morjaria</t>
+          <t>Mario Luca Balducci</t>
         </is>
       </c>
       <c r="B157" s="10" t="inlineStr">
@@ -8633,47 +8621,51 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Raam Healthcare</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr"/>
+          <t>London Land Group</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>anand@raamhealthcare.com</t>
+          <t>mbalducci@londonland.group</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H157" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="I157" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J157" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K157" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L157" s="8" t="inlineStr">
         <is>
-          <t>On the Raam Healthcare bridging loan enquiry</t>
+          <t>Sponsor principal on the REL / London Land Bromley deal</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>Anshul Morjaria</t>
+          <t>Nugen Group</t>
         </is>
       </c>
       <c r="B158" s="10" t="inlineStr">
@@ -8683,24 +8675,24 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Raam Healthcare</t>
+          <t>Nugen Group</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr"/>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>anshul@raamhealthcare.com</t>
+          <t>info@nugen-group.co.uk</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I158" s="6" t="n">
@@ -8716,14 +8708,14 @@
       </c>
       <c r="L158" s="8" t="inlineStr">
         <is>
-          <t>On the Raam Healthcare bridging loan enquiry</t>
+          <t>Developer enquiry on Hickstead &amp; Grovefield hotels</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>Rohit Morjaria</t>
+          <t>Rishi Passi</t>
         </is>
       </c>
       <c r="B159" s="10" t="inlineStr">
@@ -8733,24 +8725,24 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Raam Healthcare</t>
+          <t>Oblix Living</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr"/>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>rohit@raamhealthcare.com</t>
+          <t>rishi@oblixliving.com</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr"/>
       <c r="G159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I159" s="6" t="n">
@@ -8766,14 +8758,14 @@
       </c>
       <c r="L159" s="8" t="inlineStr">
         <is>
-          <t>Bridging loan enquiry for Raam Healthcare</t>
+          <t>Bidding on a Manchester office and discussing acquisition finance with REL</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>Adnan Adil</t>
+          <t>Rishi Khurana</t>
         </is>
       </c>
       <c r="B160" s="10" t="inlineStr">
@@ -8783,47 +8775,55 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Rasmala</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="inlineStr"/>
+          <t>Purestone Capital</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>adnan.adil@rasmala.com</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr"/>
+          <t>rishi@purestone.uk</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>+44 7946 258 420</t>
+        </is>
+      </c>
       <c r="G160" s="6" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H160" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I160" s="6" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J160" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K160" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L160" s="8" t="inlineStr">
         <is>
-          <t>Rasmala colleague on the Oryx 2 / Doxford refinancing and EE Doxford reports</t>
+          <t>Very active sponsor contact on the 80-85 Tottenham Court Road bridge and the mezzanine finance book</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>Henry Sarkisov</t>
+          <t>Anand Morjaria</t>
         </is>
       </c>
       <c r="B161" s="10" t="inlineStr">
@@ -8833,47 +8833,47 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Rasmala</t>
+          <t>Raam Healthcare</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr"/>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>henry.sarkisov@rasmala.com</t>
+          <t>anand@raamhealthcare.com</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr"/>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H161" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I161" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J161" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K161" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K161" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L161" s="8" t="inlineStr">
         <is>
-          <t>Borrower-side lead on Oryx 2 Real Estate / Doxford, refinancing out of REL via Ortus Secured Finance</t>
+          <t>On the Raam Healthcare bridging loan enquiry</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>Clemente Apollonj</t>
+          <t>Anshul Morjaria</t>
         </is>
       </c>
       <c r="B162" s="10" t="inlineStr">
@@ -8883,24 +8883,24 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Ros Capital</t>
+          <t>Raam Healthcare</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr"/>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>clemente@roscap.co.uk</t>
+          <t>anshul@raamhealthcare.com</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr"/>
       <c r="G162" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H162" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I162" s="6" t="n">
@@ -8916,14 +8916,14 @@
       </c>
       <c r="L162" s="8" t="inlineStr">
         <is>
-          <t>Sought a max-leverage Central London bridge, £12m purchase against £15m market value</t>
+          <t>On the Raam Healthcare bridging loan enquiry</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>Vijay Bhandari</t>
+          <t>Rohit Morjaria</t>
         </is>
       </c>
       <c r="B163" s="10" t="inlineStr">
@@ -8933,47 +8933,47 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Uno Hotels</t>
+          <t>Raam Healthcare</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr"/>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>vijay@unohotels.com</t>
+          <t>rohit@raamhealthcare.com</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr"/>
       <c r="G163" s="6" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H163" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I163" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K163" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L163" s="8" t="inlineStr">
         <is>
-          <t>Hotel sponsor; Hickstead &amp; Grovefield loan extension and Uno Thames Hotel terms</t>
+          <t>Bridging loan enquiry for Raam Healthcare</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>Manraj Padda</t>
+          <t>Adnan Adil</t>
         </is>
       </c>
       <c r="B164" s="10" t="inlineStr">
@@ -8983,55 +8983,47 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Westbrook Partners</t>
-        </is>
-      </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
+          <t>Rasmala</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr"/>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>mpadda@westbrookpartners.com</t>
-        </is>
-      </c>
-      <c r="F164" s="4" t="inlineStr">
-        <is>
-          <t>+44 (0) 20 7659 9458</t>
-        </is>
-      </c>
+          <t>adnan.adil@rasmala.com</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr"/>
       <c r="G164" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H164" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="I164" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K164" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K164" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L164" s="8" t="inlineStr">
         <is>
-          <t>Westbrook sponsor contact on 48 Albemarle Street</t>
+          <t>Rasmala colleague on the Oryx 2 / Doxford refinancing and EE Doxford reports</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Anders Pals</t>
+          <t>Henry Sarkisov</t>
         </is>
       </c>
       <c r="B165" s="10" t="inlineStr">
@@ -9041,132 +9033,132 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Willowtree Inc</t>
+          <t>Rasmala</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr"/>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>anders.pals@willowtreeinc.net</t>
+          <t>henry.sarkisov@rasmala.com</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr"/>
       <c r="G165" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="H165" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="I165" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J165" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K165" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L165" s="8" t="inlineStr">
         <is>
-          <t>Involved in Project Nest, Elephant &amp; Castle, London SE1</t>
+          <t>Borrower-side lead on Oryx 2 Real Estate / Doxford, refinancing out of REL via Ortus Secured Finance</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Alex Andrews</t>
-        </is>
-      </c>
-      <c r="B166" s="11" t="inlineStr">
-        <is>
-          <t>Investor / Family Office</t>
+          <t>Vijay Bhandari</t>
+        </is>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>Borrower / Sponsor</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Baccata Trustees Limited</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
+          <t>Uno Hotels</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr"/>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>aandrews@baccata.co.je</t>
-        </is>
-      </c>
-      <c r="F166" s="4" t="inlineStr">
-        <is>
-          <t>+44 (0) 1534 870670, +44 (0) 1534 496804</t>
-        </is>
-      </c>
+          <t>vijay@unohotels.com</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr"/>
       <c r="G166" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I166" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J166" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="K166" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+        <v>0</v>
+      </c>
+      <c r="K166" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L166" s="8" t="inlineStr">
         <is>
-          <t>Baccata trustee contact on 3A Palace Green and Minard Jersey coupon payments</t>
+          <t>Hotel sponsor; Hickstead &amp; Grovefield loan extension and Uno Thames Hotel terms</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Darren English</t>
-        </is>
-      </c>
-      <c r="B167" s="11" t="inlineStr">
-        <is>
-          <t>Investor / Family Office</t>
+          <t>Manraj Padda</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>Borrower / Sponsor</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Baccata Trustees Limited</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr"/>
+          <t>Westbrook Partners</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>denglish@baccata.co.je</t>
-        </is>
-      </c>
-      <c r="F167" s="4" t="inlineStr"/>
+          <t>mpadda@westbrookpartners.com</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0) 20 7659 9458</t>
+        </is>
+      </c>
       <c r="G167" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="I167" s="6" t="n">
@@ -9182,64 +9174,64 @@
       </c>
       <c r="L167" s="8" t="inlineStr">
         <is>
-          <t>Baccata contact on 3A Palace Green completion and Minard Jersey coupons</t>
+          <t>Westbrook sponsor contact on 48 Albemarle Street</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>R Wadsworth</t>
-        </is>
-      </c>
-      <c r="B168" s="11" t="inlineStr">
-        <is>
-          <t>Investor / Family Office</t>
+          <t>Anders Pals</t>
+        </is>
+      </c>
+      <c r="B168" s="10" t="inlineStr">
+        <is>
+          <t>Borrower / Sponsor</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Baccata Trustees Limited</t>
+          <t>Willowtree Inc</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr"/>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>rwadsworth@baccata.co.je</t>
+          <t>anders.pals@willowtreeinc.net</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr"/>
       <c r="G168" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="I168" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J168" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K168" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+        <v>0</v>
+      </c>
+      <c r="K168" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L168" s="8" t="inlineStr">
         <is>
-          <t>Copied on 3A Palace Green completion and loan note correspondence</t>
+          <t>Involved in Project Nest, Elephant &amp; Castle, London SE1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>Rebekka Brennan</t>
+          <t>Alex Andrews</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
@@ -9254,22 +9246,22 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>rbrennan@baccata.co.je</t>
+          <t>aandrews@baccata.co.je</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>+44 (0) 1534 870670</t>
+          <t>+44 (0) 1534 870670, +44 (0) 1534 496804</t>
         </is>
       </c>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H169" s="6" t="inlineStr">
@@ -9281,7 +9273,7 @@
         <v>5</v>
       </c>
       <c r="J169" s="6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
@@ -9290,14 +9282,14 @@
       </c>
       <c r="L169" s="8" t="inlineStr">
         <is>
-          <t>Administers monthly Minard Jersey coupon and 3A Palace Green loan note payments</t>
+          <t>Baccata trustee contact on 3A Palace Green and Minard Jersey coupon payments</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>Sean Kenny</t>
+          <t>Darren English</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
@@ -9310,21 +9302,13 @@
           <t>Baccata Trustees Limited</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>Client Director</t>
-        </is>
-      </c>
+      <c r="D170" s="4" t="inlineStr"/>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>skenny@baccata.co.je</t>
-        </is>
-      </c>
-      <c r="F170" s="4" t="inlineStr">
-        <is>
-          <t>+44 (0) 1534 870670</t>
-        </is>
-      </c>
+          <t>denglish@baccata.co.je</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr"/>
       <c r="G170" s="6" t="inlineStr">
         <is>
           <t>2026-01-29</t>
@@ -9332,14 +9316,14 @@
       </c>
       <c r="H170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I170" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J170" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
@@ -9348,14 +9332,14 @@
       </c>
       <c r="L170" s="8" t="inlineStr">
         <is>
-          <t>Jersey trustee lead on 3A Palace Green loan note and Minard Jersey coupons</t>
+          <t>Baccata contact on 3A Palace Green completion and Minard Jersey coupons</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>Sienna De Freitas</t>
+          <t>R Wadsworth</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
@@ -9368,36 +9352,28 @@
           <t>Baccata Trustees Limited</t>
         </is>
       </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
+      <c r="D171" s="4" t="inlineStr"/>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>sdefreitas@baccata.co.je</t>
-        </is>
-      </c>
-      <c r="F171" s="4" t="inlineStr">
-        <is>
-          <t>+44 (0) 1534 870670</t>
-        </is>
-      </c>
+          <t>rwadsworth@baccata.co.je</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr"/>
       <c r="G171" s="6" t="inlineStr">
         <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="H171" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
       <c r="I171" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J171" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
@@ -9406,14 +9382,14 @@
       </c>
       <c r="L171" s="8" t="inlineStr">
         <is>
-          <t>Handles Morka Holdings Ltd coupon payments</t>
+          <t>Copied on 3A Palace Green completion and loan note correspondence</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>Ajay Gokani</t>
+          <t>Rebekka Brennan</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
@@ -9423,35 +9399,39 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Elite Mobile</t>
-        </is>
-      </c>
-      <c r="D172" s="4" t="inlineStr"/>
+          <t>Baccata Trustees Limited</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>ajay@elitemobile.com</t>
+          <t>rbrennan@baccata.co.je</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>+44 (0) 208 799 8001, +44 (0) 20 8799 8000</t>
+          <t>+44 (0) 1534 870670</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I172" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J172" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
@@ -9460,14 +9440,14 @@
       </c>
       <c r="L172" s="8" t="inlineStr">
         <is>
-          <t>REL investor - approves facility extensions and reinvests redemptions (Oryx 2, DNA Uxbridge, St Clements House).</t>
+          <t>Administers monthly Minard Jersey coupon and 3A Palace Green loan note payments</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>Mihir Gokani</t>
+          <t>Sean Kenny</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
@@ -9477,16 +9457,24 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Elite Mobile</t>
-        </is>
-      </c>
-      <c r="D173" s="4" t="inlineStr"/>
+          <t>Baccata Trustees Limited</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>Client Director</t>
+        </is>
+      </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>mihir@elitemobile.com</t>
-        </is>
-      </c>
-      <c r="F173" s="4" t="inlineStr"/>
+          <t>skenny@baccata.co.je</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0) 1534 870670</t>
+        </is>
+      </c>
       <c r="G173" s="6" t="inlineStr">
         <is>
           <t>2026-01-29</t>
@@ -9494,14 +9482,14 @@
       </c>
       <c r="H173" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I173" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J173" s="6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
@@ -9510,14 +9498,14 @@
       </c>
       <c r="L173" s="8" t="inlineStr">
         <is>
-          <t>Elite Mobile side of the Chotilal Lakhani REL bond interest payments.</t>
+          <t>Jersey trustee lead on 3A Palace Green loan note and Minard Jersey coupons</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>Sarit Raja-Shah</t>
+          <t>Sienna De Freitas</t>
         </is>
       </c>
       <c r="B174" s="11" t="inlineStr">
@@ -9527,31 +9515,39 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>I&amp;M Bank</t>
-        </is>
-      </c>
-      <c r="D174" s="4" t="inlineStr"/>
+          <t>Baccata Trustees Limited</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>ssrajashah@imbank.co.ke</t>
-        </is>
-      </c>
-      <c r="F174" s="4" t="inlineStr"/>
+          <t>sdefreitas@baccata.co.je</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0) 1534 870670</t>
+        </is>
+      </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="I174" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J174" s="6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
@@ -9560,14 +9556,14 @@
       </c>
       <c r="L174" s="8" t="inlineStr">
         <is>
-          <t>REL shareholder; signs off on recycling shareholder funds (Oryx 2 redemption, Bromley, DNA Uxbridge) and receives REL management accounts</t>
+          <t>Handles Morka Holdings Ltd coupon payments</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>Hemlata / Jay</t>
+          <t>Ajay Gokani</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
@@ -9577,31 +9573,35 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Jarishka</t>
+          <t>Elite Mobile</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr"/>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>jaynbi27@gmail.com</t>
-        </is>
-      </c>
-      <c r="F175" s="4" t="inlineStr"/>
+          <t>ajay@elitemobile.com</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0) 208 799 8001, +44 (0) 20 8799 8000</t>
+        </is>
+      </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I175" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J175" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
@@ -9610,14 +9610,14 @@
       </c>
       <c r="L175" s="8" t="inlineStr">
         <is>
-          <t>Receives monthly 3A Palace Green loan note statements</t>
+          <t>REL investor - approves facility extensions and reinvests redemptions (Oryx 2, DNA Uxbridge, St Clements House).</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Ketan Morjaria</t>
+          <t>Mihir Gokani</t>
         </is>
       </c>
       <c r="B176" s="11" t="inlineStr">
@@ -9627,13 +9627,13 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Morka Group</t>
+          <t>Elite Mobile</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr"/>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>ketan@morkagroup.com</t>
+          <t>mihir@elitemobile.com</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr"/>
@@ -9644,14 +9644,14 @@
       </c>
       <c r="H176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="I176" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J176" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
@@ -9660,14 +9660,14 @@
       </c>
       <c r="L176" s="8" t="inlineStr">
         <is>
-          <t>Capital side - 7A Palace Green loan note, calls on St Clements House and Peninsular House</t>
+          <t>Elite Mobile side of the Chotilal Lakhani REL bond interest payments.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>Neel Rajani</t>
+          <t>Sarit Raja-Shah</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
@@ -9677,31 +9677,31 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Reel Wealth Ltd</t>
+          <t>I&amp;M Bank</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr"/>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>neel@reelholdings.co.uk</t>
+          <t>ssrajashah@imbank.co.ke</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr"/>
       <c r="G177" s="6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H177" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I177" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J177" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
@@ -9710,14 +9710,14 @@
       </c>
       <c r="L177" s="8" t="inlineStr">
         <is>
-          <t>Holds the Reel Wealth loan note in The Landsby, Stanmore; Shyam sends him the periodic update and interest payments</t>
+          <t>REL shareholder; signs off on recycling shareholder funds (Oryx 2 redemption, Bromley, DNA Uxbridge) and receives REL management accounts</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>Paul Bulstrode</t>
+          <t>Hemlata / Jay</t>
         </is>
       </c>
       <c r="B178" s="11" t="inlineStr">
@@ -9727,47 +9727,47 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>VG (Jersey)</t>
+          <t>Jarishka</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr"/>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>pbulstrode@vg.je</t>
+          <t>jaynbi27@gmail.com</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr"/>
       <c r="G178" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H178" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="I178" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J178" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K178" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+        <v>5</v>
+      </c>
+      <c r="K178" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L178" s="8" t="inlineStr">
         <is>
-          <t>Jersey administrator of the Oryx 2 Real Estate / Rasmala structure; scheduled payment notifications</t>
+          <t>Receives monthly 3A Palace Green loan note statements</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>Rasmala Administration Team</t>
+          <t>Ketan Morjaria</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
@@ -9777,47 +9777,47 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>VG (Jersey)</t>
+          <t>Morka Group</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr"/>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>rasmala@vg.je</t>
+          <t>ketan@morkagroup.com</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr"/>
       <c r="G179" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H179" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I179" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J179" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K179" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+        <v>7</v>
+      </c>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L179" s="8" t="inlineStr">
         <is>
-          <t>VG Jersey administration inbox for the Rasmala Oryx 2 Real Estate payments</t>
+          <t>Capital side - 7A Palace Green loan note, calls on St Clements House and Peninsular House</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>Stuart Andre</t>
+          <t>Neel Rajani</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
@@ -9827,47 +9827,47 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>VG (Jersey)</t>
+          <t>Reel Wealth Ltd</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr"/>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>sandre@vg.je</t>
+          <t>neel@reelholdings.co.uk</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr"/>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H180" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="I180" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J180" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K180" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+        <v>3</v>
+      </c>
+      <c r="K180" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L180" s="8" t="inlineStr">
         <is>
-          <t>VG Jersey administrator on the Oryx 2 Real Estate payment notifications</t>
+          <t>Holds the Reel Wealth loan note in The Landsby, Stanmore; Shyam sends him the periodic update and interest payments</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>Chris Kelly</t>
+          <t>Paul Bulstrode</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
@@ -9877,24 +9877,24 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Waypoint Asset Management</t>
+          <t>VG (Jersey)</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr"/>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>chris.kelly@waypointam.co.uk</t>
+          <t>pbulstrode@vg.je</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr"/>
       <c r="G181" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="H181" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="I181" s="6" t="n">
@@ -9910,14 +9910,14 @@
       </c>
       <c r="L181" s="8" t="inlineStr">
         <is>
-          <t>Quoted headers inside the forwarded 'FW: Tribeca' chain 26/01/2026 — Waypoint AM made the introduction on the Tribeca Holdings financing.</t>
+          <t>Jersey administrator of the Oryx 2 Real Estate / Rasmala structure; scheduled payment notifications</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>Jon Leefe</t>
+          <t>Rasmala Administration Team</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
@@ -9927,24 +9927,24 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Waypoint Asset Management</t>
+          <t>VG (Jersey)</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr"/>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>jon.leefe@waypointam.co.uk</t>
+          <t>rasmala@vg.je</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr"/>
       <c r="G182" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="H182" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="I182" s="6" t="n">
@@ -9960,14 +9960,14 @@
       </c>
       <c r="L182" s="8" t="inlineStr">
         <is>
-          <t>Quoted Cc header repeatedly inside the forwarded 'FW: Tribeca' chain 26/01/2026.</t>
+          <t>VG Jersey administration inbox for the Rasmala Oryx 2 Real Estate payments</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>Kirstyn Rutter</t>
+          <t>Stuart Andre</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
@@ -9977,24 +9977,24 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Waypoint Asset Management</t>
+          <t>VG (Jersey)</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr"/>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>kirstyn@waypointam.co.uk</t>
+          <t>sandre@vg.je</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr"/>
       <c r="G183" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="I183" s="6" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="L183" s="8" t="inlineStr">
         <is>
-          <t>Quoted Cc header repeatedly inside the forwarded 'FW: Tribeca' chain 26/01/2026.</t>
+          <t>VG Jersey administrator on the Oryx 2 Real Estate payment notifications</t>
         </is>
       </c>
     </row>
@@ -10996,7 +10996,7 @@
       </c>
       <c r="L202" s="8" t="inlineStr">
         <is>
-          <t>Quoted From/To headers throughout the forwarded 'FW: TG Jones, Uxbridge' chain 18/02/2026 — agent acting for the DNA Uxbridge landlord opposite John Loveday.</t>
+          <t>Levy Real Estate agent acting for the landlord on TG Jones, Uxbridge - the tenancy running through REL's DNA Uxbridge (Belmont Place) security.</t>
         </is>
       </c>
     </row>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="L209" s="8" t="inlineStr">
         <is>
-          <t>Quoted From headers and signature block throughout the forwarded 'FW: TG Jones, Uxbridge' chain 18/02/2026 — acting for the Post Office tenant against the DNA Uxbridge landlord.</t>
+          <t>Smith Price RRG surveyor acting for the Post Office tenant at TG Jones, Uxbridge, opposite the landlord on REL's DNA Uxbridge (Belmont Place) security.</t>
         </is>
       </c>
     </row>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>+44 (0)204 546 6050, +44 (0)204 5466050, +44(0)204 5466050</t>
+          <t>+44 (0)204 546 6050</t>
         </is>
       </c>
       <c r="G214" s="6" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>07881941338, 07881 941338</t>
+          <t>07881941338</t>
         </is>
       </c>
       <c r="G216" s="6" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>+44 7825216771, +44 7825 216771</t>
+          <t>+44 7825216771</t>
         </is>
       </c>
       <c r="G225" s="6" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>+44 7739555265, +44 7739 555265</t>
+          <t>+44 7739555265</t>
         </is>
       </c>
       <c r="G226" s="6" t="inlineStr">

--- a/Contact_List_REL.xlsx
+++ b/Contact_List_REL.xlsx
@@ -12,7 +12,7 @@
     <sheet name="README" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contact List'!$A$4:$L$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contact List'!$A$4:$L$239</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L238"/>
+  <dimension ref="A1:L239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -638,7 +638,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Built automatically from Outlook (shyam@relfinance.co.uk) — last refreshed 2026-07-28. Refreshed weekly; do not hand-edit (see README tab).</t>
+          <t>Built automatically from Outlook (shyam@relfinance.co.uk) — last refreshed 2026-08-03. Refreshed weekly; do not hand-edit (see README tab).</t>
         </is>
       </c>
     </row>
@@ -3630,11 +3630,11 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I61" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J61" s="6" t="n">
         <v>0</v>
@@ -3984,11 +3984,11 @@
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" s="6" t="n">
         <v>0</v>
@@ -4038,11 +4038,11 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I69" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J69" s="6" t="n">
         <v>0</v>
@@ -4678,11 +4678,11 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I81" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J81" s="6" t="n">
         <v>0</v>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I84" s="6" t="n">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I86" s="6" t="n">
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="I143" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J143" s="6" t="n">
         <v>0</v>
@@ -9266,14 +9266,14 @@
       </c>
       <c r="H169" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I169" s="6" t="n">
         <v>5</v>
       </c>
       <c r="J169" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>+44 (0) 1534 870670</t>
+          <t>+44 (0) 1534 870670, +44 (0) 1534 870600</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
@@ -9424,14 +9424,14 @@
       </c>
       <c r="H172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I172" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J172" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
@@ -9482,14 +9482,14 @@
       </c>
       <c r="H173" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I173" s="6" t="n">
         <v>12</v>
       </c>
       <c r="J173" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="H175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I175" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J175" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
@@ -9644,14 +9644,14 @@
       </c>
       <c r="H176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I176" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J176" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
@@ -9694,14 +9694,14 @@
       </c>
       <c r="H177" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I177" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J177" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
@@ -9744,14 +9744,14 @@
       </c>
       <c r="H178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I178" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J178" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
@@ -9794,14 +9794,14 @@
       </c>
       <c r="H179" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I179" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J179" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
@@ -10040,14 +10040,14 @@
       </c>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I184" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J184" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
@@ -10086,14 +10086,14 @@
       </c>
       <c r="H185" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I185" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J185" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
@@ -10132,14 +10132,14 @@
       </c>
       <c r="H186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I186" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J186" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="H193" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I193" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J193" s="6" t="n">
         <v>0</v>
@@ -10822,11 +10822,11 @@
       </c>
       <c r="H199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I199" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J199" s="6" t="n">
         <v>0</v>
@@ -10872,7 +10872,7 @@
       </c>
       <c r="H200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I200" s="6" t="n">
@@ -11716,14 +11716,14 @@
       </c>
       <c r="H216" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I216" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J216" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
@@ -12198,14 +12198,14 @@
       </c>
       <c r="H225" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I225" s="6" t="n">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="J225" s="6" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
@@ -12256,14 +12256,14 @@
       </c>
       <c r="H226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I226" s="6" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="J226" s="6" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>Abdul Rashid</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="B228" s="17" t="inlineStr">
@@ -12337,29 +12337,33 @@
           <t>Personal / Other</t>
         </is>
       </c>
-      <c r="C228" s="4" t="inlineStr"/>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>Keylife Financial Services</t>
+        </is>
+      </c>
       <c r="D228" s="4" t="inlineStr"/>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>qabdul1rash1@gmail.com</t>
+          <t>rishi@keylifefs.com</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr"/>
       <c r="G228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I228" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J228" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
@@ -12368,14 +12372,14 @@
       </c>
       <c r="L228" s="8" t="inlineStr">
         <is>
-          <t>Recipient of Shyam's personal "bag radar log" file share</t>
+          <t>New contact 30/07 — Shyam sent his work email and the REL website. No deal traffic yet, so the category is a placeholder; correct it once his role is clear.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>Anish Vora</t>
+          <t>Abdul Rashid</t>
         </is>
       </c>
       <c r="B229" s="17" t="inlineStr">
@@ -12387,37 +12391,41 @@
       <c r="D229" s="4" t="inlineStr"/>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>anishvora18@gmail.com</t>
+          <t>qabdul1rash1@gmail.com</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr"/>
       <c r="G229" s="6" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H229" s="6" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I229" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J229" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K229" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
-        </is>
-      </c>
-      <c r="L229" s="8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K229" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L229" s="8" t="inlineStr">
+        <is>
+          <t>Recipient of Shyam's personal "bag radar log" file share</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>Anish Vora</t>
         </is>
       </c>
       <c r="B230" s="17" t="inlineStr">
@@ -12429,18 +12437,18 @@
       <c r="D230" s="4" t="inlineStr"/>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>chloej0027@gmail.com</t>
+          <t>anishvora18@gmail.com</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr"/>
       <c r="G230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="I230" s="6" t="n">
@@ -12459,7 +12467,7 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>Darren Halcrow</t>
+          <t>Chloe</t>
         </is>
       </c>
       <c r="B231" s="17" t="inlineStr">
@@ -12471,41 +12479,37 @@
       <c r="D231" s="4" t="inlineStr"/>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>darren.halcrow@hotmail.co.uk</t>
+          <t>chloej0027@gmail.com</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr"/>
       <c r="G231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="I231" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J231" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K231" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
-        </is>
-      </c>
-      <c r="L231" s="8" t="inlineStr">
-        <is>
-          <t>Recipient of Shyam's personal "bag radar log" file share</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K231" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
+        </is>
+      </c>
+      <c r="L231" s="8" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>Deepesh Thakrar</t>
+          <t>Darren Halcrow</t>
         </is>
       </c>
       <c r="B232" s="17" t="inlineStr">
@@ -12517,37 +12521,41 @@
       <c r="D232" s="4" t="inlineStr"/>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>dc.thakrar@gmail.com</t>
+          <t>darren.halcrow@hotmail.co.uk</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr"/>
       <c r="G232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I232" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J232" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K232" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
-        </is>
-      </c>
-      <c r="L232" s="8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K232" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L232" s="8" t="inlineStr">
+        <is>
+          <t>Recipient of Shyam's personal "bag radar log" file share</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>Gary Brooks</t>
+          <t>Deepesh Thakrar</t>
         </is>
       </c>
       <c r="B233" s="17" t="inlineStr">
@@ -12559,41 +12567,37 @@
       <c r="D233" s="4" t="inlineStr"/>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>garyjbrooks@gmail.com</t>
+          <t>dc.thakrar@gmail.com</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr"/>
       <c r="G233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I233" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J233" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K233" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
-        </is>
-      </c>
-      <c r="L233" s="8" t="inlineStr">
-        <is>
-          <t>Recipient of Shyam's personal "bag radar log" file share</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K233" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
+        </is>
+      </c>
+      <c r="L233" s="8" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>J Crypto</t>
+          <t>Gary Brooks</t>
         </is>
       </c>
       <c r="B234" s="17" t="inlineStr">
@@ -12605,37 +12609,41 @@
       <c r="D234" s="4" t="inlineStr"/>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>jcrypto401@gmail.com</t>
+          <t>garyjbrooks@gmail.com</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr"/>
       <c r="G234" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H234" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I234" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J234" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K234" s="4" t="inlineStr">
         <is>
           <t>Direct correspondence</t>
         </is>
       </c>
-      <c r="L234" s="8" t="inlineStr"/>
+      <c r="L234" s="8" t="inlineStr">
+        <is>
+          <t>Recipient of Shyam's personal "bag radar log" file share</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>Joel Smart</t>
+          <t>J Crypto</t>
         </is>
       </c>
       <c r="B235" s="17" t="inlineStr">
@@ -12647,41 +12655,37 @@
       <c r="D235" s="4" t="inlineStr"/>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>joelsmart2023@gmail.com</t>
+          <t>jcrypto401@gmail.com</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr"/>
       <c r="G235" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H235" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I235" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J235" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K235" s="4" t="inlineStr">
         <is>
           <t>Direct correspondence</t>
         </is>
       </c>
-      <c r="L235" s="8" t="inlineStr">
-        <is>
-          <t>Recipient of Shyam's personal "bag radar log" file share</t>
-        </is>
-      </c>
+      <c r="L235" s="8" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>Malus Entity</t>
+          <t>Joel Smart</t>
         </is>
       </c>
       <c r="B236" s="17" t="inlineStr">
@@ -12693,7 +12697,7 @@
       <c r="D236" s="4" t="inlineStr"/>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>malus.entity@gmail.com</t>
+          <t>joelsmart2023@gmail.com</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr"/>
@@ -12727,7 +12731,7 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>Shyam Lakhani</t>
+          <t>Malus Entity</t>
         </is>
       </c>
       <c r="B237" s="17" t="inlineStr">
@@ -12739,25 +12743,25 @@
       <c r="D237" s="4" t="inlineStr"/>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>slakhani0203@gmail.com</t>
+          <t>malus.entity@gmail.com</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr"/>
       <c r="G237" s="6" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I237" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J237" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K237" s="4" t="inlineStr">
         <is>
@@ -12766,7 +12770,7 @@
       </c>
       <c r="L237" s="8" t="inlineStr">
         <is>
-          <t>Mailbox owner's personal Gmail; REL Finance employment offer correspondence.</t>
+          <t>Recipient of Shyam's personal "bag radar log" file share</t>
         </is>
       </c>
     </row>
@@ -12785,25 +12789,25 @@
       <c r="D238" s="4" t="inlineStr"/>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>shyam_302@hotmail.co.uk</t>
+          <t>slakhani0203@gmail.com</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr"/>
       <c r="G238" s="6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I238" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J238" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K238" s="4" t="inlineStr">
         <is>
@@ -12812,12 +12816,58 @@
       </c>
       <c r="L238" s="8" t="inlineStr">
         <is>
+          <t>Mailbox owner's personal Gmail; REL Finance employment offer correspondence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>Shyam Lakhani</t>
+        </is>
+      </c>
+      <c r="B239" s="17" t="inlineStr">
+        <is>
+          <t>Personal / Other</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr"/>
+      <c r="D239" s="4" t="inlineStr"/>
+      <c r="E239" s="4" t="inlineStr">
+        <is>
+          <t>shyam_302@hotmail.co.uk</t>
+        </is>
+      </c>
+      <c r="F239" s="4" t="inlineStr"/>
+      <c r="G239" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="H239" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I239" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J239" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L239" s="8" t="inlineStr">
+        <is>
           <t>Mailbox owner's own personal Hotmail address</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L238"/>
+  <autoFilter ref="A4:L239"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
@@ -12865,7 +12915,7 @@
         </is>
       </c>
       <c r="B4" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$238,A4)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$239,A4)</f>
         <v/>
       </c>
     </row>
@@ -12876,7 +12926,7 @@
         </is>
       </c>
       <c r="B5" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$238,A5)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$239,A5)</f>
         <v/>
       </c>
     </row>
@@ -12887,7 +12937,7 @@
         </is>
       </c>
       <c r="B6" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$238,A6)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$239,A6)</f>
         <v/>
       </c>
     </row>
@@ -12898,7 +12948,7 @@
         </is>
       </c>
       <c r="B7" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$238,A7)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$239,A7)</f>
         <v/>
       </c>
     </row>
@@ -12909,7 +12959,7 @@
         </is>
       </c>
       <c r="B8" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$238,A8)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$239,A8)</f>
         <v/>
       </c>
     </row>
@@ -12920,7 +12970,7 @@
         </is>
       </c>
       <c r="B9" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$238,A9)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$239,A9)</f>
         <v/>
       </c>
     </row>
@@ -12931,7 +12981,7 @@
         </is>
       </c>
       <c r="B10" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$238,A10)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$239,A10)</f>
         <v/>
       </c>
     </row>
@@ -12942,7 +12992,7 @@
         </is>
       </c>
       <c r="B11" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$238,A11)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$239,A11)</f>
         <v/>
       </c>
     </row>
@@ -12953,7 +13003,7 @@
         </is>
       </c>
       <c r="B12" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$238,A12)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$239,A12)</f>
         <v/>
       </c>
     </row>
@@ -12964,7 +13014,7 @@
         </is>
       </c>
       <c r="B13" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$238,A13)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$239,A13)</f>
         <v/>
       </c>
     </row>

--- a/Contact_List_REL.xlsx
+++ b/Contact_List_REL.xlsx
@@ -12,7 +12,7 @@
     <sheet name="README" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contact List'!$A$4:$L$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contact List'!$A$4:$L$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L239"/>
+  <dimension ref="A1:L241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -638,7 +638,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Built automatically from Outlook (shyam@relfinance.co.uk) — last refreshed 2026-08-03. Refreshed weekly; do not hand-edit (see README tab).</t>
+          <t>Built automatically from Outlook (shyam@relfinance.co.uk) — last refreshed 2026-08-10. Refreshed weekly; do not hand-edit (see README tab).</t>
         </is>
       </c>
     </row>
@@ -2772,18 +2772,18 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K44" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L44" s="8" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="I45" s="6" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I67" s="6" t="n">
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="I68" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J68" s="6" t="n">
         <v>0</v>
@@ -4346,11 +4346,11 @@
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="I75" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J75" s="6" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="I78" s="6" t="n">
@@ -4678,11 +4678,11 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="I81" s="6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J81" s="6" t="n">
         <v>0</v>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="I84" s="6" t="n">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="I85" s="6" t="n">
@@ -4916,11 +4916,11 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="I86" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" s="6" t="n">
         <v>0</v>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="I136" s="6" t="n">
@@ -7617,7 +7617,7 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>Alexander Larkins</t>
+          <t>Manjit Randhawa</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -7627,55 +7627,51 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Elysian Residences</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="inlineStr">
-        <is>
-          <t>Financial Accountant</t>
-        </is>
-      </c>
+          <t>DNA Capital Partners</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr"/>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>a.larkins@elysianresidences.com</t>
+          <t>m.randhawa@dna-cp.com</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>07771 144264</t>
+          <t>07956 444475</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="I138" s="6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J138" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K138" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+        <v>0</v>
+      </c>
+      <c r="K138" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L138" s="8" t="inlineStr">
         <is>
-          <t>Main borrower-side reporting contact on the ESSL / Stanmore and The Landsby loans.</t>
+          <t>Director of the DNA Uxbridge development manager — the signatory Osborne Clarke needed alongside Amar Randhawa.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>Ciara Eggenton</t>
+          <t>Alexander Larkins</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -7690,39 +7686,43 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Conveyancing and Progressions Manager</t>
+          <t>Financial Accountant</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>c.eggenton@elysianresidences.com</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr"/>
+          <t>a.larkins@elysianresidences.com</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>07771 144264</t>
+        </is>
+      </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I139" s="6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J139" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+        <v>3</v>
+      </c>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L139" s="8" t="inlineStr">
         <is>
-          <t>Handles ESSL reservations, completions and sales progression reporting to REL.</t>
+          <t>Main borrower-side reporting contact on the ESSL / Stanmore and The Landsby loans.</t>
         </is>
       </c>
     </row>
@@ -7749,45 +7749,41 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>c.osullivan@elysianresidences.com</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>020 8158 6454</t>
-        </is>
-      </c>
+          <t>c.eggenton@elysianresidences.com</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="I140" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J140" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K140" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K140" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L140" s="8" t="inlineStr">
         <is>
-          <t>Former address for Ciara Eggenton, now c.eggenton@elysianresidences.com.</t>
+          <t>Handles ESSL reservations, completions and sales progression reporting to REL.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>Gavin Stein</t>
+          <t>Ciara Eggenton</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -7800,29 +7796,33 @@
           <t>Elysian Residences</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr"/>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Conveyancing and Progressions Manager</t>
+        </is>
+      </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>g.stein@elysianresidences.com</t>
+          <t>c.osullivan@elysianresidences.com</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>+44 (0) 78 2460 4438</t>
+          <t>020 8158 6454</t>
         </is>
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="I141" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J141" s="6" t="n">
         <v>0</v>
@@ -7834,14 +7834,14 @@
       </c>
       <c r="L141" s="8" t="inlineStr">
         <is>
-          <t>Senior Elysian contact on The Landsby / Stanmore LTV covenant breach discussions.</t>
+          <t>Former address for Ciara Eggenton, now c.eggenton@elysianresidences.com.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>Giles Stevens</t>
+          <t>Gavin Stein</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
@@ -7854,20 +7854,20 @@
           <t>Elysian Residences</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr">
-        <is>
-          <t>Director of Transactions</t>
-        </is>
-      </c>
+      <c r="D142" s="4" t="inlineStr"/>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>g.stevens@elysianresidences.com</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr"/>
+          <t>g.stein@elysianresidences.com</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0) 78 2460 4438</t>
+        </is>
+      </c>
       <c r="G142" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H142" s="6" t="inlineStr">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="I142" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J142" s="6" t="n">
         <v>0</v>
@@ -7888,14 +7888,14 @@
       </c>
       <c r="L142" s="8" t="inlineStr">
         <is>
-          <t>Elysian transactions lead on The Landsby / Stanmore OakNorth-REL facility.</t>
+          <t>Senior Elysian contact on The Landsby / Stanmore LTV covenant breach discussions.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>Paul Harries</t>
+          <t>Giles Stevens</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
@@ -7910,22 +7910,18 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Interim Finance Consultant</t>
+          <t>Director of Transactions</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>p.harries@elysianresidences.com</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>07764 510962</t>
-        </is>
-      </c>
+          <t>g.stevens@elysianresidences.com</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H143" s="6" t="inlineStr">
@@ -7934,7 +7930,7 @@
         </is>
       </c>
       <c r="I143" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J143" s="6" t="n">
         <v>0</v>
@@ -7946,14 +7942,14 @@
       </c>
       <c r="L143" s="8" t="inlineStr">
         <is>
-          <t>Leads Elysian's HSTAM1 loan-note tap to cure the Stanmore / Landsby LTV covenant breach.</t>
+          <t>Elysian transactions lead on The Landsby / Stanmore OakNorth-REL facility.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>S. Spencer</t>
+          <t>Paul Harries</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
@@ -7966,44 +7962,52 @@
           <t>Elysian Residences</t>
         </is>
       </c>
-      <c r="D144" s="4" t="inlineStr"/>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Interim Finance Consultant</t>
+        </is>
+      </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>s.spencer@elysianresidences.com</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr"/>
+          <t>p.harries@elysianresidences.com</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>07764 510962</t>
+        </is>
+      </c>
       <c r="G144" s="6" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I144" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J144" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K144" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L144" s="8" t="inlineStr">
         <is>
-          <t>Elysian attendee on the Stanmore MI template discussions.</t>
+          <t>Leads Elysian's HSTAM1 loan-note tap to cure the Stanmore / Landsby LTV covenant breach.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>Scott Thornton</t>
+          <t>S. Spencer</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
@@ -8019,41 +8023,41 @@
       <c r="D145" s="4" t="inlineStr"/>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>s.thornton@elysianresidences.com</t>
+          <t>s.spencer@elysianresidences.com</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I145" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K145" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+        <v>0</v>
+      </c>
+      <c r="K145" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L145" s="8" t="inlineStr">
         <is>
-          <t>Elysian contact on the enhanced MI template and Stanmore monitoring.</t>
+          <t>Elysian attendee on the Stanmore MI template discussions.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>Pete Williams</t>
+          <t>Scott Thornton</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
@@ -8063,47 +8067,47 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Empire Global</t>
+          <t>Elysian Residences</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr"/>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>pete@empireglobal.co.uk</t>
+          <t>s.thornton@elysianresidences.com</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H146" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I146" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+        <v>2</v>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L146" s="8" t="inlineStr">
         <is>
-          <t>Supplied the Colonnade Hotel trading projections for a hotel financing.</t>
+          <t>Elysian contact on the enhanced MI template and Stanmore monitoring.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>Yash Hindocha</t>
+          <t>Pete Williams</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
@@ -8113,55 +8117,47 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Hindocha &amp; Co</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr">
-        <is>
-          <t>Chartered Accountant / principal contact for Anahi Properties Ltd</t>
-        </is>
-      </c>
+          <t>Empire Global</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr"/>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>yash@hindocha.co.uk</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>020 8952 9591</t>
-        </is>
-      </c>
+          <t>pete@empireglobal.co.uk</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H147" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I147" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J147" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K147" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K147" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L147" s="8" t="inlineStr">
         <is>
-          <t>Sponsor behind Anahi Properties / Ashray Holdings; took REL terms on Houndswood House (£950k gross) before funding it via family and friends. Runs Hindocha &amp; Co, chartered accountants in Edgware</t>
+          <t>Supplied the Colonnade Hotel trading projections for a hotel financing.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>Davina Desai</t>
+          <t>Yash Hindocha</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
@@ -8171,47 +8167,55 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>IPCA Group</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr"/>
+          <t>Hindocha &amp; Co</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>Chartered Accountant / principal contact for Anahi Properties Ltd</t>
+        </is>
+      </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>davina.desai@ipcagroup.com</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr"/>
+          <t>yash@hindocha.co.uk</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>020 8952 9591</t>
+        </is>
+      </c>
       <c r="G148" s="6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H148" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I148" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J148" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K148" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L148" s="8" t="inlineStr">
         <is>
-          <t>IPCA Group contact alongside Jignesh Desai</t>
+          <t>Sponsor behind Anahi Properties / Ashray Holdings; took REL terms on Houndswood House (£950k gross) before funding it via family and friends. Runs Hindocha &amp; Co, chartered accountants in Edgware</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>Jignesh Desai</t>
+          <t>Davina Desai</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
@@ -8224,21 +8228,13 @@
           <t>IPCA Group</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
+      <c r="D149" s="4" t="inlineStr"/>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>jignesh@ipcagroup.com</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>+44 7887 712 463</t>
-        </is>
-      </c>
+          <t>davina.desai@ipcagroup.com</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="6" t="inlineStr">
         <is>
           <t>2026-07-06</t>
@@ -8246,30 +8242,30 @@
       </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I149" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J149" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K149" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K149" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L149" s="8" t="inlineStr">
         <is>
-          <t>Active finance discussion with REL including the Moove transaction</t>
+          <t>IPCA Group contact alongside Jignesh Desai</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>Preena Desai</t>
+          <t>Jignesh Desai</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
@@ -8282,13 +8278,21 @@
           <t>IPCA Group</t>
         </is>
       </c>
-      <c r="D150" s="4" t="inlineStr"/>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>preena.desai@ipcagroup.com</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr"/>
+          <t>jignesh@ipcagroup.com</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>+44 7887 712 463</t>
+        </is>
+      </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
           <t>2026-07-06</t>
@@ -8296,30 +8300,30 @@
       </c>
       <c r="H150" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I150" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J150" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K150" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L150" s="8" t="inlineStr">
         <is>
-          <t>IPCA Group contact alongside Jignesh Desai</t>
+          <t>Active finance discussion with REL including the Moove transaction</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>Ajay Laxman</t>
+          <t>Preena Desai</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
@@ -8329,24 +8333,24 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>JMK Group</t>
+          <t>IPCA Group</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr"/>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>ajaylaxman@jmk-group.co.uk</t>
+          <t>preena.desai@ipcagroup.com</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I151" s="6" t="n">
@@ -8360,12 +8364,16 @@
           <t>Named in a thread</t>
         </is>
       </c>
-      <c r="L151" s="8" t="inlineStr"/>
+      <c r="L151" s="8" t="inlineStr">
+        <is>
+          <t>IPCA Group contact alongside Jignesh Desai</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>Harry Chapman</t>
+          <t>Ajay Laxman</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
@@ -8375,24 +8383,24 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Latium Group</t>
+          <t>JMK Group</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr"/>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>harry.chapman@latium.co.uk</t>
+          <t>ajaylaxman@jmk-group.co.uk</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H152" s="6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I152" s="6" t="n">
@@ -8406,16 +8414,12 @@
           <t>Named in a thread</t>
         </is>
       </c>
-      <c r="L152" s="8" t="inlineStr">
-        <is>
-          <t>Latium's contact on the 22-24 Southwark Bridge Road bridge facility</t>
-        </is>
-      </c>
+      <c r="L152" s="8" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Reis</t>
+          <t>Harry Chapman</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
@@ -8425,24 +8429,24 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Lock Terrace</t>
+          <t>Latium Group</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr"/>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>reis@lockterrace.com</t>
+          <t>harry.chapman@latium.co.uk</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I153" s="6" t="n">
@@ -8456,12 +8460,16 @@
           <t>Named in a thread</t>
         </is>
       </c>
-      <c r="L153" s="8" t="inlineStr"/>
+      <c r="L153" s="8" t="inlineStr">
+        <is>
+          <t>Latium's contact on the 22-24 Southwark Bridge Road bridge facility</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Salman</t>
+          <t>Reis</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
@@ -8477,7 +8485,7 @@
       <c r="D154" s="4" t="inlineStr"/>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>salman@lockterrace.com</t>
+          <t>reis@lockterrace.com</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr"/>
@@ -8507,7 +8515,7 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>Tariq</t>
+          <t>Salman</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
@@ -8523,7 +8531,7 @@
       <c r="D155" s="4" t="inlineStr"/>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>tariq@lockterrace.com</t>
+          <t>salman@lockterrace.com</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr"/>
@@ -8553,7 +8561,7 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>Daniela Guberova</t>
+          <t>Tariq</t>
         </is>
       </c>
       <c r="B156" s="10" t="inlineStr">
@@ -8563,55 +8571,43 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>London Land Group</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>Group Financial Controller</t>
-        </is>
-      </c>
+          <t>Lock Terrace</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr"/>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>dguberova@londonland.group</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>+44 7814 681502</t>
-        </is>
-      </c>
+          <t>tariq@lockterrace.com</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H156" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="I156" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J156" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K156" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
-        </is>
-      </c>
-      <c r="L156" s="8" t="inlineStr">
-        <is>
-          <t>Provides KYC and financial information for London Land's Bromley facility</t>
-        </is>
-      </c>
+      <c r="K156" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
+        </is>
+      </c>
+      <c r="L156" s="8" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>Mario Luca Balducci</t>
+          <t>Daniela Guberova</t>
         </is>
       </c>
       <c r="B157" s="10" t="inlineStr">
@@ -8626,18 +8622,22 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Group Financial Controller</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>mbalducci@londonland.group</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr"/>
+          <t>dguberova@londonland.group</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>+44 7814 681502</t>
+        </is>
+      </c>
       <c r="G157" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H157" s="6" t="inlineStr">
@@ -8646,7 +8646,7 @@
         </is>
       </c>
       <c r="I157" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J157" s="6" t="n">
         <v>0</v>
@@ -8658,14 +8658,14 @@
       </c>
       <c r="L157" s="8" t="inlineStr">
         <is>
-          <t>Sponsor principal on the REL / London Land Bromley deal</t>
+          <t>Provides KYC and financial information for London Land's Bromley facility</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>Nugen Group</t>
+          <t>Mario Luca Balducci</t>
         </is>
       </c>
       <c r="B158" s="10" t="inlineStr">
@@ -8675,47 +8675,51 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Nugen Group</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr"/>
+          <t>London Land Group</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>info@nugen-group.co.uk</t>
+          <t>mbalducci@londonland.group</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H158" s="6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="I158" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K158" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L158" s="8" t="inlineStr">
         <is>
-          <t>Developer enquiry on Hickstead &amp; Grovefield hotels</t>
+          <t>Sponsor principal on the REL / London Land Bromley deal</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>Rishi Passi</t>
+          <t>Nugen Group</t>
         </is>
       </c>
       <c r="B159" s="10" t="inlineStr">
@@ -8725,47 +8729,47 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Oblix Living</t>
+          <t>Nugen Group</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr"/>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>rishi@oblixliving.com</t>
+          <t>info@nugen-group.co.uk</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr"/>
       <c r="G159" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H159" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I159" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J159" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K159" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K159" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L159" s="8" t="inlineStr">
         <is>
-          <t>Bidding on a Manchester office and discussing acquisition finance with REL</t>
+          <t>Developer enquiry on Hickstead &amp; Grovefield hotels</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>Rishi Khurana</t>
+          <t>Rishi Passi</t>
         </is>
       </c>
       <c r="B160" s="10" t="inlineStr">
@@ -8775,36 +8779,28 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Purestone Capital</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
+          <t>Oblix Living</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr"/>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>rishi@purestone.uk</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>+44 7946 258 420</t>
-        </is>
-      </c>
+          <t>rishi@oblixliving.com</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr"/>
       <c r="G160" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H160" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I160" s="6" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="J160" s="6" t="n">
         <v>0</v>
@@ -8816,14 +8812,14 @@
       </c>
       <c r="L160" s="8" t="inlineStr">
         <is>
-          <t>Very active sponsor contact on the 80-85 Tottenham Court Road bridge and the mezzanine finance book</t>
+          <t>Bidding on a Manchester office and discussing acquisition finance with REL</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>Anand Morjaria</t>
+          <t>Rishi Khurana</t>
         </is>
       </c>
       <c r="B161" s="10" t="inlineStr">
@@ -8833,47 +8829,55 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Raam Healthcare</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr"/>
+          <t>Purestone Capital</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>anand@raamhealthcare.com</t>
-        </is>
-      </c>
-      <c r="F161" s="4" t="inlineStr"/>
+          <t>rishi@purestone.uk</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>+44 7946 258 420</t>
+        </is>
+      </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H161" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I161" s="6" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J161" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K161" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L161" s="8" t="inlineStr">
         <is>
-          <t>On the Raam Healthcare bridging loan enquiry</t>
+          <t>Very active sponsor contact on the 80-85 Tottenham Court Road bridge and the mezzanine finance book</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>Anshul Morjaria</t>
+          <t>Anand Morjaria</t>
         </is>
       </c>
       <c r="B162" s="10" t="inlineStr">
@@ -8889,7 +8893,7 @@
       <c r="D162" s="4" t="inlineStr"/>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>anshul@raamhealthcare.com</t>
+          <t>anand@raamhealthcare.com</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr"/>
@@ -8923,7 +8927,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>Rohit Morjaria</t>
+          <t>Anshul Morjaria</t>
         </is>
       </c>
       <c r="B163" s="10" t="inlineStr">
@@ -8939,7 +8943,7 @@
       <c r="D163" s="4" t="inlineStr"/>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>rohit@raamhealthcare.com</t>
+          <t>anshul@raamhealthcare.com</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr"/>
@@ -8954,26 +8958,26 @@
         </is>
       </c>
       <c r="I163" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J163" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K163" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K163" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L163" s="8" t="inlineStr">
         <is>
-          <t>Bridging loan enquiry for Raam Healthcare</t>
+          <t>On the Raam Healthcare bridging loan enquiry</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>Adnan Adil</t>
+          <t>Rohit Morjaria</t>
         </is>
       </c>
       <c r="B164" s="10" t="inlineStr">
@@ -8983,47 +8987,47 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Rasmala</t>
+          <t>Raam Healthcare</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr"/>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>adnan.adil@rasmala.com</t>
+          <t>rohit@raamhealthcare.com</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr"/>
       <c r="G164" s="6" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H164" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I164" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J164" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K164" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L164" s="8" t="inlineStr">
         <is>
-          <t>Rasmala colleague on the Oryx 2 / Doxford refinancing and EE Doxford reports</t>
+          <t>Bridging loan enquiry for Raam Healthcare</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Henry Sarkisov</t>
+          <t>Adnan Adil</t>
         </is>
       </c>
       <c r="B165" s="10" t="inlineStr">
@@ -9039,13 +9043,13 @@
       <c r="D165" s="4" t="inlineStr"/>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>henry.sarkisov@rasmala.com</t>
+          <t>adnan.adil@rasmala.com</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr"/>
       <c r="G165" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H165" s="6" t="inlineStr">
@@ -9054,26 +9058,26 @@
         </is>
       </c>
       <c r="I165" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J165" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K165" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K165" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L165" s="8" t="inlineStr">
         <is>
-          <t>Borrower-side lead on Oryx 2 Real Estate / Doxford, refinancing out of REL via Ortus Secured Finance</t>
+          <t>Rasmala colleague on the Oryx 2 / Doxford refinancing and EE Doxford reports</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Vijay Bhandari</t>
+          <t>Henry Sarkisov</t>
         </is>
       </c>
       <c r="B166" s="10" t="inlineStr">
@@ -9083,47 +9087,47 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Uno Hotels</t>
+          <t>Rasmala</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr"/>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>vijay@unohotels.com</t>
+          <t>henry.sarkisov@rasmala.com</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr"/>
       <c r="G166" s="6" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="H166" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="I166" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J166" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K166" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K166" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L166" s="8" t="inlineStr">
         <is>
-          <t>Hotel sponsor; Hickstead &amp; Grovefield loan extension and Uno Thames Hotel terms</t>
+          <t>Borrower-side lead on Oryx 2 Real Estate / Doxford, refinancing out of REL via Ortus Secured Finance</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Manraj Padda</t>
+          <t>Vijay Bhandari</t>
         </is>
       </c>
       <c r="B167" s="10" t="inlineStr">
@@ -9133,55 +9137,47 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Westbrook Partners</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
+          <t>Uno Hotels</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr"/>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>mpadda@westbrookpartners.com</t>
-        </is>
-      </c>
-      <c r="F167" s="4" t="inlineStr">
-        <is>
-          <t>+44 (0) 20 7659 9458</t>
-        </is>
-      </c>
+          <t>vijay@unohotels.com</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr"/>
       <c r="G167" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I167" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K167" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K167" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L167" s="8" t="inlineStr">
         <is>
-          <t>Westbrook sponsor contact on 48 Albemarle Street</t>
+          <t>Hotel sponsor; Hickstead &amp; Grovefield loan extension and Uno Thames Hotel terms</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>Anders Pals</t>
+          <t>Manraj Padda</t>
         </is>
       </c>
       <c r="B168" s="10" t="inlineStr">
@@ -9191,105 +9187,105 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Willowtree Inc</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr"/>
+          <t>Westbrook Partners</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>anders.pals@willowtreeinc.net</t>
-        </is>
-      </c>
-      <c r="F168" s="4" t="inlineStr"/>
+          <t>mpadda@westbrookpartners.com</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0) 20 7659 9458</t>
+        </is>
+      </c>
       <c r="G168" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="I168" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J168" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K168" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L168" s="8" t="inlineStr">
         <is>
-          <t>Involved in Project Nest, Elephant &amp; Castle, London SE1</t>
+          <t>Westbrook sponsor contact on 48 Albemarle Street</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>Alex Andrews</t>
-        </is>
-      </c>
-      <c r="B169" s="11" t="inlineStr">
-        <is>
-          <t>Investor / Family Office</t>
+          <t>Anders Pals</t>
+        </is>
+      </c>
+      <c r="B169" s="10" t="inlineStr">
+        <is>
+          <t>Borrower / Sponsor</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Baccata Trustees Limited</t>
-        </is>
-      </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
+          <t>Willowtree Inc</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr"/>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>aandrews@baccata.co.je</t>
-        </is>
-      </c>
-      <c r="F169" s="4" t="inlineStr">
-        <is>
-          <t>+44 (0) 1534 870670, +44 (0) 1534 496804</t>
-        </is>
-      </c>
+          <t>anders.pals@willowtreeinc.net</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr"/>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H169" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="I169" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J169" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K169" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+        <v>0</v>
+      </c>
+      <c r="K169" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L169" s="8" t="inlineStr">
         <is>
-          <t>Baccata trustee contact on 3A Palace Green and Minard Jersey coupon payments</t>
+          <t>Involved in Project Nest, Elephant &amp; Castle, London SE1</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>Darren English</t>
+          <t>Alex Andrews</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
@@ -9302,13 +9298,21 @@
           <t>Baccata Trustees Limited</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr"/>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>denglish@baccata.co.je</t>
-        </is>
-      </c>
-      <c r="F170" s="4" t="inlineStr"/>
+          <t>aandrews@baccata.co.je</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0) 1534 870670, +44 (0) 1534 496804</t>
+        </is>
+      </c>
       <c r="G170" s="6" t="inlineStr">
         <is>
           <t>2026-01-29</t>
@@ -9316,14 +9320,14 @@
       </c>
       <c r="H170" s="6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I170" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J170" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
@@ -9332,14 +9336,14 @@
       </c>
       <c r="L170" s="8" t="inlineStr">
         <is>
-          <t>Baccata contact on 3A Palace Green completion and Minard Jersey coupons</t>
+          <t>Baccata trustee contact on 3A Palace Green and Minard Jersey coupon payments</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>R Wadsworth</t>
+          <t>Darren English</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
@@ -9355,7 +9359,7 @@
       <c r="D171" s="4" t="inlineStr"/>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>rwadsworth@baccata.co.je</t>
+          <t>denglish@baccata.co.je</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr"/>
@@ -9366,14 +9370,14 @@
       </c>
       <c r="H171" s="6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I171" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
@@ -9382,14 +9386,14 @@
       </c>
       <c r="L171" s="8" t="inlineStr">
         <is>
-          <t>Copied on 3A Palace Green completion and loan note correspondence</t>
+          <t>Baccata contact on 3A Palace Green completion and Minard Jersey coupons</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>Rebekka Brennan</t>
+          <t>R Wadsworth</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
@@ -9402,36 +9406,28 @@
           <t>Baccata Trustees Limited</t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
+      <c r="D172" s="4" t="inlineStr"/>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>rbrennan@baccata.co.je</t>
-        </is>
-      </c>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>+44 (0) 1534 870670, +44 (0) 1534 870600</t>
-        </is>
-      </c>
+          <t>rwadsworth@baccata.co.je</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr"/>
       <c r="G172" s="6" t="inlineStr">
         <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="H172" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
       <c r="I172" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J172" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
@@ -9440,14 +9436,14 @@
       </c>
       <c r="L172" s="8" t="inlineStr">
         <is>
-          <t>Administers monthly Minard Jersey coupon and 3A Palace Green loan note payments</t>
+          <t>Copied on 3A Palace Green completion and loan note correspondence</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>Sean Kenny</t>
+          <t>Rebekka Brennan</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
@@ -9462,22 +9458,22 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Client Director</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>skenny@baccata.co.je</t>
+          <t>rbrennan@baccata.co.je</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>+44 (0) 1534 870670</t>
+          <t>+44 (0) 1534 870670, +44 (0) 1534 870600</t>
         </is>
       </c>
       <c r="G173" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H173" s="6" t="inlineStr">
@@ -9486,10 +9482,10 @@
         </is>
       </c>
       <c r="I173" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J173" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
@@ -9498,14 +9494,14 @@
       </c>
       <c r="L173" s="8" t="inlineStr">
         <is>
-          <t>Jersey trustee lead on 3A Palace Green loan note and Minard Jersey coupons</t>
+          <t>Administers monthly Minard Jersey coupon and 3A Palace Green loan note payments</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>Sienna De Freitas</t>
+          <t>Sean Kenny</t>
         </is>
       </c>
       <c r="B174" s="11" t="inlineStr">
@@ -9520,12 +9516,12 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Client Director</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>sdefreitas@baccata.co.je</t>
+          <t>skenny@baccata.co.je</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
@@ -9535,19 +9531,19 @@
       </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H174" s="6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I174" s="6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J174" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
@@ -9556,14 +9552,14 @@
       </c>
       <c r="L174" s="8" t="inlineStr">
         <is>
-          <t>Handles Morka Holdings Ltd coupon payments</t>
+          <t>Jersey trustee lead on 3A Palace Green loan note and Minard Jersey coupons</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>Ajay Gokani</t>
+          <t>Sienna De Freitas</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
@@ -9573,35 +9569,39 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Elite Mobile</t>
-        </is>
-      </c>
-      <c r="D175" s="4" t="inlineStr"/>
+          <t>Baccata Trustees Limited</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>ajay@elitemobile.com</t>
+          <t>sdefreitas@baccata.co.je</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>+44 (0) 208 799 8001, +44 (0) 20 8799 8000</t>
+          <t>+44 (0) 1534 870670</t>
         </is>
       </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="I175" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J175" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
@@ -9610,14 +9610,14 @@
       </c>
       <c r="L175" s="8" t="inlineStr">
         <is>
-          <t>REL investor - approves facility extensions and reinvests redemptions (Oryx 2, DNA Uxbridge, St Clements House).</t>
+          <t>Handles Morka Holdings Ltd coupon payments</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Mihir Gokani</t>
+          <t>Ajay Gokani</t>
         </is>
       </c>
       <c r="B176" s="11" t="inlineStr">
@@ -9633,10 +9633,14 @@
       <c r="D176" s="4" t="inlineStr"/>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>mihir@elitemobile.com</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr"/>
+          <t>ajay@elitemobile.com</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0) 208 799 8001, +44 (0) 20 8799 8000</t>
+        </is>
+      </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
           <t>2026-01-29</t>
@@ -9648,10 +9652,10 @@
         </is>
       </c>
       <c r="I176" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J176" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
@@ -9660,14 +9664,14 @@
       </c>
       <c r="L176" s="8" t="inlineStr">
         <is>
-          <t>Elite Mobile side of the Chotilal Lakhani REL bond interest payments.</t>
+          <t>REL investor - approves facility extensions and reinvests redemptions (Oryx 2, DNA Uxbridge, St Clements House).</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>Sarit Raja-Shah</t>
+          <t>Mihir Gokani</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
@@ -9677,13 +9681,13 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>I&amp;M Bank</t>
+          <t>Elite Mobile</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr"/>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>ssrajashah@imbank.co.ke</t>
+          <t>mihir@elitemobile.com</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr"/>
@@ -9698,10 +9702,10 @@
         </is>
       </c>
       <c r="I177" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J177" s="6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
@@ -9710,14 +9714,14 @@
       </c>
       <c r="L177" s="8" t="inlineStr">
         <is>
-          <t>REL shareholder; signs off on recycling shareholder funds (Oryx 2 redemption, Bromley, DNA Uxbridge) and receives REL management accounts</t>
+          <t>Elite Mobile side of the Chotilal Lakhani REL bond interest payments.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>Hemlata / Jay</t>
+          <t>Sarit Raja-Shah</t>
         </is>
       </c>
       <c r="B178" s="11" t="inlineStr">
@@ -9727,19 +9731,19 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Jarishka</t>
+          <t>I&amp;M Bank</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr"/>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>jaynbi27@gmail.com</t>
+          <t>ssrajashah@imbank.co.ke</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr"/>
       <c r="G178" s="6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H178" s="6" t="inlineStr">
@@ -9748,10 +9752,10 @@
         </is>
       </c>
       <c r="I178" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J178" s="6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
@@ -9760,14 +9764,14 @@
       </c>
       <c r="L178" s="8" t="inlineStr">
         <is>
-          <t>Receives monthly 3A Palace Green loan note statements</t>
+          <t>REL shareholder; signs off on recycling shareholder funds (Oryx 2 redemption, Bromley, DNA Uxbridge) and receives REL management accounts</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>Ketan Morjaria</t>
+          <t>Hemlata / Jay</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
@@ -9777,19 +9781,19 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Morka Group</t>
+          <t>Jarishka</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr"/>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>ketan@morkagroup.com</t>
+          <t>jaynbi27@gmail.com</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr"/>
       <c r="G179" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H179" s="6" t="inlineStr">
@@ -9798,10 +9802,10 @@
         </is>
       </c>
       <c r="I179" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J179" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
@@ -9810,14 +9814,14 @@
       </c>
       <c r="L179" s="8" t="inlineStr">
         <is>
-          <t>Capital side - 7A Palace Green loan note, calls on St Clements House and Peninsular House</t>
+          <t>Receives monthly 3A Palace Green loan note statements</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>Neel Rajani</t>
+          <t>Ketan Morjaria</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
@@ -9827,31 +9831,31 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Reel Wealth Ltd</t>
+          <t>Morka Group</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr"/>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>neel@reelholdings.co.uk</t>
+          <t>ketan@morkagroup.com</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr"/>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I180" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J180" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
@@ -9860,14 +9864,14 @@
       </c>
       <c r="L180" s="8" t="inlineStr">
         <is>
-          <t>Holds the Reel Wealth loan note in The Landsby, Stanmore; Shyam sends him the periodic update and interest payments</t>
+          <t>Capital side - 7A Palace Green loan note, calls on St Clements House and Peninsular House</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>Paul Bulstrode</t>
+          <t>Neel Rajani</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
@@ -9877,47 +9881,47 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>VG (Jersey)</t>
+          <t>Reel Wealth Ltd</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr"/>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>pbulstrode@vg.je</t>
+          <t>neel@reelholdings.co.uk</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr"/>
       <c r="G181" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H181" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="I181" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J181" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+        <v>3</v>
+      </c>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L181" s="8" t="inlineStr">
         <is>
-          <t>Jersey administrator of the Oryx 2 Real Estate / Rasmala structure; scheduled payment notifications</t>
+          <t>Holds the Reel Wealth loan note in The Landsby, Stanmore; Shyam sends him the periodic update and interest payments</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>Rasmala Administration Team</t>
+          <t>Paul Bulstrode</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
@@ -9933,7 +9937,7 @@
       <c r="D182" s="4" t="inlineStr"/>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>rasmala@vg.je</t>
+          <t>pbulstrode@vg.je</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr"/>
@@ -9960,14 +9964,14 @@
       </c>
       <c r="L182" s="8" t="inlineStr">
         <is>
-          <t>VG Jersey administration inbox for the Rasmala Oryx 2 Real Estate payments</t>
+          <t>Jersey administrator of the Oryx 2 Real Estate / Rasmala structure; scheduled payment notifications</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>Stuart Andre</t>
+          <t>Rasmala Administration Team</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
@@ -9983,7 +9987,7 @@
       <c r="D183" s="4" t="inlineStr"/>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>sandre@vg.je</t>
+          <t>rasmala@vg.je</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr"/>
@@ -10010,14 +10014,14 @@
       </c>
       <c r="L183" s="8" t="inlineStr">
         <is>
-          <t>VG Jersey administrator on the Oryx 2 Real Estate payment notifications</t>
+          <t>VG Jersey administration inbox for the Rasmala Oryx 2 Real Estate payments</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>Chotilal Lakhani</t>
+          <t>Stuart Andre</t>
         </is>
       </c>
       <c r="B184" s="11" t="inlineStr">
@@ -10025,45 +10029,49 @@
           <t>Investor / Family Office</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr"/>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>VG (Jersey)</t>
+        </is>
+      </c>
       <c r="D184" s="4" t="inlineStr"/>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>chhotukaka@gmail.com</t>
+          <t>sandre@vg.je</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr"/>
       <c r="G184" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="I184" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J184" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="K184" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+        <v>0</v>
+      </c>
+      <c r="K184" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L184" s="8" t="inlineStr">
         <is>
-          <t>REL Finance bondholder - receives monthly bond interest payments.</t>
+          <t>VG Jersey administrator on the Oryx 2 Real Estate payment notifications</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>Neelam Bose</t>
+          <t>Chotilal Lakhani</t>
         </is>
       </c>
       <c r="B185" s="11" t="inlineStr">
@@ -10075,13 +10083,13 @@
       <c r="D185" s="4" t="inlineStr"/>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>neelam_bose@hotmail.com</t>
+          <t>chhotukaka@gmail.com</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr"/>
       <c r="G185" s="6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H185" s="6" t="inlineStr">
@@ -10090,10 +10098,10 @@
         </is>
       </c>
       <c r="I185" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J185" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
@@ -10102,14 +10110,14 @@
       </c>
       <c r="L185" s="8" t="inlineStr">
         <is>
-          <t>Bose family loan note holder; receives monthly 3A Palace Green statements</t>
+          <t>REL Finance bondholder - receives monthly bond interest payments.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>Pragna Morjaria</t>
+          <t>Neelam Bose</t>
         </is>
       </c>
       <c r="B186" s="11" t="inlineStr">
@@ -10121,13 +10129,13 @@
       <c r="D186" s="4" t="inlineStr"/>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>pragna_morjaria@hotmail.com</t>
+          <t>neelam_bose@hotmail.com</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr"/>
       <c r="G186" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H186" s="6" t="inlineStr">
@@ -10148,64 +10156,60 @@
       </c>
       <c r="L186" s="8" t="inlineStr">
         <is>
-          <t>Morjaria family loan note holder; 7A Palace Green certificate and accession undertaking, plus 3A Palace Green statements</t>
+          <t>Bose family loan note holder; receives monthly 3A Palace Green statements</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>G. Smith</t>
-        </is>
-      </c>
-      <c r="B187" s="12" t="inlineStr">
-        <is>
-          <t>Solicitor / Legal</t>
-        </is>
-      </c>
-      <c r="C187" s="4" t="inlineStr">
-        <is>
-          <t>Fladgate LLP</t>
-        </is>
-      </c>
+          <t>Pragna Morjaria</t>
+        </is>
+      </c>
+      <c r="B187" s="11" t="inlineStr">
+        <is>
+          <t>Investor / Family Office</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr"/>
       <c r="D187" s="4" t="inlineStr"/>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>gsmith@fladgate.com</t>
+          <t>pragna_morjaria@hotmail.com</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr"/>
       <c r="G187" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H187" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I187" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J187" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K187" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+        <v>6</v>
+      </c>
+      <c r="K187" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L187" s="8" t="inlineStr">
         <is>
-          <t>Fladgate legal team on the Chart Forte (Monument) funds flow with OakNorth.</t>
+          <t>Morjaria family loan note holder; 7A Palace Green certificate and accession undertaking, plus 3A Palace Green statements</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>R. Serhal</t>
+          <t>G. Smith</t>
         </is>
       </c>
       <c r="B188" s="12" t="inlineStr">
@@ -10221,7 +10225,7 @@
       <c r="D188" s="4" t="inlineStr"/>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>rserhal@fladgate.com</t>
+          <t>gsmith@fladgate.com</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr"/>
@@ -10255,7 +10259,7 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>V. Brownell</t>
+          <t>R. Serhal</t>
         </is>
       </c>
       <c r="B189" s="12" t="inlineStr">
@@ -10271,7 +10275,7 @@
       <c r="D189" s="4" t="inlineStr"/>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>vbrownell@fladgate.com</t>
+          <t>rserhal@fladgate.com</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr"/>
@@ -10305,7 +10309,7 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>E Ooi</t>
+          <t>V. Brownell</t>
         </is>
       </c>
       <c r="B190" s="12" t="inlineStr">
@@ -10315,24 +10319,24 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Lawrence Stephens</t>
+          <t>Fladgate LLP</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr"/>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>eooi@lawstep.co.uk</t>
+          <t>vbrownell@fladgate.com</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr"/>
       <c r="G190" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H190" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I190" s="6" t="n">
@@ -10348,14 +10352,14 @@
       </c>
       <c r="L190" s="8" t="inlineStr">
         <is>
-          <t>Lawrence Stephens team member on the Oryx 2 redemption</t>
+          <t>Fladgate legal team on the Chart Forte (Monument) funds flow with OakNorth.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>L Brown</t>
+          <t>E Ooi</t>
         </is>
       </c>
       <c r="B191" s="12" t="inlineStr">
@@ -10371,18 +10375,18 @@
       <c r="D191" s="4" t="inlineStr"/>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>lbrown@lawstep.co.uk</t>
+          <t>eooi@lawstep.co.uk</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr"/>
       <c r="G191" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H191" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="I191" s="6" t="n">
@@ -10398,14 +10402,14 @@
       </c>
       <c r="L191" s="8" t="inlineStr">
         <is>
-          <t>Lawrence Stephens contact on the Uno Thames Hotel legal quote</t>
+          <t>Lawrence Stephens team member on the Oryx 2 redemption</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>Milana Katz</t>
+          <t>L Brown</t>
         </is>
       </c>
       <c r="B192" s="12" t="inlineStr">
@@ -10418,24 +10422,16 @@
           <t>Lawrence Stephens</t>
         </is>
       </c>
-      <c r="D192" s="4" t="inlineStr">
-        <is>
-          <t>Senior Associate</t>
-        </is>
-      </c>
+      <c r="D192" s="4" t="inlineStr"/>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>mkatz@lawstep.co.uk</t>
-        </is>
-      </c>
-      <c r="F192" s="4" t="inlineStr">
-        <is>
-          <t>+44 (0)20 3004 3982, +44 (0)7858 518 388</t>
-        </is>
-      </c>
+          <t>lbrown@lawstep.co.uk</t>
+        </is>
+      </c>
+      <c r="F192" s="4" t="inlineStr"/>
       <c r="G192" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H192" s="6" t="inlineStr">
@@ -10444,26 +10440,26 @@
         </is>
       </c>
       <c r="I192" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J192" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K192" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K192" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L192" s="8" t="inlineStr">
         <is>
-          <t>Ran the Oryx 2 Real Estate loan redemption for REL</t>
+          <t>Lawrence Stephens contact on the Uno Thames Hotel legal quote</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>Andrew Parsons</t>
+          <t>Milana Katz</t>
         </is>
       </c>
       <c r="B193" s="12" t="inlineStr">
@@ -10473,36 +10469,36 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Osborne Clarke</t>
+          <t>Lawrence Stephens</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Senior Associate</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>andrew.parsons@osborneclarke.com</t>
+          <t>mkatz@lawstep.co.uk</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>+44 117 917 4276</t>
+          <t>+44 (0)20 3004 3982, +44 (0)7858 518 388</t>
         </is>
       </c>
       <c r="G193" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="I193" s="6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J193" s="6" t="n">
         <v>0</v>
@@ -10514,14 +10510,14 @@
       </c>
       <c r="L193" s="8" t="inlineStr">
         <is>
-          <t>REL's lender-side counsel on the DNA Uxbridge loan extension and the GBB loan-on-loan documentation</t>
+          <t>Ran the Oryx 2 Real Estate loan redemption for REL</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>Alice King</t>
+          <t>Andrew Parsons</t>
         </is>
       </c>
       <c r="B194" s="12" t="inlineStr">
@@ -10531,36 +10527,36 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Shepherd and Wedderburn LLP</t>
+          <t>Osborne Clarke</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Trainee Solicitor, Banking &amp; Corporate Finance</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>alice.king@shepwedd.com</t>
+          <t>andrew.parsons@osborneclarke.com</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>+44 (0)20 7429 4975, +44 (0)771 378 2359</t>
+          <t>+44 117 917 4276</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H194" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I194" s="6" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J194" s="6" t="n">
         <v>0</v>
@@ -10572,14 +10568,14 @@
       </c>
       <c r="L194" s="8" t="inlineStr">
         <is>
-          <t>Drafting REL's facility agreement and subordination on 1 Westmoreland Road, Bromley (London Land)</t>
+          <t>REL's lender-side counsel on the DNA Uxbridge loan extension and the GBB loan-on-loan documentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>Lauren McLeod</t>
+          <t>Savina Sangha</t>
         </is>
       </c>
       <c r="B195" s="12" t="inlineStr">
@@ -10589,24 +10585,24 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Shepherd and Wedderburn LLP</t>
+          <t>Osborne Clarke</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr"/>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>lauren.mcleod@shepwedd.com</t>
+          <t>savina.sangha@osborneclarke.com</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr"/>
       <c r="G195" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H195" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I195" s="6" t="n">
@@ -10622,14 +10618,14 @@
       </c>
       <c r="L195" s="8" t="inlineStr">
         <is>
-          <t>Shepherd and Wedderburn team on the Bromley draft facility agreement</t>
+          <t>Works with Andrew Parsons on the DNA Uxbridge extension; runs the DocuSign execution of the reservation of rights letter.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>Sam Clarke</t>
+          <t>Alice King</t>
         </is>
       </c>
       <c r="B196" s="12" t="inlineStr">
@@ -10644,22 +10640,22 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Partner, Banking and Finance</t>
+          <t>Trainee Solicitor, Banking &amp; Corporate Finance</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>sam.clarke@shepwedd.com</t>
+          <t>alice.king@shepwedd.com</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>+44 (0)20 7429 4681, +44 (0)770 235 1526</t>
+          <t>+44 (0)20 7429 4975, +44 (0)771 378 2359</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H196" s="6" t="inlineStr">
@@ -10680,14 +10676,14 @@
       </c>
       <c r="L196" s="8" t="inlineStr">
         <is>
-          <t>Lead partner acting for REL on the 1 Westmoreland Road, Bromley financing</t>
+          <t>Drafting REL's facility agreement and subordination on 1 Westmoreland Road, Bromley (London Land)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>Chris Mills</t>
+          <t>Lauren McLeod</t>
         </is>
       </c>
       <c r="B197" s="12" t="inlineStr">
@@ -10697,24 +10693,24 @@
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Shoosmiths LLP</t>
+          <t>Shepherd and Wedderburn LLP</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr"/>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>chris.mills@shoosmiths.com</t>
+          <t>lauren.mcleod@shepwedd.com</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr"/>
       <c r="G197" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H197" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="I197" s="6" t="n">
@@ -10730,14 +10726,14 @@
       </c>
       <c r="L197" s="8" t="inlineStr">
         <is>
-          <t>Shoosmiths quote for the 1 Westmoreland Road, Bromley deal</t>
+          <t>Shepherd and Wedderburn team on the Bromley draft facility agreement</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>Sam Jadhav</t>
+          <t>Sam Clarke</t>
         </is>
       </c>
       <c r="B198" s="12" t="inlineStr">
@@ -10747,16 +10743,24 @@
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>Shoosmiths LLP</t>
-        </is>
-      </c>
-      <c r="D198" s="4" t="inlineStr"/>
+          <t>Shepherd and Wedderburn LLP</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>Partner, Banking and Finance</t>
+        </is>
+      </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>sam.jadhav@shoosmiths.com</t>
-        </is>
-      </c>
-      <c r="F198" s="4" t="inlineStr"/>
+          <t>sam.clarke@shepwedd.com</t>
+        </is>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0)20 7429 4681, +44 (0)770 235 1526</t>
+        </is>
+      </c>
       <c r="G198" s="6" t="inlineStr">
         <is>
           <t>2026-02-11</t>
@@ -10764,115 +10768,107 @@
       </c>
       <c r="H198" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="I198" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J198" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K198" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L198" s="8" t="inlineStr">
         <is>
-          <t>Shoosmiths quote for the 1 Westmoreland Road, Bromley deal</t>
+          <t>Lead partner acting for REL on the 1 Westmoreland Road, Bromley financing</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>Chris Theodosiou</t>
-        </is>
-      </c>
-      <c r="B199" s="13" t="inlineStr">
-        <is>
-          <t>Valuer / Property Professional</t>
+          <t>Chris Mills</t>
+        </is>
+      </c>
+      <c r="B199" s="12" t="inlineStr">
+        <is>
+          <t>Solicitor / Legal</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Allsop LLP</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr">
-        <is>
-          <t>Partner, Residential Valuation</t>
-        </is>
-      </c>
+          <t>Shoosmiths LLP</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr"/>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>chris.theodosiou@allsop.co.uk</t>
-        </is>
-      </c>
-      <c r="F199" s="4" t="inlineStr">
-        <is>
-          <t>020 7344 2654, 07918 284861</t>
-        </is>
-      </c>
+          <t>chris.mills@shoosmiths.com</t>
+        </is>
+      </c>
+      <c r="F199" s="4" t="inlineStr"/>
       <c r="G199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I199" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J199" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K199" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K199" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L199" s="8" t="inlineStr">
         <is>
-          <t>Valuer on the Askew Road bridge security</t>
+          <t>Shoosmiths quote for the 1 Westmoreland Road, Bromley deal</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>Josh Ware</t>
-        </is>
-      </c>
-      <c r="B200" s="13" t="inlineStr">
-        <is>
-          <t>Valuer / Property Professional</t>
+          <t>Sam Jadhav</t>
+        </is>
+      </c>
+      <c r="B200" s="12" t="inlineStr">
+        <is>
+          <t>Solicitor / Legal</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>Allsop LLP</t>
+          <t>Shoosmiths LLP</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr"/>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>josh.ware@allsop.co.uk</t>
+          <t>sam.jadhav@shoosmiths.com</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr"/>
       <c r="G200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I200" s="6" t="n">
@@ -10888,14 +10884,14 @@
       </c>
       <c r="L200" s="8" t="inlineStr">
         <is>
-          <t>Allsop valuation team on Askew Road, alongside Chris Theodosiou</t>
+          <t>Shoosmiths quote for the 1 Westmoreland Road, Bromley deal</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>Karen Callahan</t>
+          <t>Chris Theodosiou</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
@@ -10905,22 +10901,22 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Knight Frank</t>
+          <t>Allsop LLP</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Partner, Head of Hotels - Valuation &amp; Advisory</t>
+          <t>Partner, Residential Valuation</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>karen.callahan@knightfrank.com</t>
+          <t>chris.theodosiou@allsop.co.uk</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>+44 20 7861 1086</t>
+          <t>020 7344 2654, 07918 284861</t>
         </is>
       </c>
       <c r="G201" s="6" t="inlineStr">
@@ -10930,30 +10926,30 @@
       </c>
       <c r="H201" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I201" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J201" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K201" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K201" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L201" s="8" t="inlineStr">
         <is>
-          <t>Knight Frank hotel valuation contact for hospitality collateral</t>
+          <t>Valuer on the Askew Road bridge security</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>Greg Stalcup</t>
+          <t>Josh Ware</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
@@ -10963,24 +10959,24 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>Levy Real Estate LLP</t>
+          <t>Allsop LLP</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr"/>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>greg.stalcup@levyrealestate.co.uk</t>
+          <t>josh.ware@allsop.co.uk</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr"/>
       <c r="G202" s="6" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H202" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I202" s="6" t="n">
@@ -10996,14 +10992,14 @@
       </c>
       <c r="L202" s="8" t="inlineStr">
         <is>
-          <t>Levy Real Estate agent acting for the landlord on TG Jones, Uxbridge - the tenancy running through REL's DNA Uxbridge (Belmont Place) security.</t>
+          <t>Allsop valuation team on Askew Road, alongside Chris Theodosiou</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>Oliver Chivers</t>
+          <t>Karen Callahan</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
@@ -11013,47 +11009,55 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Montagu Evans</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="inlineStr"/>
+          <t>Knight Frank</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>Partner, Head of Hotels - Valuation &amp; Advisory</t>
+        </is>
+      </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>oliver.chivers@montagu-evans.co.uk</t>
-        </is>
-      </c>
-      <c r="F203" s="4" t="inlineStr"/>
+          <t>karen.callahan@knightfrank.com</t>
+        </is>
+      </c>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>+44 20 7861 1086</t>
+        </is>
+      </c>
       <c r="G203" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H203" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I203" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J203" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K203" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K203" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L203" s="8" t="inlineStr">
         <is>
-          <t>Quoted the valuation fee for Farriers Yard &amp; Forge</t>
+          <t>Knight Frank hotel valuation contact for hospitality collateral</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>Imogen Colegrave</t>
+          <t>Greg Stalcup</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
@@ -11063,24 +11067,24 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Newmark</t>
+          <t>Levy Real Estate LLP</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr"/>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>imogen.colegrave@nmrk.com</t>
+          <t>greg.stalcup@levyrealestate.co.uk</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr"/>
       <c r="G204" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H204" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="I204" s="6" t="n">
@@ -11096,14 +11100,14 @@
       </c>
       <c r="L204" s="8" t="inlineStr">
         <is>
-          <t>On the 1 Westmoreland Road Bromley valuation thread</t>
+          <t>Levy Real Estate agent acting for the landlord on TG Jones, Uxbridge - the tenancy running through REL's DNA Uxbridge (Belmont Place) security.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>Liana Psarros</t>
+          <t>Oliver Chivers</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
@@ -11113,47 +11117,47 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Newmark</t>
+          <t>Montagu Evans</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr"/>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>liana.psarros@nmrk.com</t>
+          <t>oliver.chivers@montagu-evans.co.uk</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr"/>
       <c r="G205" s="6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H205" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="I205" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J205" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K205" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K205" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L205" s="8" t="inlineStr">
         <is>
-          <t>Handled the Bromley valuation fee quote</t>
+          <t>Quoted the valuation fee for Farriers Yard &amp; Forge</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>Newmark UK Credit Control</t>
+          <t>Imogen Colegrave</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
@@ -11169,18 +11173,18 @@
       <c r="D206" s="4" t="inlineStr"/>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>ukcreditcontrol@nmrk.com</t>
+          <t>imogen.colegrave@nmrk.com</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr"/>
       <c r="G206" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H206" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I206" s="6" t="n">
@@ -11196,14 +11200,14 @@
       </c>
       <c r="L206" s="8" t="inlineStr">
         <is>
-          <t>Newmark billing contact for the Bromley valuation fee</t>
+          <t>On the 1 Westmoreland Road Bromley valuation thread</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>Robert Davies</t>
+          <t>Liana Psarros</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
@@ -11216,52 +11220,44 @@
           <t>Newmark</t>
         </is>
       </c>
-      <c r="D207" s="4" t="inlineStr">
-        <is>
-          <t>Partner, Newmark Planning and Development</t>
-        </is>
-      </c>
+      <c r="D207" s="4" t="inlineStr"/>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>robert.davies@nmrk.com</t>
-        </is>
-      </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>+44 794 458 4053, 020 7333 6207</t>
-        </is>
-      </c>
+          <t>liana.psarros@nmrk.com</t>
+        </is>
+      </c>
+      <c r="F207" s="4" t="inlineStr"/>
       <c r="G207" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H207" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="I207" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J207" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K207" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K207" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L207" s="8" t="inlineStr">
         <is>
-          <t>Lead valuer on 1 Westmoreland Road, Bromley</t>
+          <t>Handled the Bromley valuation fee quote</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>Rosanna Cole</t>
+          <t>Newmark UK Credit Control</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
@@ -11274,52 +11270,44 @@
           <t>Newmark</t>
         </is>
       </c>
-      <c r="D208" s="4" t="inlineStr">
-        <is>
-          <t>Associate, Newmark Planning and Development</t>
-        </is>
-      </c>
+      <c r="D208" s="4" t="inlineStr"/>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>rosanna.cole@nmrk.com</t>
-        </is>
-      </c>
-      <c r="F208" s="4" t="inlineStr">
-        <is>
-          <t>+44 7387537081, 020 3486 3667</t>
-        </is>
-      </c>
+          <t>ukcreditcontrol@nmrk.com</t>
+        </is>
+      </c>
+      <c r="F208" s="4" t="inlineStr"/>
       <c r="G208" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H208" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="I208" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J208" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K208" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K208" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L208" s="8" t="inlineStr">
         <is>
-          <t>Working draft valuation figures for 1 Westmoreland Road, Bromley</t>
+          <t>Newmark billing contact for the Bromley valuation fee</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>John Loveday</t>
+          <t>Robert Davies</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
@@ -11329,155 +11317,167 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Smith Price RRG</t>
-        </is>
-      </c>
-      <c r="D209" s="4" t="inlineStr"/>
+          <t>Newmark</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t>Partner, Newmark Planning and Development</t>
+        </is>
+      </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>johnloveday@sprrg.co.uk</t>
+          <t>robert.davies@nmrk.com</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>+44 20 7409 2100, +44 7778 158125</t>
+          <t>+44 794 458 4053, 020 7333 6207</t>
         </is>
       </c>
       <c r="G209" s="6" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H209" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="I209" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J209" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K209" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K209" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L209" s="8" t="inlineStr">
         <is>
-          <t>Smith Price RRG surveyor acting for the Post Office tenant at TG Jones, Uxbridge, opposite the landlord on REL's DNA Uxbridge (Belmont Place) security.</t>
+          <t>Lead valuer on 1 Westmoreland Road, Bromley</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>Gordon Thrower</t>
-        </is>
-      </c>
-      <c r="B210" s="14" t="inlineStr">
-        <is>
-          <t>Accountant / Tax</t>
+          <t>Rosanna Cole</t>
+        </is>
+      </c>
+      <c r="B210" s="13" t="inlineStr">
+        <is>
+          <t>Valuer / Property Professional</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>MHA</t>
-        </is>
-      </c>
-      <c r="D210" s="4" t="inlineStr"/>
+          <t>Newmark</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="inlineStr">
+        <is>
+          <t>Associate, Newmark Planning and Development</t>
+        </is>
+      </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>gordon.thrower@mha.co.uk</t>
-        </is>
-      </c>
-      <c r="F210" s="4" t="inlineStr"/>
+          <t>rosanna.cole@nmrk.com</t>
+        </is>
+      </c>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>+44 7387537081, 020 3486 3667</t>
+        </is>
+      </c>
       <c r="G210" s="6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H210" s="6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="I210" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J210" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K210" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
-        </is>
-      </c>
-      <c r="L210" s="8" t="inlineStr"/>
+      <c r="K210" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L210" s="8" t="inlineStr">
+        <is>
+          <t>Working draft valuation figures for 1 Westmoreland Road, Bromley</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>MHA Payroll Services</t>
-        </is>
-      </c>
-      <c r="B211" s="14" t="inlineStr">
-        <is>
-          <t>Accountant / Tax</t>
+          <t>John Loveday</t>
+        </is>
+      </c>
+      <c r="B211" s="13" t="inlineStr">
+        <is>
+          <t>Valuer / Property Professional</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>MHA</t>
-        </is>
-      </c>
-      <c r="D211" s="4" t="inlineStr">
-        <is>
-          <t>Outsource Services</t>
-        </is>
-      </c>
+          <t>Smith Price RRG</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr"/>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>macintyrehudsonpayrollservices@mha.co.uk</t>
+          <t>johnloveday@sprrg.co.uk</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>+44 (0)121 237 1855, +44 (0)20 7429 4100</t>
+          <t>+44 20 7409 2100, +44 7778 158125</t>
         </is>
       </c>
       <c r="G211" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H211" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="I211" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J211" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K211" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K211" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L211" s="8" t="inlineStr">
         <is>
-          <t>Runs REL Finance monthly payroll input</t>
+          <t>Smith Price RRG surveyor acting for the Post Office tenant at TG Jones, Uxbridge, opposite the landlord on REL's DNA Uxbridge (Belmont Place) security.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>Neil Stern</t>
+          <t>Gordon Thrower</t>
         </is>
       </c>
       <c r="B212" s="14" t="inlineStr">
@@ -11493,18 +11493,18 @@
       <c r="D212" s="4" t="inlineStr"/>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>neil.stern@mha.co.uk</t>
+          <t>gordon.thrower@mha.co.uk</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr"/>
       <c r="G212" s="6" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I212" s="6" t="n">
@@ -11518,16 +11518,12 @@
           <t>Named in a thread</t>
         </is>
       </c>
-      <c r="L212" s="8" t="inlineStr">
-        <is>
-          <t>Senior MHA contact on REL management accounts and the DNA Uxbridge deal</t>
-        </is>
-      </c>
+      <c r="L212" s="8" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>Selena Mariposa</t>
+          <t>MHA Payroll Services</t>
         </is>
       </c>
       <c r="B213" s="14" t="inlineStr">
@@ -11540,40 +11536,52 @@
           <t>MHA</t>
         </is>
       </c>
-      <c r="D213" s="4" t="inlineStr"/>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>Outsource Services</t>
+        </is>
+      </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>selena.mariposa@mha.co.uk</t>
-        </is>
-      </c>
-      <c r="F213" s="4" t="inlineStr"/>
+          <t>macintyrehudsonpayrollservices@mha.co.uk</t>
+        </is>
+      </c>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>+44 (0)121 237 1855, +44 (0)20 7429 4100</t>
+        </is>
+      </c>
       <c r="G213" s="6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H213" s="6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I213" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J213" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K213" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
-        </is>
-      </c>
-      <c r="L213" s="8" t="inlineStr"/>
+      <c r="K213" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L213" s="8" t="inlineStr">
+        <is>
+          <t>Runs REL Finance monthly payroll input</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>Taimur Sultan</t>
+          <t>Neil Stern</t>
         </is>
       </c>
       <c r="B214" s="14" t="inlineStr">
@@ -11586,21 +11594,13 @@
           <t>MHA</t>
         </is>
       </c>
-      <c r="D214" s="4" t="inlineStr">
-        <is>
-          <t>Accounts Manager</t>
-        </is>
-      </c>
+      <c r="D214" s="4" t="inlineStr"/>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>taimur.sultan@mha.co.uk</t>
-        </is>
-      </c>
-      <c r="F214" s="4" t="inlineStr">
-        <is>
-          <t>+44 (0)204 546 6050</t>
-        </is>
-      </c>
+          <t>neil.stern@mha.co.uk</t>
+        </is>
+      </c>
+      <c r="F214" s="4" t="inlineStr"/>
       <c r="G214" s="6" t="inlineStr">
         <is>
           <t>2025-01-27</t>
@@ -11612,115 +11612,111 @@
         </is>
       </c>
       <c r="I214" s="6" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J214" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K214" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+        <v>0</v>
+      </c>
+      <c r="K214" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L214" s="8" t="inlineStr">
         <is>
-          <t>Prepares REL's quarterly management accounts - day-to-day MHA contact</t>
+          <t>Senior MHA contact on REL management accounts and the DNA Uxbridge deal</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>Rob</t>
-        </is>
-      </c>
-      <c r="B215" s="15" t="inlineStr">
-        <is>
-          <t>Service Provider</t>
+          <t>Selena Mariposa</t>
+        </is>
+      </c>
+      <c r="B215" s="14" t="inlineStr">
+        <is>
+          <t>Accountant / Tax</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Feed.fm</t>
+          <t>MHA</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr"/>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>rob@feed.fm</t>
+          <t>selena.mariposa@mha.co.uk</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr"/>
       <c r="G215" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H215" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I215" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J215" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K215" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
-        </is>
-      </c>
-      <c r="L215" s="8" t="inlineStr">
-        <is>
-          <t>Replied to an Adaptr (Feed.fm) music licensing web enquiry.</t>
-        </is>
-      </c>
+      <c r="K215" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
+        </is>
+      </c>
+      <c r="L215" s="8" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>Tyler Sear</t>
-        </is>
-      </c>
-      <c r="B216" s="15" t="inlineStr">
-        <is>
-          <t>Service Provider</t>
+          <t>Taimur Sultan</t>
+        </is>
+      </c>
+      <c r="B216" s="14" t="inlineStr">
+        <is>
+          <t>Accountant / Tax</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Green Cardinal Design</t>
+          <t>MHA</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Accounts Manager</t>
         </is>
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>tyler@green-cardinaldesign.com</t>
+          <t>taimur.sultan@mha.co.uk</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>07881941338</t>
+          <t>+44 (0)204 546 6050</t>
         </is>
       </c>
       <c r="G216" s="6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I216" s="6" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J216" s="6" t="n">
         <v>1</v>
@@ -11732,14 +11728,14 @@
       </c>
       <c r="L216" s="8" t="inlineStr">
         <is>
-          <t>Builds and maintains the REL Finance website; sends monthly traffic analytics</t>
+          <t>Prepares REL's quarterly management accounts - day-to-day MHA contact</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>Office of Financial Sanctions Implementation</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="B217" s="15" t="inlineStr">
@@ -11749,47 +11745,47 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>HM Treasury</t>
+          <t>Feed.fm</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr"/>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>ofsi@hmtreasury.gov.uk</t>
+          <t>rob@feed.fm</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr"/>
       <c r="G217" s="6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H217" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I217" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J217" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K217" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K217" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L217" s="8" t="inlineStr">
         <is>
-          <t>HM Treasury sanctions unit handling REL's OFSI submission INT/2025/8106728</t>
+          <t>Replied to an Adaptr (Feed.fm) music licensing web enquiry.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>Laurel Weikert</t>
+          <t>Tyler Sear</t>
         </is>
       </c>
       <c r="B218" s="15" t="inlineStr">
@@ -11799,35 +11795,39 @@
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Green Cardinal Design</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>laurel.j.weikert@rippling.com</t>
-        </is>
-      </c>
-      <c r="F218" s="4" t="inlineStr"/>
+          <t>tyler@green-cardinaldesign.com</t>
+        </is>
+      </c>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>07881941338</t>
+        </is>
+      </c>
       <c r="G218" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H218" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I218" s="6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J218" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
@@ -11836,14 +11836,14 @@
       </c>
       <c r="L218" s="8" t="inlineStr">
         <is>
-          <t>Rippling HR/payroll platform sales rep prospecting REL</t>
+          <t>Builds and maintains the REL Finance website; sends monthly traffic analytics</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>Benji Dymant</t>
+          <t>Office of Financial Sanctions Implementation</t>
         </is>
       </c>
       <c r="B219" s="15" t="inlineStr">
@@ -11853,51 +11853,47 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Teneo</t>
-        </is>
-      </c>
-      <c r="D219" s="4" t="inlineStr">
-        <is>
-          <t>Senior Managing Director</t>
-        </is>
-      </c>
+          <t>HM Treasury</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr"/>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>benji.dymant@teneo.com</t>
+          <t>ofsi@hmtreasury.gov.uk</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr"/>
       <c r="G219" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H219" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I219" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J219" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K219" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K219" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L219" s="8" t="inlineStr">
         <is>
-          <t>Teneo advisory on the OFSI sanctions licence submission INT/2025/8106728</t>
+          <t>HM Treasury sanctions unit handling REL's OFSI submission INT/2025/8106728</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>Rebecca Leeser</t>
+          <t>Laurel Weikert</t>
         </is>
       </c>
       <c r="B220" s="15" t="inlineStr">
@@ -11907,82 +11903,86 @@
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Teneo</t>
-        </is>
-      </c>
-      <c r="D220" s="4" t="inlineStr"/>
+          <t>Rippling</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>rebecca.leeser@teneo.com</t>
+          <t>laurel.j.weikert@rippling.com</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr"/>
       <c r="G220" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H220" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I220" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J220" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K220" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K220" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L220" s="8" t="inlineStr">
         <is>
-          <t>Teneo team on the OFSI sanctions licence submission</t>
+          <t>Rippling HR/payroll platform sales rep prospecting REL</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>Tashin Morjaria</t>
-        </is>
-      </c>
-      <c r="B221" s="16" t="inlineStr">
-        <is>
-          <t>Internal (REL Finance)</t>
+          <t>Benji Dymant</t>
+        </is>
+      </c>
+      <c r="B221" s="15" t="inlineStr">
+        <is>
+          <t>Service Provider</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Morka Group</t>
+          <t>Teneo</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Senior Managing Director</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>tashin@morkagroup.com</t>
+          <t>benji.dymant@teneo.com</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr"/>
       <c r="G221" s="6" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H221" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="I221" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J221" s="6" t="n">
         <v>0</v>
@@ -11994,72 +11994,64 @@
       </c>
       <c r="L221" s="8" t="inlineStr">
         <is>
-          <t>REL Finance Director writing from his Morka Group address</t>
+          <t>Teneo advisory on the OFSI sanctions licence submission INT/2025/8106728</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>Chloe Jiang</t>
-        </is>
-      </c>
-      <c r="B222" s="16" t="inlineStr">
-        <is>
-          <t>Internal (REL Finance)</t>
+          <t>Rebecca Leeser</t>
+        </is>
+      </c>
+      <c r="B222" s="15" t="inlineStr">
+        <is>
+          <t>Service Provider</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>REL Finance</t>
-        </is>
-      </c>
-      <c r="D222" s="4" t="inlineStr">
-        <is>
-          <t>Head of Investor Relations</t>
-        </is>
-      </c>
+          <t>Teneo</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr"/>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>info@relfinance.co.uk</t>
-        </is>
-      </c>
-      <c r="F222" s="4" t="inlineStr">
-        <is>
-          <t>+44 7788 284403</t>
-        </is>
-      </c>
+          <t>rebecca.leeser@teneo.com</t>
+        </is>
+      </c>
+      <c r="F222" s="4" t="inlineStr"/>
       <c r="G222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="I222" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J222" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K222" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K222" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L222" s="8" t="inlineStr">
         <is>
-          <t>REL general enquiries inbox; forwarded the Priory Park Hotel, Kilburn development exit bridge enquiry</t>
+          <t>Teneo team on the OFSI sanctions licence submission</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>Sophie Thornton</t>
+          <t>Tashin Morjaria</t>
         </is>
       </c>
       <c r="B223" s="16" t="inlineStr">
@@ -12069,31 +12061,35 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>REL Finance</t>
-        </is>
-      </c>
-      <c r="D223" s="4" t="inlineStr"/>
+          <t>Morka Group</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>sophie@relfinance.co.uk</t>
+          <t>tashin@morkagroup.com</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr"/>
       <c r="G223" s="6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H223" s="6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I223" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J223" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
@@ -12102,14 +12098,14 @@
       </c>
       <c r="L223" s="8" t="inlineStr">
         <is>
-          <t>REL colleague; Teams admin and Oryx 2 scheduled payment notifications</t>
+          <t>REL Finance Director writing from his Morka Group address</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>Sumeer Bose</t>
+          <t>Chloe Jiang</t>
         </is>
       </c>
       <c r="B224" s="16" t="inlineStr">
@@ -12124,27 +12120,31 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Head of Investor Relations</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>bosesumeer@gmail.com</t>
-        </is>
-      </c>
-      <c r="F224" s="4" t="inlineStr"/>
+          <t>info@relfinance.co.uk</t>
+        </is>
+      </c>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>+44 7788 284403</t>
+        </is>
+      </c>
       <c r="G224" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H224" s="6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I224" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J224" s="6" t="n">
         <v>0</v>
@@ -12156,14 +12156,14 @@
       </c>
       <c r="L224" s="8" t="inlineStr">
         <is>
-          <t>Personal Gmail of REL director Sumeer Bose; used to forward domain/SaaS admin notices</t>
+          <t>REL general enquiries inbox; forwarded the Priory Park Hotel, Kilburn development exit bridge enquiry</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>Sumeer Bose</t>
+          <t>Sophie Thornton</t>
         </is>
       </c>
       <c r="B225" s="16" t="inlineStr">
@@ -12176,36 +12176,28 @@
           <t>REL Finance</t>
         </is>
       </c>
-      <c r="D225" s="4" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
+      <c r="D225" s="4" t="inlineStr"/>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>sumeer@relfinance.co.uk</t>
-        </is>
-      </c>
-      <c r="F225" s="4" t="inlineStr">
-        <is>
-          <t>+44 7825216771</t>
-        </is>
-      </c>
+          <t>sophie@relfinance.co.uk</t>
+        </is>
+      </c>
+      <c r="F225" s="4" t="inlineStr"/>
       <c r="G225" s="6" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H225" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="I225" s="6" t="n">
-        <v>492</v>
+        <v>1</v>
       </c>
       <c r="J225" s="6" t="n">
-        <v>182</v>
+        <v>1</v>
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
@@ -12214,14 +12206,14 @@
       </c>
       <c r="L225" s="8" t="inlineStr">
         <is>
-          <t>REL director; fronts origination, terms and loan management across the book</t>
+          <t>REL colleague; Teams admin and Oryx 2 scheduled payment notifications</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>Tashin Morjaria</t>
+          <t>Sumeer Bose</t>
         </is>
       </c>
       <c r="B226" s="16" t="inlineStr">
@@ -12241,29 +12233,25 @@
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>tashin@relfinance.co.uk</t>
-        </is>
-      </c>
-      <c r="F226" s="4" t="inlineStr">
-        <is>
-          <t>+44 7739555265</t>
-        </is>
-      </c>
+          <t>bosesumeer@gmail.com</t>
+        </is>
+      </c>
+      <c r="F226" s="4" t="inlineStr"/>
       <c r="G226" s="6" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I226" s="6" t="n">
-        <v>280</v>
+        <v>2</v>
       </c>
       <c r="J226" s="6" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
@@ -12272,48 +12260,56 @@
       </c>
       <c r="L226" s="8" t="inlineStr">
         <is>
-          <t>REL director; fronts origination and deal execution across the book</t>
+          <t>Personal Gmail of REL director Sumeer Bose; used to forward domain/SaaS admin notices</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>Shyam Lakhani</t>
-        </is>
-      </c>
-      <c r="B227" s="17" t="inlineStr">
-        <is>
-          <t>Personal / Other</t>
+          <t>Sumeer Bose</t>
+        </is>
+      </c>
+      <c r="B227" s="16" t="inlineStr">
+        <is>
+          <t>Internal (REL Finance)</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Department for Education</t>
-        </is>
-      </c>
-      <c r="D227" s="4" t="inlineStr"/>
+          <t>REL Finance</t>
+        </is>
+      </c>
+      <c r="D227" s="4" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>shyam.lakhani@education.gov.uk</t>
-        </is>
-      </c>
-      <c r="F227" s="4" t="inlineStr"/>
+          <t>sumeer@relfinance.co.uk</t>
+        </is>
+      </c>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>+44 7825216771</t>
+        </is>
+      </c>
       <c r="G227" s="6" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="H227" s="6" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I227" s="6" t="n">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="J227" s="6" t="n">
-        <v>5</v>
+        <v>182</v>
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
@@ -12322,48 +12318,56 @@
       </c>
       <c r="L227" s="8" t="inlineStr">
         <is>
-          <t>Mailbox owner's former Department for Education address, used for self-forwarded mail.</t>
+          <t>REL director; fronts origination, terms and loan management across the book</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>Rishi</t>
-        </is>
-      </c>
-      <c r="B228" s="17" t="inlineStr">
-        <is>
-          <t>Personal / Other</t>
+          <t>Tashin Morjaria</t>
+        </is>
+      </c>
+      <c r="B228" s="16" t="inlineStr">
+        <is>
+          <t>Internal (REL Finance)</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Keylife Financial Services</t>
-        </is>
-      </c>
-      <c r="D228" s="4" t="inlineStr"/>
+          <t>REL Finance</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>rishi@keylifefs.com</t>
-        </is>
-      </c>
-      <c r="F228" s="4" t="inlineStr"/>
+          <t>tashin@relfinance.co.uk</t>
+        </is>
+      </c>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>+44 7739555265</t>
+        </is>
+      </c>
       <c r="G228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="H228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I228" s="6" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="J228" s="6" t="n">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
@@ -12372,14 +12376,14 @@
       </c>
       <c r="L228" s="8" t="inlineStr">
         <is>
-          <t>New contact 30/07 — Shyam sent his work email and the REL website. No deal traffic yet, so the category is a placeholder; correct it once his role is clear.</t>
+          <t>REL director; fronts origination and deal execution across the book</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>Abdul Rashid</t>
+          <t>Shyam Lakhani</t>
         </is>
       </c>
       <c r="B229" s="17" t="inlineStr">
@@ -12387,29 +12391,33 @@
           <t>Personal / Other</t>
         </is>
       </c>
-      <c r="C229" s="4" t="inlineStr"/>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>Department for Education</t>
+        </is>
+      </c>
       <c r="D229" s="4" t="inlineStr"/>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>qabdul1rash1@gmail.com</t>
+          <t>shyam.lakhani@education.gov.uk</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr"/>
       <c r="G229" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H229" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="I229" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J229" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
@@ -12418,14 +12426,14 @@
       </c>
       <c r="L229" s="8" t="inlineStr">
         <is>
-          <t>Recipient of Shyam's personal "bag radar log" file share</t>
+          <t>Mailbox owner's former Department for Education address, used for self-forwarded mail.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>Anish Vora</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="B230" s="17" t="inlineStr">
@@ -12433,41 +12441,49 @@
           <t>Personal / Other</t>
         </is>
       </c>
-      <c r="C230" s="4" t="inlineStr"/>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>Keylife Financial Services</t>
+        </is>
+      </c>
       <c r="D230" s="4" t="inlineStr"/>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>anishvora18@gmail.com</t>
+          <t>rishi@keylifefs.com</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr"/>
       <c r="G230" s="6" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H230" s="6" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I230" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J230" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K230" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
-        </is>
-      </c>
-      <c r="L230" s="8" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="K230" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L230" s="8" t="inlineStr">
+        <is>
+          <t>New contact 30/07 — Shyam sent his work email and the REL website. No deal traffic yet, so the category is a placeholder; correct it once his role is clear.</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>Abdul Rashid</t>
         </is>
       </c>
       <c r="B231" s="17" t="inlineStr">
@@ -12479,37 +12495,41 @@
       <c r="D231" s="4" t="inlineStr"/>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>chloej0027@gmail.com</t>
+          <t>qabdul1rash1@gmail.com</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr"/>
       <c r="G231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I231" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J231" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K231" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
-        </is>
-      </c>
-      <c r="L231" s="8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K231" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L231" s="8" t="inlineStr">
+        <is>
+          <t>Recipient of Shyam's personal "bag radar log" file share</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>Darren Halcrow</t>
+          <t>Anish Vora</t>
         </is>
       </c>
       <c r="B232" s="17" t="inlineStr">
@@ -12521,41 +12541,37 @@
       <c r="D232" s="4" t="inlineStr"/>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>darren.halcrow@hotmail.co.uk</t>
+          <t>anishvora18@gmail.com</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr"/>
       <c r="G232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="I232" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J232" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K232" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
-        </is>
-      </c>
-      <c r="L232" s="8" t="inlineStr">
-        <is>
-          <t>Recipient of Shyam's personal "bag radar log" file share</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K232" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
+        </is>
+      </c>
+      <c r="L232" s="8" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>Deepesh Thakrar</t>
+          <t>Chloe</t>
         </is>
       </c>
       <c r="B233" s="17" t="inlineStr">
@@ -12567,18 +12583,18 @@
       <c r="D233" s="4" t="inlineStr"/>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>dc.thakrar@gmail.com</t>
+          <t>chloej0027@gmail.com</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr"/>
       <c r="G233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="I233" s="6" t="n">
@@ -12597,7 +12613,7 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>Gary Brooks</t>
+          <t>Darren Halcrow</t>
         </is>
       </c>
       <c r="B234" s="17" t="inlineStr">
@@ -12609,7 +12625,7 @@
       <c r="D234" s="4" t="inlineStr"/>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>garyjbrooks@gmail.com</t>
+          <t>darren.halcrow@hotmail.co.uk</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr"/>
@@ -12643,7 +12659,7 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>J Crypto</t>
+          <t>Deepesh Thakrar</t>
         </is>
       </c>
       <c r="B235" s="17" t="inlineStr">
@@ -12655,29 +12671,29 @@
       <c r="D235" s="4" t="inlineStr"/>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>jcrypto401@gmail.com</t>
+          <t>dc.thakrar@gmail.com</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr"/>
       <c r="G235" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H235" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I235" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J235" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K235" s="4" t="inlineStr">
-        <is>
-          <t>Direct correspondence</t>
+      <c r="K235" s="7" t="inlineStr">
+        <is>
+          <t>Named in a thread</t>
         </is>
       </c>
       <c r="L235" s="8" t="inlineStr"/>
@@ -12685,7 +12701,7 @@
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>Joel Smart</t>
+          <t>Gary Brooks</t>
         </is>
       </c>
       <c r="B236" s="17" t="inlineStr">
@@ -12697,7 +12713,7 @@
       <c r="D236" s="4" t="inlineStr"/>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>joelsmart2023@gmail.com</t>
+          <t>garyjbrooks@gmail.com</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr"/>
@@ -12731,7 +12747,7 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>Malus Entity</t>
+          <t>J Crypto</t>
         </is>
       </c>
       <c r="B237" s="17" t="inlineStr">
@@ -12743,41 +12759,37 @@
       <c r="D237" s="4" t="inlineStr"/>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>malus.entity@gmail.com</t>
+          <t>jcrypto401@gmail.com</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr"/>
       <c r="G237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I237" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J237" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K237" s="4" t="inlineStr">
         <is>
           <t>Direct correspondence</t>
         </is>
       </c>
-      <c r="L237" s="8" t="inlineStr">
-        <is>
-          <t>Recipient of Shyam's personal "bag radar log" file share</t>
-        </is>
-      </c>
+      <c r="L237" s="8" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>Shyam Lakhani</t>
+          <t>Joel Smart</t>
         </is>
       </c>
       <c r="B238" s="17" t="inlineStr">
@@ -12789,25 +12801,25 @@
       <c r="D238" s="4" t="inlineStr"/>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>slakhani0203@gmail.com</t>
+          <t>joelsmart2023@gmail.com</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr"/>
       <c r="G238" s="6" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I238" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J238" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K238" s="4" t="inlineStr">
         <is>
@@ -12816,14 +12828,14 @@
       </c>
       <c r="L238" s="8" t="inlineStr">
         <is>
-          <t>Mailbox owner's personal Gmail; REL Finance employment offer correspondence.</t>
+          <t>Recipient of Shyam's personal "bag radar log" file share</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>Shyam Lakhani</t>
+          <t>Malus Entity</t>
         </is>
       </c>
       <c r="B239" s="17" t="inlineStr">
@@ -12835,39 +12847,131 @@
       <c r="D239" s="4" t="inlineStr"/>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>shyam_302@hotmail.co.uk</t>
+          <t>malus.entity@gmail.com</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr"/>
       <c r="G239" s="6" t="inlineStr">
         <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H239" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="I239" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K239" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L239" s="8" t="inlineStr">
+        <is>
+          <t>Recipient of Shyam's personal "bag radar log" file share</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>Shyam Lakhani</t>
+        </is>
+      </c>
+      <c r="B240" s="17" t="inlineStr">
+        <is>
+          <t>Personal / Other</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr"/>
+      <c r="D240" s="4" t="inlineStr"/>
+      <c r="E240" s="4" t="inlineStr">
+        <is>
+          <t>slakhani0203@gmail.com</t>
+        </is>
+      </c>
+      <c r="F240" s="4" t="inlineStr"/>
+      <c r="G240" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="H240" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I240" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J240" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K240" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L240" s="8" t="inlineStr">
+        <is>
+          <t>Mailbox owner's personal Gmail; REL Finance employment offer correspondence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>Shyam Lakhani</t>
+        </is>
+      </c>
+      <c r="B241" s="17" t="inlineStr">
+        <is>
+          <t>Personal / Other</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr"/>
+      <c r="D241" s="4" t="inlineStr"/>
+      <c r="E241" s="4" t="inlineStr">
+        <is>
+          <t>shyam_302@hotmail.co.uk</t>
+        </is>
+      </c>
+      <c r="F241" s="4" t="inlineStr"/>
+      <c r="G241" s="6" t="inlineStr">
+        <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="H239" s="6" t="inlineStr">
+      <c r="H241" s="6" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="I239" s="6" t="n">
+      <c r="I241" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J239" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K239" s="4" t="inlineStr">
+      <c r="J241" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" s="4" t="inlineStr">
         <is>
           <t>Direct correspondence</t>
         </is>
       </c>
-      <c r="L239" s="8" t="inlineStr">
+      <c r="L241" s="8" t="inlineStr">
         <is>
           <t>Mailbox owner's own personal Hotmail address</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L239"/>
+  <autoFilter ref="A4:L241"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
@@ -12915,7 +13019,7 @@
         </is>
       </c>
       <c r="B4" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$239,A4)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$241,A4)</f>
         <v/>
       </c>
     </row>
@@ -12926,7 +13030,7 @@
         </is>
       </c>
       <c r="B5" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$239,A5)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$241,A5)</f>
         <v/>
       </c>
     </row>
@@ -12937,7 +13041,7 @@
         </is>
       </c>
       <c r="B6" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$239,A6)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$241,A6)</f>
         <v/>
       </c>
     </row>
@@ -12948,7 +13052,7 @@
         </is>
       </c>
       <c r="B7" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$239,A7)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$241,A7)</f>
         <v/>
       </c>
     </row>
@@ -12959,7 +13063,7 @@
         </is>
       </c>
       <c r="B8" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$239,A8)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$241,A8)</f>
         <v/>
       </c>
     </row>
@@ -12970,7 +13074,7 @@
         </is>
       </c>
       <c r="B9" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$239,A9)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$241,A9)</f>
         <v/>
       </c>
     </row>
@@ -12981,7 +13085,7 @@
         </is>
       </c>
       <c r="B10" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$239,A10)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$241,A10)</f>
         <v/>
       </c>
     </row>
@@ -12992,7 +13096,7 @@
         </is>
       </c>
       <c r="B11" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$239,A11)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$241,A11)</f>
         <v/>
       </c>
     </row>
@@ -13003,7 +13107,7 @@
         </is>
       </c>
       <c r="B12" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$239,A12)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$241,A12)</f>
         <v/>
       </c>
     </row>
@@ -13014,7 +13118,7 @@
         </is>
       </c>
       <c r="B13" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$239,A13)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$241,A13)</f>
         <v/>
       </c>
     </row>

--- a/Contact_List_REL.xlsx
+++ b/Contact_List_REL.xlsx
@@ -12,7 +12,7 @@
     <sheet name="README" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contact List'!$A$4:$L$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contact List'!$A$4:$L$244</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L243"/>
+  <dimension ref="A1:L244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -638,7 +638,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Built automatically from Outlook (shyam@relfinance.co.uk) — last refreshed 2026-08-13. Refreshed weekly; do not hand-edit (see README tab).</t>
+          <t>Built automatically from Outlook (shyam@relfinance.co.uk) — last refreshed 2026-08-14. Refreshed weekly; do not hand-edit (see README tab).</t>
         </is>
       </c>
     </row>
@@ -1986,11 +1986,11 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I29" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J29" s="6" t="n">
         <v>0</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I30" s="6" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I80" s="6" t="n">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I83" s="6" t="n">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I86" s="6" t="n">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I87" s="6" t="n">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I88" s="6" t="n">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I111" s="6" t="n">
@@ -7806,11 +7806,11 @@
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I141" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J141" s="6" t="n">
         <v>3</v>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="I144" s="6" t="n">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="I145" s="6" t="n">
@@ -8084,11 +8084,11 @@
       </c>
       <c r="H146" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="I146" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J146" s="6" t="n">
         <v>0</v>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="H196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I196" s="6" t="n">
@@ -10688,7 +10688,11 @@
           <t>Osborne Clarke</t>
         </is>
       </c>
-      <c r="D197" s="4" t="inlineStr"/>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
           <t>savina.sangha@osborneclarke.com</t>
@@ -10702,18 +10706,18 @@
       </c>
       <c r="H197" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I197" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J197" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K197" s="7" t="inlineStr">
-        <is>
-          <t>Named in a thread</t>
+      <c r="K197" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
         </is>
       </c>
       <c r="L197" s="8" t="inlineStr">
@@ -12402,11 +12406,11 @@
       </c>
       <c r="H229" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I229" s="6" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="J229" s="6" t="n">
         <v>182</v>
@@ -12460,11 +12464,11 @@
       </c>
       <c r="H230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I230" s="6" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J230" s="6" t="n">
         <v>170</v>
@@ -12981,7 +12985,7 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>Shyam Lakhani</t>
+          <t>Riana Karia</t>
         </is>
       </c>
       <c r="B242" s="17" t="inlineStr">
@@ -12993,25 +12997,25 @@
       <c r="D242" s="4" t="inlineStr"/>
       <c r="E242" s="4" t="inlineStr">
         <is>
-          <t>slakhani0203@gmail.com</t>
+          <t>rianakaria@icloud.com</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr"/>
       <c r="G242" s="6" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I242" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J242" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K242" s="4" t="inlineStr">
         <is>
@@ -13020,7 +13024,7 @@
       </c>
       <c r="L242" s="8" t="inlineStr">
         <is>
-          <t>Mailbox owner's personal Gmail; REL Finance employment offer correspondence.</t>
+          <t>Authored the REL / LandlordInvest JV proposal paper sent to the directors 13/08. Personal address, no firm given — category is a placeholder until her role is clear.</t>
         </is>
       </c>
     </row>
@@ -13039,25 +13043,25 @@
       <c r="D243" s="4" t="inlineStr"/>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>shyam_302@hotmail.co.uk</t>
+          <t>slakhani0203@gmail.com</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr"/>
       <c r="G243" s="6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H243" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I243" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J243" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K243" s="4" t="inlineStr">
         <is>
@@ -13066,12 +13070,58 @@
       </c>
       <c r="L243" s="8" t="inlineStr">
         <is>
+          <t>Mailbox owner's personal Gmail; REL Finance employment offer correspondence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>Shyam Lakhani</t>
+        </is>
+      </c>
+      <c r="B244" s="17" t="inlineStr">
+        <is>
+          <t>Personal / Other</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr"/>
+      <c r="D244" s="4" t="inlineStr"/>
+      <c r="E244" s="4" t="inlineStr">
+        <is>
+          <t>shyam_302@hotmail.co.uk</t>
+        </is>
+      </c>
+      <c r="F244" s="4" t="inlineStr"/>
+      <c r="G244" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="H244" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I244" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J244" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" s="4" t="inlineStr">
+        <is>
+          <t>Direct correspondence</t>
+        </is>
+      </c>
+      <c r="L244" s="8" t="inlineStr">
+        <is>
           <t>Mailbox owner's own personal Hotmail address</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L243"/>
+  <autoFilter ref="A4:L244"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
@@ -13119,7 +13169,7 @@
         </is>
       </c>
       <c r="B4" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$243,A4)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$244,A4)</f>
         <v/>
       </c>
     </row>
@@ -13130,7 +13180,7 @@
         </is>
       </c>
       <c r="B5" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$243,A5)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$244,A5)</f>
         <v/>
       </c>
     </row>
@@ -13141,7 +13191,7 @@
         </is>
       </c>
       <c r="B6" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$243,A6)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$244,A6)</f>
         <v/>
       </c>
     </row>
@@ -13152,7 +13202,7 @@
         </is>
       </c>
       <c r="B7" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$243,A7)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$244,A7)</f>
         <v/>
       </c>
     </row>
@@ -13163,7 +13213,7 @@
         </is>
       </c>
       <c r="B8" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$243,A8)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$244,A8)</f>
         <v/>
       </c>
     </row>
@@ -13174,7 +13224,7 @@
         </is>
       </c>
       <c r="B9" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$243,A9)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$244,A9)</f>
         <v/>
       </c>
     </row>
@@ -13185,7 +13235,7 @@
         </is>
       </c>
       <c r="B10" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$243,A10)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$244,A10)</f>
         <v/>
       </c>
     </row>
@@ -13196,7 +13246,7 @@
         </is>
       </c>
       <c r="B11" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$243,A11)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$244,A11)</f>
         <v/>
       </c>
     </row>
@@ -13207,7 +13257,7 @@
         </is>
       </c>
       <c r="B12" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$243,A12)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$244,A12)</f>
         <v/>
       </c>
     </row>
@@ -13218,7 +13268,7 @@
         </is>
       </c>
       <c r="B13" s="21">
-        <f>COUNTIF('Contact List'!$B$5:$B$243,A13)</f>
+        <f>COUNTIF('Contact List'!$B$5:$B$244,A13)</f>
         <v/>
       </c>
     </row>

--- a/Contact_List_REL.xlsx
+++ b/Contact_List_REL.xlsx
@@ -12160,7 +12160,7 @@
       </c>
       <c r="B225" s="16" t="inlineStr">
         <is>
-          <t>Internal (REL Finance)</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="B226" s="16" t="inlineStr">
         <is>
-          <t>Internal (REL Finance)</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="B227" s="16" t="inlineStr">
         <is>
-          <t>Internal (REL Finance)</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="B228" s="16" t="inlineStr">
         <is>
-          <t>Internal (REL Finance)</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="B229" s="16" t="inlineStr">
         <is>
-          <t>Internal (REL Finance)</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="B230" s="16" t="inlineStr">
         <is>
-          <t>Internal (REL Finance)</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
@@ -13253,7 +13253,7 @@
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
         <is>
-          <t>Internal (REL Finance)</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="B12" s="21">
@@ -13323,7 +13323,7 @@
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>Every external (and internal) contact from Shyam Lakhani's Outlook mailbox, categorised as Broker, Lender / Bank, Borrower / Sponsor, Solicitor / Legal, Valuer, Investor, Accountant, Service Provider, Internal or Other.</t>
+          <t>Every external (and internal) contact from Shyam Lakhani Outlook mailbox, categorised as Broker, Lender / Bank, Borrower / Sponsor, Solicitor / Legal, Valuer, Investor, Accountant, Service Provider, Internal or Other.</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
         <is>
-          <t>3. 'How Found' says where the address came from. 'Direct correspondence' means the contact has emailed Shyam or been emailed by him. 'Named in a thread' means the address was recovered from a forwarded message header or a quoted signature — the contact is real, but nobody at REL has emailed them from this mailbox.</t>
+          <t>3. 'How Found' says where the address came from. 'Direct correspondence' means the contact has emailed Shyam or been emailed by them. 'Named in a thread' means the address was recovered from a forwarded message header or a quoted signature — the contact is real, but nobody at REL has emailed them from this mailbox.</t>
         </is>
       </c>
     </row>
